--- a/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="79332" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="82501" uniqueCount="1130">
   <si>
     <t>Year</t>
   </si>
@@ -2351,6 +2351,1059 @@
   </si>
   <si>
     <t>C:\Users\Tyler\Downloads\JUNIOR LAB SPRING 2026\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\fracture\Fracture_20251119_175941_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10444\compression\COMPRESSION_20250407_192028_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10444\compression\COMPRESSION_20250407_192028_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10444\tension\TENSION_20250407_190145_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10444\tension\TENSION_20250407_190145_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10444\fracture\Fracture_20250407_193026_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10444\fracture\Fracture_20250407_193026_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10444\fracture\Fracture_20250407_193026_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10444\fracture\Fracture_20250407_193026_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10444\fracture\Fracture_20250407_193026_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10444\fracture\Fracture_20250407_193026_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10444\fracture\Fracture_20250407_193026_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10444\fracture\Fracture_20250407_193026_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10448\compression\COMPRESSION_20250410_122710_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10448\compression\COMPRESSION_20250410_122710_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10448\tension\TENSION_20250410_121606_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10448\tension\TENSION_20250408_85829_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10448\fracture\Fracture_20250407_85345_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10448\fracture\Fracture_20250407_85345_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10448\fracture\Fracture_20250407_85345_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10448\fracture\Fracture_20250407_85345_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10448\fracture\Fracture_20250407_85345_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10448\fracture\Fracture_20250407_85345_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10448\fracture\Fracture_20250407_85345_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10448\fracture\Fracture_20250407_85345_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10451\compression\COMPRESSION_20250407_155960_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10451\tension\TENSION_20250407_164257_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10451\tension\TENSION_20250407_164257_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10451\fracture\Fracture_20250407_170752_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10451\fracture\Fracture_20250407_170752_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10451\fracture\Fracture_20250407_170752_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10451\fracture\Fracture_20250407_170752_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10451\fracture\Fracture_20250407_170752_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10451\fracture\Fracture_20250407_170752_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\monday\monday_10451\fracture\Fracture_20250407_170752_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10438\compression\CNT Compression_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10438\compression\CNT Compression_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10438\tension\CNT Tension_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10438\tension\CNT Tension_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10438\fracture\Epoxy 4 Compact Tension_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10438\fracture\Epoxy 4 Compact Tension_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10438\fracture\Epoxy 4 Compact Tension_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10438\fracture\Epoxy 4 Compact Tension_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10438\fracture\Epoxy 4 Compact Tension_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10438\fracture\Epoxy 4 Compact Tension_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10438\fracture\Epoxy 4 Compact Tension_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10438\fracture\Epoxy 4 Compact Tension_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10447\compression\COMPRESSION_20250408_144234_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10447\compression\COMPRESSION_20250408_144234_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10447\tension\TENSION_20250408_142244_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10447\fracture\Fracture_20250408_152121_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10447\fracture\Fracture_20250408_152121_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10447\fracture\Fracture_20250408_152121_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10447\fracture\Fracture_20250408_152121_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10447\fracture\Fracture_20250408_150531_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10447\fracture\Fracture_20250408_150531_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10447\fracture\Fracture_20250408_150531_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10452\compression\COMPRESSION_20250408_83342_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10452\compression\COMPRESSION_20250408_83342_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10452\tension\TENSION_20250408_85829_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10452\tension\TENSION_20250408_85829_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10452\fracture\Fracture_20250408_91538_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10452\fracture\Fracture_20250408_91538_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10452\fracture\Fracture_20250408_91538_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10452\fracture\Fracture_20250408_91538_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10452\fracture\Fracture_20250408_91538_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10452\fracture\Fracture_20250408_91538_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10452\fracture\Fracture_20250408_91538_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10452\fracture\Fracture_20250408_91538_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10454\compression\compression_epoxy_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10454\compression\compression_cnt_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10454\fracture\compactTension_cnt_4_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10454\fracture\compactTension_cnt_4_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10454\fracture\compactTension_cnt_4_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10454\fracture\compactTension_cnt_4_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10454\fracture\compactTension_cnt_4_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10454\fracture\compactTension_cnt_4_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10454\fracture\compactTension_cnt_4_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\tuesday\tuesday_10454\fracture\compactTension_cnt_4_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\compression\COMPRESSION_20250409_172535_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\compression\COMPRESSION_20250409_172535_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\tension\TENSION_20250409_171048_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\tension\TENSION_20250409_171048_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\compression\COMPRESSION_20250409_141814_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\compression\COMPRESSION_20250409_141814_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\compression\COMPRESSION_20250410_143927_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\compression\COMPRESSION_20250410_143927_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\tension\TENSION_20250410_151057_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10446\tension\TENSION_20250410_151057_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\compression\COMPRESSION_20250409_83645_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\compression\COMPRESSION_20250409_83645_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\fracture\Fracture_20250410_124314_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10435\compression\COMPRESSION_20250410_90238_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10435\compression\COMPRESSION_20250410_90238_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10435\fracture\Fracture_20250410_82559_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10435\fracture\Fracture_20250410_82559_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10435\fracture\Fracture_20250410_82559_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10435\fracture\Fracture_20250410_82559_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10435\fracture\Fracture_20250410_82559_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10435\fracture\Fracture_20250410_82559_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10435\fracture\Fracture_20250410_82559_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10435\fracture\Fracture_20250410_82559_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10437\compression\COMPRESSION_20250410_122710_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10437\compression\COMPRESSION_20250410_122710_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10437\tension\TENSION_20250410_121606_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10437\tension\TENSION_20250408_85829_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10437\fracture\Fracture_20250410_130126_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10437\fracture\Fracture_20250410_130126_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10437\fracture\Fracture_20250410_130126_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10437\fracture\Fracture_20250410_130126_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10437\fracture\Fracture_20250410_124314_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10437\fracture\Fracture_20250410_124314_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10437\fracture\Fracture_20250410_124314_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\thursday\thursday_10437\fracture\Fracture_20250410_124314_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10436\compression\COMPRESSION_20250411_120041_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10436\compression\COMPRESSION_20250411_120041_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10436\tension\TENSION_20250411_113816_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10436\tension\TENSION_20250411_113816_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10436\fracture\Fracture_20250411_121036_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10436\fracture\Fracture_20250411_121036_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10436\fracture\Fracture_20250411_121036_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10436\fracture\Fracture_20250411_121036_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10436\fracture\Fracture_20250411_121036_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10436\fracture\Fracture_20250411_121036_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10436\fracture\Fracture_20250411_121036_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10436\fracture\Fracture_20250411_121036_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10450\compression\COMPRESSION_20250411_150039_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10450\compression\COMPRESSION_20250411_150039_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10450\tension\TENSION_20250411_145017_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10450\fracture\Fracture_20250411_151909_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10450\fracture\Fracture_20250411_151909_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10450\fracture\Fracture_20250411_151909_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10450\fracture\Fracture_20250411_151909_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10450\fracture\Fracture_20250411_151909_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10450\fracture\Fracture_20250411_151909_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10450\fracture\Fracture_20250411_151909_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch1\friday\friday_10450\fracture\Fracture_20250411_151909_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10444\compression\COMPRESSION_20250407_192028_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10444\tension\TENSION_20250407_190145_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10444\tension\TENSION_20250407_190145_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10444\fracture\Fracture_20250407_193026_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10444\fracture\Fracture_20250407_193026_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10444\fracture\Fracture_20250407_193026_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10444\fracture\Fracture_20250407_193026_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10444\fracture\Fracture_20250407_193026_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10444\fracture\Fracture_20250407_193026_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10444\fracture\Fracture_20250407_193026_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10444\fracture\Fracture_20250407_193026_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10448\compression\COMPRESSION_20250421_90459_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10448\compression\COMPRESSION_20250421_90459_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10448\tension\TENSION_20250421_84334_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10448\tension\TENSION_20250421_84334_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10448\fracture\Fracture_20250421_91433_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10448\fracture\Fracture_20250421_91433_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10448\fracture\Fracture_20250421_91433_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10448\fracture\Fracture_20250421_91433_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10448\fracture\Fracture_20250421_91433_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10448\fracture\Fracture_20250421_91433_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10448\fracture\Fracture_20250421_91433_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10448\fracture\Fracture_20250421_91433_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10451\tension\TENSION_20250407_164257_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10451\tension\TENSION_20250407_164257_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10451\fracture\Fracture_20250407_170752_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10451\fracture\Fracture_20250407_170752_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10451\fracture\Fracture_20250407_170752_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10451\fracture\Fracture_20250407_170752_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10451\fracture\Fracture_20250407_170752_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10451\fracture\Fracture_20250407_170752_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_10451\fracture\Fracture_20250407_170752_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_91284\compression\COMPRESSION_20251117_150528_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_91284\compression\COMPRESSION_20251117_150528_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_91284\tension\TENSION_20251117_144229_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_91284\tension\TENSION_20251117_144229_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_91284\fracture\Fracture_20251117_152233_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_91284\fracture\Fracture_20251117_152233_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_91284\fracture\Fracture_20251117_152233_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_91284\fracture\Fracture_20251117_152233_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_91284\fracture\Fracture_20251117_152233_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_91284\fracture\Fracture_20251117_152233_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_91284\fracture\Fracture_20251117_152233_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\monday\monday_91284\fracture\Fracture_20251117_152233_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10438\compression\CNT Compression_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10438\compression\CNT Compression_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10438\tension\CNT Tension_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10438\tension\CNT Tension_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10438\fracture\Epoxy 4 Compact Tension_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10438\fracture\Epoxy 4 Compact Tension_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10438\fracture\Epoxy 4 Compact Tension_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10438\fracture\Epoxy 4 Compact Tension_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10438\fracture\Epoxy 4 Compact Tension_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10438\fracture\Epoxy 4 Compact Tension_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10438\fracture\Epoxy 4 Compact Tension_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10438\fracture\Epoxy 4 Compact Tension_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10447\compression\COMPRESSION_20250408_144234_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10447\compression\COMPRESSION_20250408_144234_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10447\fracture\Fracture_20250408_152121_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10447\fracture\Fracture_20250408_152121_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10447\fracture\Fracture_20250408_152121_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10447\fracture\Fracture_20250408_152121_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10447\fracture\Fracture_20250408_150531_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10447\fracture\Fracture_20250408_150531_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10447\fracture\Fracture_20250408_150531_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10452\compression\COMPRESSION_20250408_83342_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10452\compression\COMPRESSION_20250408_83342_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10452\tension\TENSION_20250408_85829_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10452\tension\TENSION_20250408_85829_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10452\fracture\Fracture_20250408_91538_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10452\fracture\Fracture_20250408_91538_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10452\fracture\Fracture_20250408_91538_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10452\fracture\Fracture_20250408_91538_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10452\fracture\Fracture_20250408_91538_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10452\fracture\Fracture_20250408_91538_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10452\fracture\Fracture_20250408_91538_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10452\fracture\Fracture_20250408_91538_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10454\compression\compression_epoxy_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10454\compression\compression_cnt_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10454\fracture\compactTension_cnt_4_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10454\fracture\compactTension_cnt_4_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10454\fracture\compactTension_cnt_4_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10454\fracture\compactTension_cnt_4_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10454\fracture\compactTension_cnt_4_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10454\fracture\compactTension_cnt_4_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10454\fracture\compactTension_cnt_4_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_10454\fracture\compactTension_cnt_4_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_80463\compression\COMPRESSION_20251118_160446_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_80463\compression\COMPRESSION_20251118_160446_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_80463\tension\TENSION_20251118_15523_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_80463\tension\TENSION_20251117_144229_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_80463\fracture\Fracture_20251118_162158_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_80463\fracture\Fracture_20251118_162158_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_80463\fracture\Fracture_20251118_162158_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_80463\fracture\Fracture_20251118_162158_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_80463\fracture\Fracture_20251118_162158_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_80463\fracture\Fracture_20251118_162158_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_80463\fracture\Fracture_20251118_162158_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\tuesday\tuesday_80463\fracture\Fracture_20251118_162158_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\compression\COMPRESSION_20250409_172535_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\compression\COMPRESSION_20250409_172535_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\tension\TENSION_20250409_171048_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\tension\TENSION_20250409_171048_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10440\fracture\Fracture_20250409_173835_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\compression\COMPRESSION_20250409_141814_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\compression\COMPRESSION_20250409_141814_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10441\fracture\Fracture_20250409_142846_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10446\compression\COMPRESSION_20250410_143927_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10446\compression\COMPRESSION_20250410_143927_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10446\tension\TENSION_20250410_151057_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10446\tension\TENSION_20250410_151057_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\compression\COMPRESSION_20250409_83645_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\compression\COMPRESSION_20250409_83645_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\fracture\Fracture_20250407_85345_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_10453\fracture\Fracture_20250409_90339_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\compression\COMPRESSION_20251119_182203_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\compression\COMPRESSION_20251119_182203_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\tension\TENSION_20251119_183903_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\tension\TENSION_20251119_183903_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\fracture\Fracture_20251119_175941_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\fracture\Fracture_20251119_175941_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\fracture\Fracture_20251119_175941_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\fracture\Fracture_20251119_175941_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\fracture\Fracture_20251119_175941_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\fracture\Fracture_20251119_175941_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\fracture\Fracture_20251119_175941_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\wednesday\wednesday_80464\fracture\Fracture_20251119_175941_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10435\compression\COMPRESSION_20250410_90238_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10435\compression\COMPRESSION_20250410_90238_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10435\tension\TENSION_20250410_95607_4.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10435\fracture\Fracture_20250410_82559_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10435\fracture\Fracture_20250410_82559_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10435\fracture\Fracture_20250410_82559_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10435\fracture\Fracture_20250410_82559_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10435\fracture\Fracture_20250410_82559_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10435\fracture\Fracture_20250410_82559_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10435\fracture\Fracture_20250410_82559_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10435\fracture\Fracture_20250410_82559_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10437\compression\COMPRESSION_20250410_122710_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10437\compression\COMPRESSION_20250410_122710_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10437\tension\TENSION_20250410_121606_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10437\tension\TENSION_20250421_84334_3.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10437\fracture\Fracture_20250410_130126_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10437\fracture\Fracture_20250410_130126_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10437\fracture\Fracture_20250410_130126_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10437\fracture\Fracture_20250410_130126_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10437\fracture\Fracture_20250410_124314_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10437\fracture\Fracture_20250410_124314_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10437\fracture\Fracture_20250410_124314_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\thursday\thursday_10437\fracture\Fracture_20250410_124314_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10436\compression\COMPRESSION_20250411_120041_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10436\compression\COMPRESSION_20250411_120041_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10436\tension\TENSION_20250411_113816_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10436\fracture\Fracture_20250411_121036_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10436\fracture\Fracture_20250411_121036_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10436\fracture\Fracture_20250411_121036_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10436\fracture\Fracture_20250411_121036_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10436\fracture\Fracture_20250411_121036_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10436\fracture\Fracture_20250411_121036_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10436\fracture\Fracture_20250411_121036_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10436\fracture\Fracture_20250411_121036_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10450\compression\COMPRESSION_20250411_150039_1_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10450\compression\COMPRESSION_20250411_150039_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10450\tension\TENSION_20250411_145017_1.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10450\fracture\Fracture_20250411_151909_7_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10450\fracture\Fracture_20250411_151909_5_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10450\fracture\Fracture_20250411_151909_6_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10450\fracture\Fracture_20250411_151909_8_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10450\fracture\Fracture_20250411_151909_3_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10450\fracture\Fracture_20250411_151909_4_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10450\fracture\Fracture_20250411_151909_2_2.csv</t>
+  </si>
+  <si>
+    <t>C:\Users\PC\GitHub\Junior_Lab_Repo\OrganizedData\2025_organized\batch2\friday\friday_10450\fracture\Fracture_20250411_151909_1_2.csv</t>
   </si>
 </sst>
 </file>
@@ -2399,16 +3452,16 @@
   <dimension ref="A1:J397"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" customWidth="true"/>
-    <col min="2" max="2" width="6.54296875" customWidth="true"/>
-    <col min="3" max="3" width="10.36328125" customWidth="true"/>
-    <col min="4" max="4" width="16.36328125" customWidth="true"/>
-    <col min="5" max="5" width="11.81640625" customWidth="true"/>
-    <col min="6" max="6" width="11.90625" customWidth="true"/>
-    <col min="7" max="7" width="7.90625" customWidth="true"/>
-    <col min="8" max="8" width="36.26953125" customWidth="true"/>
-    <col min="9" max="9" width="167.54296875" customWidth="true"/>
-    <col min="10" max="10" width="10.453125" customWidth="true"/>
+    <col min="1" max="1" width="14.85546875" customWidth="true"/>
+    <col min="2" max="2" width="7" customWidth="true"/>
+    <col min="3" max="3" width="11.28515625" customWidth="true"/>
+    <col min="4" max="4" width="17.28515625" customWidth="true"/>
+    <col min="5" max="5" width="12.7109375" customWidth="true"/>
+    <col min="6" max="6" width="13" customWidth="true"/>
+    <col min="7" max="7" width="8.5703125" customWidth="true"/>
+    <col min="8" max="8" width="37.42578125" customWidth="true"/>
+    <col min="9" max="9" width="147" customWidth="true"/>
+    <col min="10" max="10" width="10.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2469,7 +3522,7 @@
         <v>46</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>212</v>
+        <v>779</v>
       </c>
       <c r="J2" s="0">
         <v>13088.609399999999</v>
@@ -2501,7 +3554,7 @@
         <v>47</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>213</v>
+        <v>780</v>
       </c>
       <c r="J3" s="0">
         <v>9104.8721000000005</v>
@@ -2533,7 +3586,7 @@
         <v>48</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>214</v>
+        <v>781</v>
       </c>
       <c r="J4" s="0">
         <v>1438.8326</v>
@@ -2565,7 +3618,7 @@
         <v>49</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>215</v>
+        <v>782</v>
       </c>
       <c r="J5" s="0">
         <v>1210.5242000000001</v>
@@ -2597,7 +3650,7 @@
         <v>50</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>216</v>
+        <v>783</v>
       </c>
       <c r="J6" s="0">
         <v>542.07240000000002</v>
@@ -2629,7 +3682,7 @@
         <v>51</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>217</v>
+        <v>784</v>
       </c>
       <c r="J7" s="0">
         <v>528.39120000000003</v>
@@ -2661,7 +3714,7 @@
         <v>52</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>218</v>
+        <v>785</v>
       </c>
       <c r="J8" s="0">
         <v>519.83349999999996</v>
@@ -2693,7 +3746,7 @@
         <v>53</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>219</v>
+        <v>786</v>
       </c>
       <c r="J9" s="0">
         <v>465.38400000000001</v>
@@ -2725,7 +3778,7 @@
         <v>54</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>220</v>
+        <v>787</v>
       </c>
       <c r="J10" s="0">
         <v>387.42579999999998</v>
@@ -2757,7 +3810,7 @@
         <v>55</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>221</v>
+        <v>788</v>
       </c>
       <c r="J11" s="0">
         <v>376.01639999999998</v>
@@ -2789,7 +3842,7 @@
         <v>56</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>222</v>
+        <v>789</v>
       </c>
       <c r="J12" s="0">
         <v>367.9187</v>
@@ -2821,7 +3874,7 @@
         <v>57</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>223</v>
+        <v>790</v>
       </c>
       <c r="J13" s="0">
         <v>345.6712</v>
@@ -2853,7 +3906,7 @@
         <v>58</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>224</v>
+        <v>791</v>
       </c>
       <c r="J14" s="0">
         <v>9741.5614999999998</v>
@@ -2885,7 +3938,7 @@
         <v>59</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>225</v>
+        <v>792</v>
       </c>
       <c r="J15" s="0">
         <v>8198.8974999999991</v>
@@ -2917,7 +3970,7 @@
         <v>60</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>226</v>
+        <v>793</v>
       </c>
       <c r="J16" s="0">
         <v>1259.1116</v>
@@ -2949,7 +4002,7 @@
         <v>61</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>227</v>
+        <v>794</v>
       </c>
       <c r="J17" s="0">
         <v>863.95190000000002</v>
@@ -2981,7 +4034,7 @@
         <v>62</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>228</v>
+        <v>795</v>
       </c>
       <c r="J18" s="0">
         <v>574.15189999999996</v>
@@ -3013,7 +4066,7 @@
         <v>63</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>229</v>
+        <v>796</v>
       </c>
       <c r="J19" s="0">
         <v>514.2156</v>
@@ -3045,7 +4098,7 @@
         <v>64</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>230</v>
+        <v>797</v>
       </c>
       <c r="J20" s="0">
         <v>497.6062</v>
@@ -3077,7 +4130,7 @@
         <v>65</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>231</v>
+        <v>798</v>
       </c>
       <c r="J21" s="0">
         <v>496.00400000000002</v>
@@ -3109,7 +4162,7 @@
         <v>66</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>232</v>
+        <v>799</v>
       </c>
       <c r="J22" s="0">
         <v>389.9522</v>
@@ -3141,7 +4194,7 @@
         <v>67</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>233</v>
+        <v>800</v>
       </c>
       <c r="J23" s="0">
         <v>332.78969999999998</v>
@@ -3173,7 +4226,7 @@
         <v>68</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>234</v>
+        <v>801</v>
       </c>
       <c r="J24" s="0">
         <v>320.5446</v>
@@ -3205,7 +4258,7 @@
         <v>69</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>235</v>
+        <v>802</v>
       </c>
       <c r="J25" s="0">
         <v>288.99189999999999</v>
@@ -3237,7 +4290,7 @@
         <v>71</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>237</v>
+        <v>803</v>
       </c>
       <c r="J26" s="0">
         <v>5932.7479999999996</v>
@@ -3269,7 +4322,7 @@
         <v>72</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>238</v>
+        <v>804</v>
       </c>
       <c r="J27" s="0">
         <v>901.9991</v>
@@ -3301,7 +4354,7 @@
         <v>73</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>239</v>
+        <v>805</v>
       </c>
       <c r="J28" s="0">
         <v>893.56960000000004</v>
@@ -3333,7 +4386,7 @@
         <v>74</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>240</v>
+        <v>806</v>
       </c>
       <c r="J29" s="0">
         <v>549.74869999999999</v>
@@ -3365,7 +4418,7 @@
         <v>75</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>241</v>
+        <v>807</v>
       </c>
       <c r="J30" s="0">
         <v>530.14729999999997</v>
@@ -3397,7 +4450,7 @@
         <v>76</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>242</v>
+        <v>808</v>
       </c>
       <c r="J31" s="0">
         <v>489.4966</v>
@@ -3429,7 +4482,7 @@
         <v>77</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>243</v>
+        <v>809</v>
       </c>
       <c r="J32" s="0">
         <v>482.49549999999999</v>
@@ -3461,7 +4514,7 @@
         <v>78</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>244</v>
+        <v>810</v>
       </c>
       <c r="J33" s="0">
         <v>378.9196</v>
@@ -3493,7 +4546,7 @@
         <v>79</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>245</v>
+        <v>811</v>
       </c>
       <c r="J34" s="0">
         <v>366.15300000000002</v>
@@ -3525,7 +4578,7 @@
         <v>80</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>246</v>
+        <v>812</v>
       </c>
       <c r="J35" s="0">
         <v>340.57749999999999</v>
@@ -3557,7 +4610,7 @@
         <v>82</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>248</v>
+        <v>813</v>
       </c>
       <c r="J36" s="0">
         <v>10466.208000000001</v>
@@ -3589,7 +4642,7 @@
         <v>83</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>249</v>
+        <v>814</v>
       </c>
       <c r="J37" s="0">
         <v>7328.0029000000004</v>
@@ -3621,7 +4674,7 @@
         <v>84</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>250</v>
+        <v>815</v>
       </c>
       <c r="J38" s="0">
         <v>1015.5606</v>
@@ -3653,7 +4706,7 @@
         <v>85</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>251</v>
+        <v>816</v>
       </c>
       <c r="J39" s="0">
         <v>908.67830000000004</v>
@@ -3685,7 +4738,7 @@
         <v>86</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>252</v>
+        <v>817</v>
       </c>
       <c r="J40" s="0">
         <v>520.97770000000003</v>
@@ -3717,7 +4770,7 @@
         <v>87</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>253</v>
+        <v>818</v>
       </c>
       <c r="J41" s="0">
         <v>488.97149999999999</v>
@@ -3749,7 +4802,7 @@
         <v>88</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>254</v>
+        <v>819</v>
       </c>
       <c r="J42" s="0">
         <v>484.75029999999998</v>
@@ -3781,7 +4834,7 @@
         <v>89</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>255</v>
+        <v>820</v>
       </c>
       <c r="J43" s="0">
         <v>438.36930000000001</v>
@@ -3813,7 +4866,7 @@
         <v>90</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>256</v>
+        <v>821</v>
       </c>
       <c r="J44" s="0">
         <v>369.10219999999998</v>
@@ -3845,7 +4898,7 @@
         <v>91</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>257</v>
+        <v>822</v>
       </c>
       <c r="J45" s="0">
         <v>342.30680000000001</v>
@@ -3877,7 +4930,7 @@
         <v>92</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>258</v>
+        <v>823</v>
       </c>
       <c r="J46" s="0">
         <v>280.75409999999999</v>
@@ -3909,7 +4962,7 @@
         <v>93</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>259</v>
+        <v>824</v>
       </c>
       <c r="J47" s="0">
         <v>270.84679999999997</v>
@@ -3941,7 +4994,7 @@
         <v>94</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>260</v>
+        <v>825</v>
       </c>
       <c r="J48" s="0">
         <v>8934.2567999999992</v>
@@ -3973,7 +5026,7 @@
         <v>95</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>261</v>
+        <v>826</v>
       </c>
       <c r="J49" s="0">
         <v>7192.2339000000002</v>
@@ -4005,7 +5058,7 @@
         <v>97</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>263</v>
+        <v>827</v>
       </c>
       <c r="J50" s="0">
         <v>892.98720000000003</v>
@@ -4037,7 +5090,7 @@
         <v>99</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>265</v>
+        <v>828</v>
       </c>
       <c r="J51" s="0">
         <v>489.01900000000001</v>
@@ -4069,7 +5122,7 @@
         <v>100</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>266</v>
+        <v>829</v>
       </c>
       <c r="J52" s="0">
         <v>486.78719999999999</v>
@@ -4101,7 +5154,7 @@
         <v>101</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>267</v>
+        <v>830</v>
       </c>
       <c r="J53" s="0">
         <v>478.59969999999999</v>
@@ -4133,7 +5186,7 @@
         <v>102</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>268</v>
+        <v>831</v>
       </c>
       <c r="J54" s="0">
         <v>456.38220000000001</v>
@@ -4165,7 +5218,7 @@
         <v>103</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>269</v>
+        <v>832</v>
       </c>
       <c r="J55" s="0">
         <v>361.197</v>
@@ -4197,7 +5250,7 @@
         <v>104</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>270</v>
+        <v>833</v>
       </c>
       <c r="J56" s="0">
         <v>350.10750000000002</v>
@@ -4229,7 +5282,7 @@
         <v>105</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>271</v>
+        <v>834</v>
       </c>
       <c r="J57" s="0">
         <v>332.8802</v>
@@ -4261,7 +5314,7 @@
         <v>106</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>272</v>
+        <v>835</v>
       </c>
       <c r="J58" s="0">
         <v>9850.5967000000001</v>
@@ -4293,7 +5346,7 @@
         <v>107</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>273</v>
+        <v>836</v>
       </c>
       <c r="J59" s="0">
         <v>8299.1229999999996</v>
@@ -4325,7 +5378,7 @@
         <v>108</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>274</v>
+        <v>837</v>
       </c>
       <c r="J60" s="0">
         <v>1061.2550000000001</v>
@@ -4357,7 +5410,7 @@
         <v>61</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>275</v>
+        <v>838</v>
       </c>
       <c r="J61" s="0">
         <v>863.95190000000002</v>
@@ -4389,7 +5442,7 @@
         <v>109</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>276</v>
+        <v>839</v>
       </c>
       <c r="J62" s="0">
         <v>537.24440000000004</v>
@@ -4421,7 +5474,7 @@
         <v>110</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>277</v>
+        <v>840</v>
       </c>
       <c r="J63" s="0">
         <v>512.39139999999998</v>
@@ -4453,7 +5506,7 @@
         <v>111</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>278</v>
+        <v>841</v>
       </c>
       <c r="J64" s="0">
         <v>461.678</v>
@@ -4485,7 +5538,7 @@
         <v>112</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>279</v>
+        <v>842</v>
       </c>
       <c r="J65" s="0">
         <v>446.13510000000002</v>
@@ -4517,7 +5570,7 @@
         <v>113</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>280</v>
+        <v>843</v>
       </c>
       <c r="J66" s="0">
         <v>416.1148</v>
@@ -4549,7 +5602,7 @@
         <v>114</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>281</v>
+        <v>844</v>
       </c>
       <c r="J67" s="0">
         <v>385.80329999999998</v>
@@ -4581,7 +5634,7 @@
         <v>115</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>282</v>
+        <v>845</v>
       </c>
       <c r="J68" s="0">
         <v>376.43869999999998</v>
@@ -4613,7 +5666,7 @@
         <v>116</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>283</v>
+        <v>846</v>
       </c>
       <c r="J69" s="0">
         <v>340.64490000000001</v>
@@ -4645,7 +5698,7 @@
         <v>117</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>284</v>
+        <v>847</v>
       </c>
       <c r="J70" s="0">
         <v>9114.7715000000008</v>
@@ -4677,7 +5730,7 @@
         <v>118</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>285</v>
+        <v>848</v>
       </c>
       <c r="J71" s="0">
         <v>7656.0316999999996</v>
@@ -4709,7 +5762,7 @@
         <v>121</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>288</v>
+        <v>849</v>
       </c>
       <c r="J72" s="0">
         <v>542.5788</v>
@@ -4741,7 +5794,7 @@
         <v>122</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>289</v>
+        <v>850</v>
       </c>
       <c r="J73" s="0">
         <v>534.76580000000001</v>
@@ -4773,7 +5826,7 @@
         <v>123</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>290</v>
+        <v>851</v>
       </c>
       <c r="J74" s="0">
         <v>484.83710000000002</v>
@@ -4805,7 +5858,7 @@
         <v>124</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>291</v>
+        <v>852</v>
       </c>
       <c r="J75" s="0">
         <v>468.87529999999998</v>
@@ -4837,7 +5890,7 @@
         <v>125</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>292</v>
+        <v>853</v>
       </c>
       <c r="J76" s="0">
         <v>398.83769999999998</v>
@@ -4869,7 +5922,7 @@
         <v>126</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>293</v>
+        <v>854</v>
       </c>
       <c r="J77" s="0">
         <v>337.36939999999999</v>
@@ -4901,7 +5954,7 @@
         <v>127</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>294</v>
+        <v>855</v>
       </c>
       <c r="J78" s="0">
         <v>311.84429999999998</v>
@@ -4933,7 +5986,7 @@
         <v>128</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>295</v>
+        <v>856</v>
       </c>
       <c r="J79" s="0">
         <v>245.285</v>
@@ -4965,7 +6018,7 @@
         <v>507</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>679</v>
+        <v>857</v>
       </c>
       <c r="J80" s="0">
         <v>10897.75</v>
@@ -4997,7 +6050,7 @@
         <v>508</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>680</v>
+        <v>858</v>
       </c>
       <c r="J81" s="0">
         <v>5963.8306000000002</v>
@@ -5029,7 +6082,7 @@
         <v>509</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>681</v>
+        <v>859</v>
       </c>
       <c r="J82" s="0">
         <v>1364.115</v>
@@ -5061,7 +6114,7 @@
         <v>510</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>682</v>
+        <v>860</v>
       </c>
       <c r="J83" s="0">
         <v>1002.6719000000001</v>
@@ -5093,7 +6146,7 @@
         <v>511</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>683</v>
+        <v>861</v>
       </c>
       <c r="J84" s="0">
         <v>557.97879999999998</v>
@@ -5125,7 +6178,7 @@
         <v>512</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>684</v>
+        <v>862</v>
       </c>
       <c r="J85" s="0">
         <v>511.4341</v>
@@ -5157,7 +6210,7 @@
         <v>513</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>685</v>
+        <v>863</v>
       </c>
       <c r="J86" s="0">
         <v>485.53699999999998</v>
@@ -5189,7 +6242,7 @@
         <v>514</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>686</v>
+        <v>864</v>
       </c>
       <c r="J87" s="0">
         <v>456.29579999999999</v>
@@ -5221,7 +6274,7 @@
         <v>515</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>687</v>
+        <v>865</v>
       </c>
       <c r="J88" s="0">
         <v>403.62130000000002</v>
@@ -5253,7 +6306,7 @@
         <v>516</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>688</v>
+        <v>866</v>
       </c>
       <c r="J89" s="0">
         <v>384.92849999999999</v>
@@ -5285,7 +6338,7 @@
         <v>517</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>689</v>
+        <v>867</v>
       </c>
       <c r="J90" s="0">
         <v>345.9332</v>
@@ -5317,7 +6370,7 @@
         <v>518</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>690</v>
+        <v>868</v>
       </c>
       <c r="J91" s="0">
         <v>329.33870000000002</v>
@@ -5349,7 +6402,7 @@
         <v>519</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>691</v>
+        <v>869</v>
       </c>
       <c r="J92" s="0">
         <v>9494.3554999999997</v>
@@ -5381,7 +6434,7 @@
         <v>520</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>692</v>
+        <v>870</v>
       </c>
       <c r="J93" s="0">
         <v>6959.3242</v>
@@ -5413,7 +6466,7 @@
         <v>523</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>695</v>
+        <v>871</v>
       </c>
       <c r="J94" s="0">
         <v>528.32619999999997</v>
@@ -5445,7 +6498,7 @@
         <v>524</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>696</v>
+        <v>872</v>
       </c>
       <c r="J95" s="0">
         <v>502.16129999999998</v>
@@ -5477,7 +6530,7 @@
         <v>525</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>697</v>
+        <v>873</v>
       </c>
       <c r="J96" s="0">
         <v>468.14839999999998</v>
@@ -5509,7 +6562,7 @@
         <v>526</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>698</v>
+        <v>874</v>
       </c>
       <c r="J97" s="0">
         <v>413.35890000000001</v>
@@ -5541,7 +6594,7 @@
         <v>527</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>699</v>
+        <v>875</v>
       </c>
       <c r="J98" s="0">
         <v>410.47199999999998</v>
@@ -5573,7 +6626,7 @@
         <v>528</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>700</v>
+        <v>876</v>
       </c>
       <c r="J99" s="0">
         <v>371.8809</v>
@@ -5605,7 +6658,7 @@
         <v>529</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>701</v>
+        <v>877</v>
       </c>
       <c r="J100" s="0">
         <v>347.0478</v>
@@ -5637,7 +6690,7 @@
         <v>530</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>702</v>
+        <v>878</v>
       </c>
       <c r="J101" s="0">
         <v>302.97559999999999</v>
@@ -5669,7 +6722,7 @@
         <v>531</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>703</v>
+        <v>879</v>
       </c>
       <c r="J102" s="0">
         <v>8923.2001999999993</v>
@@ -5701,7 +6754,7 @@
         <v>532</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>704</v>
+        <v>880</v>
       </c>
       <c r="J103" s="0">
         <v>7434.9364999999998</v>
@@ -5733,7 +6786,7 @@
         <v>533</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>705</v>
+        <v>881</v>
       </c>
       <c r="J104" s="0">
         <v>1198.5989</v>
@@ -5765,7 +6818,7 @@
         <v>534</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>706</v>
+        <v>882</v>
       </c>
       <c r="J105" s="0">
         <v>1016.6576</v>
@@ -5797,7 +6850,7 @@
         <v>543</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>715</v>
+        <v>883</v>
       </c>
       <c r="J106" s="0">
         <v>10363.415999999999</v>
@@ -5829,7 +6882,7 @@
         <v>544</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>716</v>
+        <v>884</v>
       </c>
       <c r="J107" s="0">
         <v>8731.0702999999994</v>
@@ -5861,7 +6914,7 @@
         <v>547</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>719</v>
+        <v>885</v>
       </c>
       <c r="J108" s="0">
         <v>509.65910000000002</v>
@@ -5893,7 +6946,7 @@
         <v>548</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>720</v>
+        <v>886</v>
       </c>
       <c r="J109" s="0">
         <v>473.81920000000002</v>
@@ -5925,7 +6978,7 @@
         <v>549</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>721</v>
+        <v>887</v>
       </c>
       <c r="J110" s="0">
         <v>386.12639999999999</v>
@@ -5957,7 +7010,7 @@
         <v>550</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>722</v>
+        <v>888</v>
       </c>
       <c r="J111" s="0">
         <v>381.40570000000002</v>
@@ -5989,7 +7042,7 @@
         <v>551</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>723</v>
+        <v>889</v>
       </c>
       <c r="J112" s="0">
         <v>371.59660000000002</v>
@@ -6021,7 +7074,7 @@
         <v>552</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>724</v>
+        <v>890</v>
       </c>
       <c r="J113" s="0">
         <v>364.02569999999997</v>
@@ -6053,7 +7106,7 @@
         <v>146</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>725</v>
+        <v>891</v>
       </c>
       <c r="J114" s="0">
         <v>342.74220000000003</v>
@@ -6085,7 +7138,7 @@
         <v>553</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>726</v>
+        <v>892</v>
       </c>
       <c r="J115" s="0">
         <v>331.7552</v>
@@ -6117,7 +7170,7 @@
         <v>129</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>296</v>
+        <v>893</v>
       </c>
       <c r="J116" s="0">
         <v>8389.2909999999993</v>
@@ -6149,7 +7202,7 @@
         <v>130</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>297</v>
+        <v>894</v>
       </c>
       <c r="J117" s="0">
         <v>8068.0429999999997</v>
@@ -6181,7 +7234,7 @@
         <v>133</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>300</v>
+        <v>895</v>
       </c>
       <c r="J118" s="0">
         <v>528.16520000000003</v>
@@ -6213,7 +7266,7 @@
         <v>134</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>301</v>
+        <v>896</v>
       </c>
       <c r="J119" s="0">
         <v>464.43889999999999</v>
@@ -6245,7 +7298,7 @@
         <v>135</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>302</v>
+        <v>897</v>
       </c>
       <c r="J120" s="0">
         <v>449.87619999999998</v>
@@ -6277,7 +7330,7 @@
         <v>136</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>303</v>
+        <v>898</v>
       </c>
       <c r="J121" s="0">
         <v>447.66699999999997</v>
@@ -6309,7 +7362,7 @@
         <v>137</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>304</v>
+        <v>899</v>
       </c>
       <c r="J122" s="0">
         <v>391.69869999999997</v>
@@ -6341,7 +7394,7 @@
         <v>138</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>305</v>
+        <v>900</v>
       </c>
       <c r="J123" s="0">
         <v>372.4153</v>
@@ -6373,7 +7426,7 @@
         <v>139</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>306</v>
+        <v>901</v>
       </c>
       <c r="J124" s="0">
         <v>366.97289999999998</v>
@@ -6405,7 +7458,7 @@
         <v>140</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>307</v>
+        <v>902</v>
       </c>
       <c r="J125" s="0">
         <v>329.11259999999999</v>
@@ -6437,7 +7490,7 @@
         <v>58</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>308</v>
+        <v>903</v>
       </c>
       <c r="J126" s="0">
         <v>9741.5614999999998</v>
@@ -6469,7 +7522,7 @@
         <v>59</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>309</v>
+        <v>904</v>
       </c>
       <c r="J127" s="0">
         <v>8198.8974999999991</v>
@@ -6501,7 +7554,7 @@
         <v>60</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>310</v>
+        <v>905</v>
       </c>
       <c r="J128" s="0">
         <v>1259.1116</v>
@@ -6533,7 +7586,7 @@
         <v>61</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>311</v>
+        <v>906</v>
       </c>
       <c r="J129" s="0">
         <v>863.95190000000002</v>
@@ -6565,7 +7618,7 @@
         <v>141</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>312</v>
+        <v>907</v>
       </c>
       <c r="J130" s="0">
         <v>539.45429999999999</v>
@@ -6597,7 +7650,7 @@
         <v>142</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>313</v>
+        <v>908</v>
       </c>
       <c r="J131" s="0">
         <v>485.64830000000001</v>
@@ -6629,7 +7682,7 @@
         <v>143</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>314</v>
+        <v>909</v>
       </c>
       <c r="J132" s="0">
         <v>457.39609999999999</v>
@@ -6661,7 +7714,7 @@
         <v>144</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>315</v>
+        <v>910</v>
       </c>
       <c r="J133" s="0">
         <v>454.66460000000001</v>
@@ -6693,7 +7746,7 @@
         <v>145</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>316</v>
+        <v>911</v>
       </c>
       <c r="J134" s="0">
         <v>368.51979999999998</v>
@@ -6725,7 +7778,7 @@
         <v>146</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>317</v>
+        <v>912</v>
       </c>
       <c r="J135" s="0">
         <v>342.74220000000003</v>
@@ -6757,7 +7810,7 @@
         <v>147</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>318</v>
+        <v>913</v>
       </c>
       <c r="J136" s="0">
         <v>302.46800000000002</v>
@@ -6789,7 +7842,7 @@
         <v>148</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>319</v>
+        <v>914</v>
       </c>
       <c r="J137" s="0">
         <v>300.47250000000003</v>
@@ -6821,7 +7874,7 @@
         <v>149</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>320</v>
+        <v>915</v>
       </c>
       <c r="J138" s="0">
         <v>10892.9414</v>
@@ -6853,7 +7906,7 @@
         <v>150</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>321</v>
+        <v>916</v>
       </c>
       <c r="J139" s="0">
         <v>5918.6806999999999</v>
@@ -6885,7 +7938,7 @@
         <v>151</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>322</v>
+        <v>917</v>
       </c>
       <c r="J140" s="0">
         <v>829.46619999999996</v>
@@ -6917,7 +7970,7 @@
         <v>152</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>323</v>
+        <v>918</v>
       </c>
       <c r="J141" s="0">
         <v>726.14110000000005</v>
@@ -6949,7 +8002,7 @@
         <v>153</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>324</v>
+        <v>919</v>
       </c>
       <c r="J142" s="0">
         <v>498.3132</v>
@@ -6981,7 +8034,7 @@
         <v>154</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>325</v>
+        <v>920</v>
       </c>
       <c r="J143" s="0">
         <v>487.10520000000002</v>
@@ -7013,7 +8066,7 @@
         <v>155</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>326</v>
+        <v>921</v>
       </c>
       <c r="J144" s="0">
         <v>485.66770000000002</v>
@@ -7045,7 +8098,7 @@
         <v>156</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>327</v>
+        <v>922</v>
       </c>
       <c r="J145" s="0">
         <v>478.11529999999999</v>
@@ -7077,7 +8130,7 @@
         <v>157</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>328</v>
+        <v>923</v>
       </c>
       <c r="J146" s="0">
         <v>375.48970000000003</v>
@@ -7109,7 +8162,7 @@
         <v>158</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>329</v>
+        <v>924</v>
       </c>
       <c r="J147" s="0">
         <v>359.0838</v>
@@ -7141,7 +8194,7 @@
         <v>159</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>330</v>
+        <v>925</v>
       </c>
       <c r="J148" s="0">
         <v>338.9837</v>
@@ -7173,7 +8226,7 @@
         <v>160</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>331</v>
+        <v>926</v>
       </c>
       <c r="J149" s="0">
         <v>293.55579999999998</v>
@@ -7205,7 +8258,7 @@
         <v>161</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>332</v>
+        <v>927</v>
       </c>
       <c r="J150" s="0">
         <v>9826.1103999999996</v>
@@ -7237,7 +8290,7 @@
         <v>162</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>333</v>
+        <v>928</v>
       </c>
       <c r="J151" s="0">
         <v>7957.9004000000004</v>
@@ -7269,7 +8322,7 @@
         <v>163</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>334</v>
+        <v>929</v>
       </c>
       <c r="J152" s="0">
         <v>1958.7829999999999</v>
@@ -7301,7 +8354,7 @@
         <v>165</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>336</v>
+        <v>930</v>
       </c>
       <c r="J153" s="0">
         <v>574.80640000000005</v>
@@ -7333,7 +8386,7 @@
         <v>166</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>337</v>
+        <v>931</v>
       </c>
       <c r="J154" s="0">
         <v>532.89999999999998</v>
@@ -7365,7 +8418,7 @@
         <v>167</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>338</v>
+        <v>932</v>
       </c>
       <c r="J155" s="0">
         <v>470.99040000000002</v>
@@ -7397,7 +8450,7 @@
         <v>168</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>339</v>
+        <v>933</v>
       </c>
       <c r="J156" s="0">
         <v>428.05349999999999</v>
@@ -7429,7 +8482,7 @@
         <v>169</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>340</v>
+        <v>934</v>
       </c>
       <c r="J157" s="0">
         <v>370.83409999999998</v>
@@ -7461,7 +8514,7 @@
         <v>170</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>341</v>
+        <v>935</v>
       </c>
       <c r="J158" s="0">
         <v>361.65289999999999</v>
@@ -7493,7 +8546,7 @@
         <v>171</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>342</v>
+        <v>936</v>
       </c>
       <c r="J159" s="0">
         <v>328.18830000000003</v>
@@ -7525,7 +8578,7 @@
         <v>172</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>343</v>
+        <v>937</v>
       </c>
       <c r="J160" s="0">
         <v>313.28399999999999</v>
@@ -7557,7 +8610,7 @@
         <v>47</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>345</v>
+        <v>938</v>
       </c>
       <c r="J161" s="0">
         <v>9104.8721000000005</v>
@@ -7589,7 +8642,7 @@
         <v>48</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>346</v>
+        <v>939</v>
       </c>
       <c r="J162" s="0">
         <v>1438.8326</v>
@@ -7621,7 +8674,7 @@
         <v>49</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>347</v>
+        <v>940</v>
       </c>
       <c r="J163" s="0">
         <v>1210.5242000000001</v>
@@ -7653,7 +8706,7 @@
         <v>50</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>348</v>
+        <v>941</v>
       </c>
       <c r="J164" s="0">
         <v>542.07240000000002</v>
@@ -7685,7 +8738,7 @@
         <v>51</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>349</v>
+        <v>942</v>
       </c>
       <c r="J165" s="0">
         <v>528.39120000000003</v>
@@ -7717,7 +8770,7 @@
         <v>52</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>350</v>
+        <v>943</v>
       </c>
       <c r="J166" s="0">
         <v>519.83349999999996</v>
@@ -7749,7 +8802,7 @@
         <v>53</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>351</v>
+        <v>944</v>
       </c>
       <c r="J167" s="0">
         <v>465.38400000000001</v>
@@ -7781,7 +8834,7 @@
         <v>54</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>352</v>
+        <v>945</v>
       </c>
       <c r="J168" s="0">
         <v>387.42579999999998</v>
@@ -7813,7 +8866,7 @@
         <v>55</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>353</v>
+        <v>946</v>
       </c>
       <c r="J169" s="0">
         <v>376.01639999999998</v>
@@ -7845,7 +8898,7 @@
         <v>56</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>354</v>
+        <v>947</v>
       </c>
       <c r="J170" s="0">
         <v>367.9187</v>
@@ -7877,7 +8930,7 @@
         <v>57</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>355</v>
+        <v>948</v>
       </c>
       <c r="J171" s="0">
         <v>345.6712</v>
@@ -7909,7 +8962,7 @@
         <v>173</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>356</v>
+        <v>949</v>
       </c>
       <c r="J172" s="0">
         <v>11026.299800000001</v>
@@ -7941,7 +8994,7 @@
         <v>174</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>357</v>
+        <v>950</v>
       </c>
       <c r="J173" s="0">
         <v>8759.9452999999994</v>
@@ -7973,7 +9026,7 @@
         <v>175</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>358</v>
+        <v>951</v>
       </c>
       <c r="J174" s="0">
         <v>1159.0046</v>
@@ -8005,7 +9058,7 @@
         <v>176</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>359</v>
+        <v>952</v>
       </c>
       <c r="J175" s="0">
         <v>1153.3887</v>
@@ -8037,7 +9090,7 @@
         <v>177</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>360</v>
+        <v>953</v>
       </c>
       <c r="J176" s="0">
         <v>531.56039999999996</v>
@@ -8069,7 +9122,7 @@
         <v>178</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>361</v>
+        <v>954</v>
       </c>
       <c r="J177" s="0">
         <v>513.93790000000001</v>
@@ -8101,7 +9154,7 @@
         <v>179</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>362</v>
+        <v>955</v>
       </c>
       <c r="J178" s="0">
         <v>499.63580000000002</v>
@@ -8133,7 +9186,7 @@
         <v>180</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>363</v>
+        <v>956</v>
       </c>
       <c r="J179" s="0">
         <v>475.38760000000002</v>
@@ -8165,7 +9218,7 @@
         <v>181</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>364</v>
+        <v>957</v>
       </c>
       <c r="J180" s="0">
         <v>357.59019999999998</v>
@@ -8197,7 +9250,7 @@
         <v>182</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>365</v>
+        <v>958</v>
       </c>
       <c r="J181" s="0">
         <v>346.22629999999998</v>
@@ -8229,7 +9282,7 @@
         <v>183</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>366</v>
+        <v>959</v>
       </c>
       <c r="J182" s="0">
         <v>331.46199999999999</v>
@@ -8261,7 +9314,7 @@
         <v>184</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>367</v>
+        <v>960</v>
       </c>
       <c r="J183" s="0">
         <v>308.1046</v>
@@ -8293,7 +9346,7 @@
         <v>72</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>370</v>
+        <v>961</v>
       </c>
       <c r="J184" s="0">
         <v>901.9991</v>
@@ -8325,7 +9378,7 @@
         <v>73</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>371</v>
+        <v>962</v>
       </c>
       <c r="J185" s="0">
         <v>893.56960000000004</v>
@@ -8357,7 +9410,7 @@
         <v>74</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>372</v>
+        <v>963</v>
       </c>
       <c r="J186" s="0">
         <v>549.74869999999999</v>
@@ -8389,7 +9442,7 @@
         <v>75</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>373</v>
+        <v>964</v>
       </c>
       <c r="J187" s="0">
         <v>530.14729999999997</v>
@@ -8421,7 +9474,7 @@
         <v>76</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>374</v>
+        <v>965</v>
       </c>
       <c r="J188" s="0">
         <v>489.4966</v>
@@ -8453,7 +9506,7 @@
         <v>77</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>375</v>
+        <v>966</v>
       </c>
       <c r="J189" s="0">
         <v>482.49549999999999</v>
@@ -8485,7 +9538,7 @@
         <v>78</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>376</v>
+        <v>967</v>
       </c>
       <c r="J190" s="0">
         <v>378.9196</v>
@@ -8517,7 +9570,7 @@
         <v>79</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>377</v>
+        <v>968</v>
       </c>
       <c r="J191" s="0">
         <v>366.15300000000002</v>
@@ -8549,7 +9602,7 @@
         <v>80</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>378</v>
+        <v>969</v>
       </c>
       <c r="J192" s="0">
         <v>340.57749999999999</v>
@@ -8581,7 +9634,7 @@
         <v>185</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>380</v>
+        <v>970</v>
       </c>
       <c r="J193" s="0">
         <v>4307.7025999999996</v>
@@ -8613,7 +9666,7 @@
         <v>186</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>381</v>
+        <v>971</v>
       </c>
       <c r="J194" s="0">
         <v>1837.0477000000001</v>
@@ -8645,7 +9698,7 @@
         <v>187</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>382</v>
+        <v>972</v>
       </c>
       <c r="J195" s="0">
         <v>616.08360000000005</v>
@@ -8677,7 +9730,7 @@
         <v>188</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>383</v>
+        <v>973</v>
       </c>
       <c r="J196" s="0">
         <v>552.42719999999997</v>
@@ -8709,7 +9762,7 @@
         <v>189</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>384</v>
+        <v>974</v>
       </c>
       <c r="J197" s="0">
         <v>399.44740000000002</v>
@@ -8741,7 +9794,7 @@
         <v>190</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>385</v>
+        <v>975</v>
       </c>
       <c r="J198" s="0">
         <v>377.98289999999997</v>
@@ -8773,7 +9826,7 @@
         <v>191</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>386</v>
+        <v>976</v>
       </c>
       <c r="J199" s="0">
         <v>376.71690000000001</v>
@@ -8805,7 +9858,7 @@
         <v>192</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>387</v>
+        <v>977</v>
       </c>
       <c r="J200" s="0">
         <v>375.52019999999999</v>
@@ -8837,7 +9890,7 @@
         <v>193</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>388</v>
+        <v>978</v>
       </c>
       <c r="J201" s="0">
         <v>370.8648</v>
@@ -8869,7 +9922,7 @@
         <v>194</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>389</v>
+        <v>979</v>
       </c>
       <c r="J202" s="0">
         <v>342.89479999999998</v>
@@ -8901,7 +9954,7 @@
         <v>195</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>390</v>
+        <v>980</v>
       </c>
       <c r="J203" s="0">
         <v>307.26029999999997</v>
@@ -8933,7 +9986,7 @@
         <v>196</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>391</v>
+        <v>981</v>
       </c>
       <c r="J204" s="0">
         <v>261.58179999999999</v>
@@ -8965,7 +10018,7 @@
         <v>82</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>392</v>
+        <v>982</v>
       </c>
       <c r="J205" s="0">
         <v>10466.208000000001</v>
@@ -8997,7 +10050,7 @@
         <v>83</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>393</v>
+        <v>983</v>
       </c>
       <c r="J206" s="0">
         <v>7328.0029000000004</v>
@@ -9029,7 +10082,7 @@
         <v>84</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>394</v>
+        <v>984</v>
       </c>
       <c r="J207" s="0">
         <v>1015.5606</v>
@@ -9061,7 +10114,7 @@
         <v>85</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>395</v>
+        <v>985</v>
       </c>
       <c r="J208" s="0">
         <v>908.67830000000004</v>
@@ -9093,7 +10146,7 @@
         <v>86</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>396</v>
+        <v>986</v>
       </c>
       <c r="J209" s="0">
         <v>520.97770000000003</v>
@@ -9125,7 +10178,7 @@
         <v>87</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>397</v>
+        <v>987</v>
       </c>
       <c r="J210" s="0">
         <v>488.97149999999999</v>
@@ -9157,7 +10210,7 @@
         <v>88</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>398</v>
+        <v>988</v>
       </c>
       <c r="J211" s="0">
         <v>484.75029999999998</v>
@@ -9189,7 +10242,7 @@
         <v>89</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>399</v>
+        <v>989</v>
       </c>
       <c r="J212" s="0">
         <v>438.36930000000001</v>
@@ -9221,7 +10274,7 @@
         <v>90</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>400</v>
+        <v>990</v>
       </c>
       <c r="J213" s="0">
         <v>369.10219999999998</v>
@@ -9253,7 +10306,7 @@
         <v>91</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>401</v>
+        <v>991</v>
       </c>
       <c r="J214" s="0">
         <v>342.30680000000001</v>
@@ -9285,7 +10338,7 @@
         <v>92</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>402</v>
+        <v>992</v>
       </c>
       <c r="J215" s="0">
         <v>280.75409999999999</v>
@@ -9317,7 +10370,7 @@
         <v>93</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>403</v>
+        <v>993</v>
       </c>
       <c r="J216" s="0">
         <v>270.84679999999997</v>
@@ -9349,7 +10402,7 @@
         <v>94</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>404</v>
+        <v>994</v>
       </c>
       <c r="J217" s="0">
         <v>8934.2567999999992</v>
@@ -9381,7 +10434,7 @@
         <v>95</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>405</v>
+        <v>995</v>
       </c>
       <c r="J218" s="0">
         <v>7192.2339000000002</v>
@@ -9413,7 +10466,7 @@
         <v>99</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>409</v>
+        <v>996</v>
       </c>
       <c r="J219" s="0">
         <v>489.01900000000001</v>
@@ -9445,7 +10498,7 @@
         <v>100</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>410</v>
+        <v>997</v>
       </c>
       <c r="J220" s="0">
         <v>486.78719999999999</v>
@@ -9477,7 +10530,7 @@
         <v>101</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>411</v>
+        <v>998</v>
       </c>
       <c r="J221" s="0">
         <v>478.59969999999999</v>
@@ -9509,7 +10562,7 @@
         <v>102</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>412</v>
+        <v>999</v>
       </c>
       <c r="J222" s="0">
         <v>456.38220000000001</v>
@@ -9541,7 +10594,7 @@
         <v>103</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>413</v>
+        <v>1000</v>
       </c>
       <c r="J223" s="0">
         <v>361.197</v>
@@ -9573,7 +10626,7 @@
         <v>104</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>414</v>
+        <v>1001</v>
       </c>
       <c r="J224" s="0">
         <v>350.10750000000002</v>
@@ -9605,7 +10658,7 @@
         <v>105</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>415</v>
+        <v>1002</v>
       </c>
       <c r="J225" s="0">
         <v>332.8802</v>
@@ -9637,7 +10690,7 @@
         <v>106</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>416</v>
+        <v>1003</v>
       </c>
       <c r="J226" s="0">
         <v>9850.5967000000001</v>
@@ -9669,7 +10722,7 @@
         <v>107</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>417</v>
+        <v>1004</v>
       </c>
       <c r="J227" s="0">
         <v>8299.1229999999996</v>
@@ -9701,7 +10754,7 @@
         <v>108</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>418</v>
+        <v>1005</v>
       </c>
       <c r="J228" s="0">
         <v>1061.2550000000001</v>
@@ -9733,7 +10786,7 @@
         <v>61</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>419</v>
+        <v>1006</v>
       </c>
       <c r="J229" s="0">
         <v>863.95190000000002</v>
@@ -9765,7 +10818,7 @@
         <v>109</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>420</v>
+        <v>1007</v>
       </c>
       <c r="J230" s="0">
         <v>537.24440000000004</v>
@@ -9797,7 +10850,7 @@
         <v>110</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>421</v>
+        <v>1008</v>
       </c>
       <c r="J231" s="0">
         <v>512.39139999999998</v>
@@ -9829,7 +10882,7 @@
         <v>111</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>422</v>
+        <v>1009</v>
       </c>
       <c r="J232" s="0">
         <v>461.678</v>
@@ -9861,7 +10914,7 @@
         <v>112</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>423</v>
+        <v>1010</v>
       </c>
       <c r="J233" s="0">
         <v>446.13510000000002</v>
@@ -9893,7 +10946,7 @@
         <v>113</v>
       </c>
       <c r="I234" s="0" t="s">
-        <v>424</v>
+        <v>1011</v>
       </c>
       <c r="J234" s="0">
         <v>416.1148</v>
@@ -9925,7 +10978,7 @@
         <v>114</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>425</v>
+        <v>1012</v>
       </c>
       <c r="J235" s="0">
         <v>385.80329999999998</v>
@@ -9957,7 +11010,7 @@
         <v>115</v>
       </c>
       <c r="I236" s="0" t="s">
-        <v>426</v>
+        <v>1013</v>
       </c>
       <c r="J236" s="0">
         <v>376.43869999999998</v>
@@ -9989,7 +11042,7 @@
         <v>116</v>
       </c>
       <c r="I237" s="0" t="s">
-        <v>427</v>
+        <v>1014</v>
       </c>
       <c r="J237" s="0">
         <v>340.64490000000001</v>
@@ -10021,7 +11074,7 @@
         <v>117</v>
       </c>
       <c r="I238" s="0" t="s">
-        <v>428</v>
+        <v>1015</v>
       </c>
       <c r="J238" s="0">
         <v>9114.7715000000008</v>
@@ -10053,7 +11106,7 @@
         <v>118</v>
       </c>
       <c r="I239" s="0" t="s">
-        <v>429</v>
+        <v>1016</v>
       </c>
       <c r="J239" s="0">
         <v>7656.0316999999996</v>
@@ -10085,7 +11138,7 @@
         <v>121</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>432</v>
+        <v>1017</v>
       </c>
       <c r="J240" s="0">
         <v>542.5788</v>
@@ -10117,7 +11170,7 @@
         <v>122</v>
       </c>
       <c r="I241" s="0" t="s">
-        <v>433</v>
+        <v>1018</v>
       </c>
       <c r="J241" s="0">
         <v>534.76580000000001</v>
@@ -10149,7 +11202,7 @@
         <v>123</v>
       </c>
       <c r="I242" s="0" t="s">
-        <v>434</v>
+        <v>1019</v>
       </c>
       <c r="J242" s="0">
         <v>484.83710000000002</v>
@@ -10181,7 +11234,7 @@
         <v>124</v>
       </c>
       <c r="I243" s="0" t="s">
-        <v>435</v>
+        <v>1020</v>
       </c>
       <c r="J243" s="0">
         <v>468.87529999999998</v>
@@ -10213,7 +11266,7 @@
         <v>125</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>436</v>
+        <v>1021</v>
       </c>
       <c r="J244" s="0">
         <v>398.83769999999998</v>
@@ -10245,7 +11298,7 @@
         <v>126</v>
       </c>
       <c r="I245" s="0" t="s">
-        <v>437</v>
+        <v>1022</v>
       </c>
       <c r="J245" s="0">
         <v>337.36939999999999</v>
@@ -10277,7 +11330,7 @@
         <v>127</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>438</v>
+        <v>1023</v>
       </c>
       <c r="J246" s="0">
         <v>311.84429999999998</v>
@@ -10309,7 +11362,7 @@
         <v>128</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>439</v>
+        <v>1024</v>
       </c>
       <c r="J247" s="0">
         <v>245.285</v>
@@ -10341,7 +11394,7 @@
         <v>197</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>440</v>
+        <v>1025</v>
       </c>
       <c r="J248" s="0">
         <v>2887.6174000000001</v>
@@ -10373,7 +11426,7 @@
         <v>198</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>441</v>
+        <v>1026</v>
       </c>
       <c r="J249" s="0">
         <v>2872.1073999999999</v>
@@ -10405,7 +11458,7 @@
         <v>199</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>442</v>
+        <v>1027</v>
       </c>
       <c r="J250" s="0">
         <v>975.3777</v>
@@ -10437,7 +11490,7 @@
         <v>187</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>443</v>
+        <v>1028</v>
       </c>
       <c r="J251" s="0">
         <v>616.08360000000005</v>
@@ -10469,7 +11522,7 @@
         <v>200</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>444</v>
+        <v>1029</v>
       </c>
       <c r="J252" s="0">
         <v>465.53719999999999</v>
@@ -10501,7 +11554,7 @@
         <v>201</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>445</v>
+        <v>1030</v>
       </c>
       <c r="J253" s="0">
         <v>436.18400000000003</v>
@@ -10533,7 +11586,7 @@
         <v>202</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>446</v>
+        <v>1031</v>
       </c>
       <c r="J254" s="0">
         <v>415.78980000000001</v>
@@ -10565,7 +11618,7 @@
         <v>203</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>447</v>
+        <v>1032</v>
       </c>
       <c r="J255" s="0">
         <v>391.16430000000003</v>
@@ -10597,7 +11650,7 @@
         <v>204</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>448</v>
+        <v>1033</v>
       </c>
       <c r="J256" s="0">
         <v>362.91770000000002</v>
@@ -10629,7 +11682,7 @@
         <v>205</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>449</v>
+        <v>1034</v>
       </c>
       <c r="J257" s="0">
         <v>315.58260000000001</v>
@@ -10661,7 +11714,7 @@
         <v>206</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>450</v>
+        <v>1035</v>
       </c>
       <c r="J258" s="0">
         <v>315.33229999999998</v>
@@ -10693,7 +11746,7 @@
         <v>207</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>451</v>
+        <v>1036</v>
       </c>
       <c r="J259" s="0">
         <v>254.02879999999999</v>
@@ -10725,7 +11778,7 @@
         <v>507</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>727</v>
+        <v>1037</v>
       </c>
       <c r="J260" s="0">
         <v>10897.75</v>
@@ -10757,7 +11810,7 @@
         <v>508</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>728</v>
+        <v>1038</v>
       </c>
       <c r="J261" s="0">
         <v>5963.8306000000002</v>
@@ -10789,7 +11842,7 @@
         <v>509</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>729</v>
+        <v>1039</v>
       </c>
       <c r="J262" s="0">
         <v>1364.115</v>
@@ -10821,7 +11874,7 @@
         <v>510</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>730</v>
+        <v>1040</v>
       </c>
       <c r="J263" s="0">
         <v>1002.6719000000001</v>
@@ -10853,7 +11906,7 @@
         <v>511</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>731</v>
+        <v>1041</v>
       </c>
       <c r="J264" s="0">
         <v>557.97879999999998</v>
@@ -10885,7 +11938,7 @@
         <v>512</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>732</v>
+        <v>1042</v>
       </c>
       <c r="J265" s="0">
         <v>511.4341</v>
@@ -10917,7 +11970,7 @@
         <v>513</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>733</v>
+        <v>1043</v>
       </c>
       <c r="J266" s="0">
         <v>485.53699999999998</v>
@@ -10949,7 +12002,7 @@
         <v>514</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>734</v>
+        <v>1044</v>
       </c>
       <c r="J267" s="0">
         <v>456.29579999999999</v>
@@ -10981,7 +12034,7 @@
         <v>515</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>735</v>
+        <v>1045</v>
       </c>
       <c r="J268" s="0">
         <v>403.62130000000002</v>
@@ -11013,7 +12066,7 @@
         <v>516</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>736</v>
+        <v>1046</v>
       </c>
       <c r="J269" s="0">
         <v>384.92849999999999</v>
@@ -11045,7 +12098,7 @@
         <v>517</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>737</v>
+        <v>1047</v>
       </c>
       <c r="J270" s="0">
         <v>345.9332</v>
@@ -11077,7 +12130,7 @@
         <v>518</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>738</v>
+        <v>1048</v>
       </c>
       <c r="J271" s="0">
         <v>329.33870000000002</v>
@@ -11109,7 +12162,7 @@
         <v>519</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>739</v>
+        <v>1049</v>
       </c>
       <c r="J272" s="0">
         <v>9494.3554999999997</v>
@@ -11141,7 +12194,7 @@
         <v>520</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>740</v>
+        <v>1050</v>
       </c>
       <c r="J273" s="0">
         <v>6959.3242</v>
@@ -11173,7 +12226,7 @@
         <v>523</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>743</v>
+        <v>1051</v>
       </c>
       <c r="J274" s="0">
         <v>528.32619999999997</v>
@@ -11205,7 +12258,7 @@
         <v>524</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>744</v>
+        <v>1052</v>
       </c>
       <c r="J275" s="0">
         <v>502.16129999999998</v>
@@ -11237,7 +12290,7 @@
         <v>525</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>745</v>
+        <v>1053</v>
       </c>
       <c r="J276" s="0">
         <v>468.14839999999998</v>
@@ -11269,7 +12322,7 @@
         <v>526</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>746</v>
+        <v>1054</v>
       </c>
       <c r="J277" s="0">
         <v>413.35890000000001</v>
@@ -11301,7 +12354,7 @@
         <v>527</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>747</v>
+        <v>1055</v>
       </c>
       <c r="J278" s="0">
         <v>410.47199999999998</v>
@@ -11333,7 +12386,7 @@
         <v>528</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>748</v>
+        <v>1056</v>
       </c>
       <c r="J279" s="0">
         <v>371.8809</v>
@@ -11365,7 +12418,7 @@
         <v>529</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>749</v>
+        <v>1057</v>
       </c>
       <c r="J280" s="0">
         <v>347.0478</v>
@@ -11397,7 +12450,7 @@
         <v>530</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>750</v>
+        <v>1058</v>
       </c>
       <c r="J281" s="0">
         <v>302.97559999999999</v>
@@ -11429,7 +12482,7 @@
         <v>531</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>751</v>
+        <v>1059</v>
       </c>
       <c r="J282" s="0">
         <v>8923.2001999999993</v>
@@ -11461,7 +12514,7 @@
         <v>532</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>752</v>
+        <v>1060</v>
       </c>
       <c r="J283" s="0">
         <v>7434.9364999999998</v>
@@ -11493,7 +12546,7 @@
         <v>533</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>753</v>
+        <v>1061</v>
       </c>
       <c r="J284" s="0">
         <v>1198.5989</v>
@@ -11525,7 +12578,7 @@
         <v>534</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>754</v>
+        <v>1062</v>
       </c>
       <c r="J285" s="0">
         <v>1016.6576</v>
@@ -11557,7 +12610,7 @@
         <v>543</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>755</v>
+        <v>1063</v>
       </c>
       <c r="J286" s="0">
         <v>10363.415999999999</v>
@@ -11589,7 +12642,7 @@
         <v>544</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>756</v>
+        <v>1064</v>
       </c>
       <c r="J287" s="0">
         <v>8731.0702999999994</v>
@@ -11621,7 +12674,7 @@
         <v>547</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>759</v>
+        <v>1065</v>
       </c>
       <c r="J288" s="0">
         <v>509.65910000000002</v>
@@ -11653,7 +12706,7 @@
         <v>64</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>760</v>
+        <v>1066</v>
       </c>
       <c r="J289" s="0">
         <v>497.6062</v>
@@ -11685,7 +12738,7 @@
         <v>548</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>761</v>
+        <v>1067</v>
       </c>
       <c r="J290" s="0">
         <v>473.81920000000002</v>
@@ -11717,7 +12770,7 @@
         <v>549</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>762</v>
+        <v>1068</v>
       </c>
       <c r="J291" s="0">
         <v>386.12639999999999</v>
@@ -11749,7 +12802,7 @@
         <v>550</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>763</v>
+        <v>1069</v>
       </c>
       <c r="J292" s="0">
         <v>381.40570000000002</v>
@@ -11781,7 +12834,7 @@
         <v>551</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>764</v>
+        <v>1070</v>
       </c>
       <c r="J293" s="0">
         <v>371.59660000000002</v>
@@ -11813,7 +12866,7 @@
         <v>552</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>765</v>
+        <v>1071</v>
       </c>
       <c r="J294" s="0">
         <v>364.02569999999997</v>
@@ -11845,7 +12898,7 @@
         <v>553</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>766</v>
+        <v>1072</v>
       </c>
       <c r="J295" s="0">
         <v>331.7552</v>
@@ -11877,7 +12930,7 @@
         <v>554</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>767</v>
+        <v>1073</v>
       </c>
       <c r="J296" s="0">
         <v>1621.762</v>
@@ -11909,7 +12962,7 @@
         <v>555</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>768</v>
+        <v>1074</v>
       </c>
       <c r="J297" s="0">
         <v>1023.5883</v>
@@ -11941,7 +12994,7 @@
         <v>556</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>769</v>
+        <v>1075</v>
       </c>
       <c r="J298" s="0">
         <v>634.67409999999995</v>
@@ -11973,7 +13026,7 @@
         <v>557</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>770</v>
+        <v>1076</v>
       </c>
       <c r="J299" s="0">
         <v>589.45230000000004</v>
@@ -12005,7 +13058,7 @@
         <v>558</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>771</v>
+        <v>1077</v>
       </c>
       <c r="J300" s="0">
         <v>441.32260000000002</v>
@@ -12037,7 +13090,7 @@
         <v>559</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>772</v>
+        <v>1078</v>
       </c>
       <c r="J301" s="0">
         <v>406.00639999999999</v>
@@ -12069,7 +13122,7 @@
         <v>560</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>773</v>
+        <v>1079</v>
       </c>
       <c r="J302" s="0">
         <v>404.98939999999999</v>
@@ -12101,7 +13154,7 @@
         <v>561</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>774</v>
+        <v>1080</v>
       </c>
       <c r="J303" s="0">
         <v>356.87450000000001</v>
@@ -12133,7 +13186,7 @@
         <v>562</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>775</v>
+        <v>1081</v>
       </c>
       <c r="J304" s="0">
         <v>326.86750000000001</v>
@@ -12165,7 +13218,7 @@
         <v>563</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>776</v>
+        <v>1082</v>
       </c>
       <c r="J305" s="0">
         <v>313.15320000000003</v>
@@ -12197,7 +13250,7 @@
         <v>564</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>777</v>
+        <v>1083</v>
       </c>
       <c r="J306" s="0">
         <v>302.25330000000002</v>
@@ -12229,7 +13282,7 @@
         <v>565</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>778</v>
+        <v>1084</v>
       </c>
       <c r="J307" s="0">
         <v>241.7327</v>
@@ -12261,7 +13314,7 @@
         <v>129</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>452</v>
+        <v>1085</v>
       </c>
       <c r="J308" s="0">
         <v>8389.2909999999993</v>
@@ -12293,7 +13346,7 @@
         <v>130</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>453</v>
+        <v>1086</v>
       </c>
       <c r="J309" s="0">
         <v>8068.0429999999997</v>
@@ -12325,7 +13378,7 @@
         <v>208</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>454</v>
+        <v>1087</v>
       </c>
       <c r="J310" s="0">
         <v>1304.9119000000001</v>
@@ -12357,7 +13410,7 @@
         <v>133</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>456</v>
+        <v>1088</v>
       </c>
       <c r="J311" s="0">
         <v>528.16520000000003</v>
@@ -12389,7 +13442,7 @@
         <v>134</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>457</v>
+        <v>1089</v>
       </c>
       <c r="J312" s="0">
         <v>464.43889999999999</v>
@@ -12421,7 +13474,7 @@
         <v>135</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>458</v>
+        <v>1090</v>
       </c>
       <c r="J313" s="0">
         <v>449.87619999999998</v>
@@ -12453,7 +13506,7 @@
         <v>136</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>459</v>
+        <v>1091</v>
       </c>
       <c r="J314" s="0">
         <v>447.66699999999997</v>
@@ -12485,7 +13538,7 @@
         <v>137</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>460</v>
+        <v>1092</v>
       </c>
       <c r="J315" s="0">
         <v>391.69869999999997</v>
@@ -12517,7 +13570,7 @@
         <v>138</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>461</v>
+        <v>1093</v>
       </c>
       <c r="J316" s="0">
         <v>372.4153</v>
@@ -12549,7 +13602,7 @@
         <v>139</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>462</v>
+        <v>1094</v>
       </c>
       <c r="J317" s="0">
         <v>366.97289999999998</v>
@@ -12581,7 +13634,7 @@
         <v>140</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>463</v>
+        <v>1095</v>
       </c>
       <c r="J318" s="0">
         <v>329.11259999999999</v>
@@ -12613,7 +13666,7 @@
         <v>58</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>464</v>
+        <v>1096</v>
       </c>
       <c r="J319" s="0">
         <v>9741.5614999999998</v>
@@ -12645,7 +13698,7 @@
         <v>59</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>465</v>
+        <v>1097</v>
       </c>
       <c r="J320" s="0">
         <v>8198.8974999999991</v>
@@ -12677,7 +13730,7 @@
         <v>60</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>466</v>
+        <v>1098</v>
       </c>
       <c r="J321" s="0">
         <v>1259.1116</v>
@@ -12709,7 +13762,7 @@
         <v>210</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>467</v>
+        <v>1099</v>
       </c>
       <c r="J322" s="0">
         <v>964.0145</v>
@@ -12741,7 +13794,7 @@
         <v>141</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>468</v>
+        <v>1100</v>
       </c>
       <c r="J323" s="0">
         <v>539.45429999999999</v>
@@ -12773,7 +13826,7 @@
         <v>142</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>469</v>
+        <v>1101</v>
       </c>
       <c r="J324" s="0">
         <v>485.64830000000001</v>
@@ -12805,7 +13858,7 @@
         <v>143</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>470</v>
+        <v>1102</v>
       </c>
       <c r="J325" s="0">
         <v>457.39609999999999</v>
@@ -12837,7 +13890,7 @@
         <v>144</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>471</v>
+        <v>1103</v>
       </c>
       <c r="J326" s="0">
         <v>454.66460000000001</v>
@@ -12869,7 +13922,7 @@
         <v>145</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>472</v>
+        <v>1104</v>
       </c>
       <c r="J327" s="0">
         <v>368.51979999999998</v>
@@ -12901,7 +13954,7 @@
         <v>146</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>473</v>
+        <v>1105</v>
       </c>
       <c r="J328" s="0">
         <v>342.74220000000003</v>
@@ -12933,7 +13986,7 @@
         <v>147</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>474</v>
+        <v>1106</v>
       </c>
       <c r="J329" s="0">
         <v>302.46800000000002</v>
@@ -12965,7 +14018,7 @@
         <v>148</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>475</v>
+        <v>1107</v>
       </c>
       <c r="J330" s="0">
         <v>300.47250000000003</v>
@@ -12997,7 +14050,7 @@
         <v>149</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>476</v>
+        <v>1108</v>
       </c>
       <c r="J331" s="0">
         <v>10892.9414</v>
@@ -13029,7 +14082,7 @@
         <v>150</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>477</v>
+        <v>1109</v>
       </c>
       <c r="J332" s="0">
         <v>5918.6806999999999</v>
@@ -13061,7 +14114,7 @@
         <v>152</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>479</v>
+        <v>1110</v>
       </c>
       <c r="J333" s="0">
         <v>726.14110000000005</v>
@@ -13093,7 +14146,7 @@
         <v>153</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>480</v>
+        <v>1111</v>
       </c>
       <c r="J334" s="0">
         <v>498.3132</v>
@@ -13125,7 +14178,7 @@
         <v>154</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>481</v>
+        <v>1112</v>
       </c>
       <c r="J335" s="0">
         <v>487.10520000000002</v>
@@ -13157,7 +14210,7 @@
         <v>155</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>482</v>
+        <v>1113</v>
       </c>
       <c r="J336" s="0">
         <v>485.66770000000002</v>
@@ -13189,7 +14242,7 @@
         <v>156</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>483</v>
+        <v>1114</v>
       </c>
       <c r="J337" s="0">
         <v>478.11529999999999</v>
@@ -13221,7 +14274,7 @@
         <v>157</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>484</v>
+        <v>1115</v>
       </c>
       <c r="J338" s="0">
         <v>375.48970000000003</v>
@@ -13253,7 +14306,7 @@
         <v>158</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>485</v>
+        <v>1116</v>
       </c>
       <c r="J339" s="0">
         <v>359.0838</v>
@@ -13285,7 +14338,7 @@
         <v>159</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>486</v>
+        <v>1117</v>
       </c>
       <c r="J340" s="0">
         <v>338.9837</v>
@@ -13317,7 +14370,7 @@
         <v>160</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>487</v>
+        <v>1118</v>
       </c>
       <c r="J341" s="0">
         <v>293.55579999999998</v>
@@ -13349,7 +14402,7 @@
         <v>161</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>488</v>
+        <v>1119</v>
       </c>
       <c r="J342" s="0">
         <v>9826.1103999999996</v>
@@ -13381,7 +14434,7 @@
         <v>162</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>489</v>
+        <v>1120</v>
       </c>
       <c r="J343" s="0">
         <v>7957.9004000000004</v>
@@ -13413,7 +14466,7 @@
         <v>163</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>490</v>
+        <v>1121</v>
       </c>
       <c r="J344" s="0">
         <v>1958.7829999999999</v>
@@ -13445,7 +14498,7 @@
         <v>165</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>492</v>
+        <v>1122</v>
       </c>
       <c r="J345" s="0">
         <v>574.80640000000005</v>
@@ -13477,7 +14530,7 @@
         <v>166</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>493</v>
+        <v>1123</v>
       </c>
       <c r="J346" s="0">
         <v>532.89999999999998</v>
@@ -13509,7 +14562,7 @@
         <v>167</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>494</v>
+        <v>1124</v>
       </c>
       <c r="J347" s="0">
         <v>470.99040000000002</v>
@@ -13541,7 +14594,7 @@
         <v>168</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>495</v>
+        <v>1125</v>
       </c>
       <c r="J348" s="0">
         <v>428.05349999999999</v>
@@ -13573,7 +14626,7 @@
         <v>169</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>496</v>
+        <v>1126</v>
       </c>
       <c r="J349" s="0">
         <v>370.83409999999998</v>
@@ -13605,7 +14658,7 @@
         <v>170</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>497</v>
+        <v>1127</v>
       </c>
       <c r="J350" s="0">
         <v>361.65289999999999</v>
@@ -13637,7 +14690,7 @@
         <v>171</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>498</v>
+        <v>1128</v>
       </c>
       <c r="J351" s="0">
         <v>328.18830000000003</v>
@@ -13669,7 +14722,7 @@
         <v>172</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>499</v>
+        <v>1129</v>
       </c>
       <c r="J352" s="0">
         <v>313.28399999999999</v>

--- a/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="82501" uniqueCount="1130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="193416" uniqueCount="1130">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="193416" uniqueCount="1130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="199754" uniqueCount="1130">
   <si>
     <t>Year</t>
   </si>
@@ -3452,16 +3452,16 @@
   <dimension ref="A1:J397"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" customWidth="true"/>
-    <col min="2" max="2" width="7" customWidth="true"/>
-    <col min="3" max="3" width="11.28515625" customWidth="true"/>
-    <col min="4" max="4" width="17.28515625" customWidth="true"/>
-    <col min="5" max="5" width="12.7109375" customWidth="true"/>
-    <col min="6" max="6" width="13" customWidth="true"/>
-    <col min="7" max="7" width="8.5703125" customWidth="true"/>
-    <col min="8" max="8" width="37.42578125" customWidth="true"/>
-    <col min="9" max="9" width="147" customWidth="true"/>
-    <col min="10" max="10" width="10.7109375" customWidth="true"/>
+    <col min="1" max="1" width="14.08984375" customWidth="true"/>
+    <col min="2" max="2" width="6.54296875" customWidth="true"/>
+    <col min="3" max="3" width="10.36328125" customWidth="true"/>
+    <col min="4" max="4" width="16.36328125" customWidth="true"/>
+    <col min="5" max="5" width="11.81640625" customWidth="true"/>
+    <col min="6" max="6" width="11.90625" customWidth="true"/>
+    <col min="7" max="7" width="7.90625" customWidth="true"/>
+    <col min="8" max="8" width="36.26953125" customWidth="true"/>
+    <col min="9" max="9" width="167.54296875" customWidth="true"/>
+    <col min="10" max="10" width="10.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3522,7 +3522,7 @@
         <v>46</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>779</v>
+        <v>212</v>
       </c>
       <c r="J2" s="0">
         <v>13088.609399999999</v>
@@ -3554,7 +3554,7 @@
         <v>47</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>780</v>
+        <v>213</v>
       </c>
       <c r="J3" s="0">
         <v>9104.8721000000005</v>
@@ -3586,7 +3586,7 @@
         <v>48</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>781</v>
+        <v>214</v>
       </c>
       <c r="J4" s="0">
         <v>1438.8326</v>
@@ -3618,7 +3618,7 @@
         <v>49</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>782</v>
+        <v>215</v>
       </c>
       <c r="J5" s="0">
         <v>1210.5242000000001</v>
@@ -3650,7 +3650,7 @@
         <v>50</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>783</v>
+        <v>216</v>
       </c>
       <c r="J6" s="0">
         <v>542.07240000000002</v>
@@ -3682,7 +3682,7 @@
         <v>51</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>784</v>
+        <v>217</v>
       </c>
       <c r="J7" s="0">
         <v>528.39120000000003</v>
@@ -3714,7 +3714,7 @@
         <v>52</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>785</v>
+        <v>218</v>
       </c>
       <c r="J8" s="0">
         <v>519.83349999999996</v>
@@ -3746,7 +3746,7 @@
         <v>53</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>786</v>
+        <v>219</v>
       </c>
       <c r="J9" s="0">
         <v>465.38400000000001</v>
@@ -3778,7 +3778,7 @@
         <v>54</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>787</v>
+        <v>220</v>
       </c>
       <c r="J10" s="0">
         <v>387.42579999999998</v>
@@ -3810,7 +3810,7 @@
         <v>55</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>788</v>
+        <v>221</v>
       </c>
       <c r="J11" s="0">
         <v>376.01639999999998</v>
@@ -3842,7 +3842,7 @@
         <v>56</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>789</v>
+        <v>222</v>
       </c>
       <c r="J12" s="0">
         <v>367.9187</v>
@@ -3874,7 +3874,7 @@
         <v>57</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>790</v>
+        <v>223</v>
       </c>
       <c r="J13" s="0">
         <v>345.6712</v>
@@ -3906,7 +3906,7 @@
         <v>58</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>791</v>
+        <v>224</v>
       </c>
       <c r="J14" s="0">
         <v>9741.5614999999998</v>
@@ -3938,7 +3938,7 @@
         <v>59</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>792</v>
+        <v>225</v>
       </c>
       <c r="J15" s="0">
         <v>8198.8974999999991</v>
@@ -3970,7 +3970,7 @@
         <v>60</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>793</v>
+        <v>226</v>
       </c>
       <c r="J16" s="0">
         <v>1259.1116</v>
@@ -4002,7 +4002,7 @@
         <v>61</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>794</v>
+        <v>227</v>
       </c>
       <c r="J17" s="0">
         <v>863.95190000000002</v>
@@ -4034,7 +4034,7 @@
         <v>62</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>795</v>
+        <v>228</v>
       </c>
       <c r="J18" s="0">
         <v>574.15189999999996</v>
@@ -4066,7 +4066,7 @@
         <v>63</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>796</v>
+        <v>229</v>
       </c>
       <c r="J19" s="0">
         <v>514.2156</v>
@@ -4098,7 +4098,7 @@
         <v>64</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>797</v>
+        <v>230</v>
       </c>
       <c r="J20" s="0">
         <v>497.6062</v>
@@ -4130,7 +4130,7 @@
         <v>65</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>798</v>
+        <v>231</v>
       </c>
       <c r="J21" s="0">
         <v>496.00400000000002</v>
@@ -4162,7 +4162,7 @@
         <v>66</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>799</v>
+        <v>232</v>
       </c>
       <c r="J22" s="0">
         <v>389.9522</v>
@@ -4194,7 +4194,7 @@
         <v>67</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>800</v>
+        <v>233</v>
       </c>
       <c r="J23" s="0">
         <v>332.78969999999998</v>
@@ -4226,7 +4226,7 @@
         <v>68</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>801</v>
+        <v>234</v>
       </c>
       <c r="J24" s="0">
         <v>320.5446</v>
@@ -4258,7 +4258,7 @@
         <v>69</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>802</v>
+        <v>235</v>
       </c>
       <c r="J25" s="0">
         <v>288.99189999999999</v>
@@ -4290,7 +4290,7 @@
         <v>71</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>803</v>
+        <v>237</v>
       </c>
       <c r="J26" s="0">
         <v>5932.7479999999996</v>
@@ -4322,7 +4322,7 @@
         <v>72</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>804</v>
+        <v>238</v>
       </c>
       <c r="J27" s="0">
         <v>901.9991</v>
@@ -4354,7 +4354,7 @@
         <v>73</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>805</v>
+        <v>239</v>
       </c>
       <c r="J28" s="0">
         <v>893.56960000000004</v>
@@ -4386,7 +4386,7 @@
         <v>74</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>806</v>
+        <v>240</v>
       </c>
       <c r="J29" s="0">
         <v>549.74869999999999</v>
@@ -4418,7 +4418,7 @@
         <v>75</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>807</v>
+        <v>241</v>
       </c>
       <c r="J30" s="0">
         <v>530.14729999999997</v>
@@ -4450,7 +4450,7 @@
         <v>76</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>808</v>
+        <v>242</v>
       </c>
       <c r="J31" s="0">
         <v>489.4966</v>
@@ -4482,7 +4482,7 @@
         <v>77</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>809</v>
+        <v>243</v>
       </c>
       <c r="J32" s="0">
         <v>482.49549999999999</v>
@@ -4514,7 +4514,7 @@
         <v>78</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>810</v>
+        <v>244</v>
       </c>
       <c r="J33" s="0">
         <v>378.9196</v>
@@ -4546,7 +4546,7 @@
         <v>79</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>811</v>
+        <v>245</v>
       </c>
       <c r="J34" s="0">
         <v>366.15300000000002</v>
@@ -4578,7 +4578,7 @@
         <v>80</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>812</v>
+        <v>246</v>
       </c>
       <c r="J35" s="0">
         <v>340.57749999999999</v>
@@ -4610,7 +4610,7 @@
         <v>82</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>813</v>
+        <v>248</v>
       </c>
       <c r="J36" s="0">
         <v>10466.208000000001</v>
@@ -4642,7 +4642,7 @@
         <v>83</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>814</v>
+        <v>249</v>
       </c>
       <c r="J37" s="0">
         <v>7328.0029000000004</v>
@@ -4674,7 +4674,7 @@
         <v>84</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>815</v>
+        <v>250</v>
       </c>
       <c r="J38" s="0">
         <v>1015.5606</v>
@@ -4706,7 +4706,7 @@
         <v>85</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>816</v>
+        <v>251</v>
       </c>
       <c r="J39" s="0">
         <v>908.67830000000004</v>
@@ -4738,7 +4738,7 @@
         <v>86</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>817</v>
+        <v>252</v>
       </c>
       <c r="J40" s="0">
         <v>520.97770000000003</v>
@@ -4770,7 +4770,7 @@
         <v>87</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>818</v>
+        <v>253</v>
       </c>
       <c r="J41" s="0">
         <v>488.97149999999999</v>
@@ -4802,7 +4802,7 @@
         <v>88</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>819</v>
+        <v>254</v>
       </c>
       <c r="J42" s="0">
         <v>484.75029999999998</v>
@@ -4834,7 +4834,7 @@
         <v>89</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>820</v>
+        <v>255</v>
       </c>
       <c r="J43" s="0">
         <v>438.36930000000001</v>
@@ -4866,7 +4866,7 @@
         <v>90</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>821</v>
+        <v>256</v>
       </c>
       <c r="J44" s="0">
         <v>369.10219999999998</v>
@@ -4898,7 +4898,7 @@
         <v>91</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>822</v>
+        <v>257</v>
       </c>
       <c r="J45" s="0">
         <v>342.30680000000001</v>
@@ -4930,7 +4930,7 @@
         <v>92</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>823</v>
+        <v>258</v>
       </c>
       <c r="J46" s="0">
         <v>280.75409999999999</v>
@@ -4962,7 +4962,7 @@
         <v>93</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>824</v>
+        <v>259</v>
       </c>
       <c r="J47" s="0">
         <v>270.84679999999997</v>
@@ -4994,7 +4994,7 @@
         <v>94</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>825</v>
+        <v>260</v>
       </c>
       <c r="J48" s="0">
         <v>8934.2567999999992</v>
@@ -5026,7 +5026,7 @@
         <v>95</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>826</v>
+        <v>261</v>
       </c>
       <c r="J49" s="0">
         <v>7192.2339000000002</v>
@@ -5058,7 +5058,7 @@
         <v>97</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>827</v>
+        <v>263</v>
       </c>
       <c r="J50" s="0">
         <v>892.98720000000003</v>
@@ -5090,7 +5090,7 @@
         <v>99</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>828</v>
+        <v>265</v>
       </c>
       <c r="J51" s="0">
         <v>489.01900000000001</v>
@@ -5122,7 +5122,7 @@
         <v>100</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>829</v>
+        <v>266</v>
       </c>
       <c r="J52" s="0">
         <v>486.78719999999999</v>
@@ -5154,7 +5154,7 @@
         <v>101</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>830</v>
+        <v>267</v>
       </c>
       <c r="J53" s="0">
         <v>478.59969999999999</v>
@@ -5186,7 +5186,7 @@
         <v>102</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>831</v>
+        <v>268</v>
       </c>
       <c r="J54" s="0">
         <v>456.38220000000001</v>
@@ -5218,7 +5218,7 @@
         <v>103</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>832</v>
+        <v>269</v>
       </c>
       <c r="J55" s="0">
         <v>361.197</v>
@@ -5250,7 +5250,7 @@
         <v>104</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>833</v>
+        <v>270</v>
       </c>
       <c r="J56" s="0">
         <v>350.10750000000002</v>
@@ -5282,7 +5282,7 @@
         <v>105</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>834</v>
+        <v>271</v>
       </c>
       <c r="J57" s="0">
         <v>332.8802</v>
@@ -5314,7 +5314,7 @@
         <v>106</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>835</v>
+        <v>272</v>
       </c>
       <c r="J58" s="0">
         <v>9850.5967000000001</v>
@@ -5346,7 +5346,7 @@
         <v>107</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>836</v>
+        <v>273</v>
       </c>
       <c r="J59" s="0">
         <v>8299.1229999999996</v>
@@ -5378,7 +5378,7 @@
         <v>108</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>837</v>
+        <v>274</v>
       </c>
       <c r="J60" s="0">
         <v>1061.2550000000001</v>
@@ -5410,7 +5410,7 @@
         <v>61</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>838</v>
+        <v>275</v>
       </c>
       <c r="J61" s="0">
         <v>863.95190000000002</v>
@@ -5442,7 +5442,7 @@
         <v>109</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>839</v>
+        <v>276</v>
       </c>
       <c r="J62" s="0">
         <v>537.24440000000004</v>
@@ -5474,7 +5474,7 @@
         <v>110</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>840</v>
+        <v>277</v>
       </c>
       <c r="J63" s="0">
         <v>512.39139999999998</v>
@@ -5506,7 +5506,7 @@
         <v>111</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>841</v>
+        <v>278</v>
       </c>
       <c r="J64" s="0">
         <v>461.678</v>
@@ -5538,7 +5538,7 @@
         <v>112</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>842</v>
+        <v>279</v>
       </c>
       <c r="J65" s="0">
         <v>446.13510000000002</v>
@@ -5570,7 +5570,7 @@
         <v>113</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>843</v>
+        <v>280</v>
       </c>
       <c r="J66" s="0">
         <v>416.1148</v>
@@ -5602,7 +5602,7 @@
         <v>114</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>844</v>
+        <v>281</v>
       </c>
       <c r="J67" s="0">
         <v>385.80329999999998</v>
@@ -5634,7 +5634,7 @@
         <v>115</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>845</v>
+        <v>282</v>
       </c>
       <c r="J68" s="0">
         <v>376.43869999999998</v>
@@ -5666,7 +5666,7 @@
         <v>116</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>846</v>
+        <v>283</v>
       </c>
       <c r="J69" s="0">
         <v>340.64490000000001</v>
@@ -5698,7 +5698,7 @@
         <v>117</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>847</v>
+        <v>284</v>
       </c>
       <c r="J70" s="0">
         <v>9114.7715000000008</v>
@@ -5730,7 +5730,7 @@
         <v>118</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>848</v>
+        <v>285</v>
       </c>
       <c r="J71" s="0">
         <v>7656.0316999999996</v>
@@ -5762,7 +5762,7 @@
         <v>121</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>849</v>
+        <v>288</v>
       </c>
       <c r="J72" s="0">
         <v>542.5788</v>
@@ -5794,7 +5794,7 @@
         <v>122</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>850</v>
+        <v>289</v>
       </c>
       <c r="J73" s="0">
         <v>534.76580000000001</v>
@@ -5826,7 +5826,7 @@
         <v>123</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>851</v>
+        <v>290</v>
       </c>
       <c r="J74" s="0">
         <v>484.83710000000002</v>
@@ -5858,7 +5858,7 @@
         <v>124</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>852</v>
+        <v>291</v>
       </c>
       <c r="J75" s="0">
         <v>468.87529999999998</v>
@@ -5890,7 +5890,7 @@
         <v>125</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>853</v>
+        <v>292</v>
       </c>
       <c r="J76" s="0">
         <v>398.83769999999998</v>
@@ -5922,7 +5922,7 @@
         <v>126</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>854</v>
+        <v>293</v>
       </c>
       <c r="J77" s="0">
         <v>337.36939999999999</v>
@@ -5954,7 +5954,7 @@
         <v>127</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>855</v>
+        <v>294</v>
       </c>
       <c r="J78" s="0">
         <v>311.84429999999998</v>
@@ -5986,7 +5986,7 @@
         <v>128</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>856</v>
+        <v>295</v>
       </c>
       <c r="J79" s="0">
         <v>245.285</v>
@@ -6018,7 +6018,7 @@
         <v>507</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>857</v>
+        <v>679</v>
       </c>
       <c r="J80" s="0">
         <v>10897.75</v>
@@ -6050,7 +6050,7 @@
         <v>508</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>858</v>
+        <v>680</v>
       </c>
       <c r="J81" s="0">
         <v>5963.8306000000002</v>
@@ -6082,7 +6082,7 @@
         <v>509</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>859</v>
+        <v>681</v>
       </c>
       <c r="J82" s="0">
         <v>1364.115</v>
@@ -6114,7 +6114,7 @@
         <v>510</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>860</v>
+        <v>682</v>
       </c>
       <c r="J83" s="0">
         <v>1002.6719000000001</v>
@@ -6146,7 +6146,7 @@
         <v>511</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>861</v>
+        <v>683</v>
       </c>
       <c r="J84" s="0">
         <v>557.97879999999998</v>
@@ -6178,7 +6178,7 @@
         <v>512</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>862</v>
+        <v>684</v>
       </c>
       <c r="J85" s="0">
         <v>511.4341</v>
@@ -6210,7 +6210,7 @@
         <v>513</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>863</v>
+        <v>685</v>
       </c>
       <c r="J86" s="0">
         <v>485.53699999999998</v>
@@ -6242,7 +6242,7 @@
         <v>514</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>864</v>
+        <v>686</v>
       </c>
       <c r="J87" s="0">
         <v>456.29579999999999</v>
@@ -6274,7 +6274,7 @@
         <v>515</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>865</v>
+        <v>687</v>
       </c>
       <c r="J88" s="0">
         <v>403.62130000000002</v>
@@ -6306,7 +6306,7 @@
         <v>516</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>866</v>
+        <v>688</v>
       </c>
       <c r="J89" s="0">
         <v>384.92849999999999</v>
@@ -6338,7 +6338,7 @@
         <v>517</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>867</v>
+        <v>689</v>
       </c>
       <c r="J90" s="0">
         <v>345.9332</v>
@@ -6370,7 +6370,7 @@
         <v>518</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>868</v>
+        <v>690</v>
       </c>
       <c r="J91" s="0">
         <v>329.33870000000002</v>
@@ -6402,7 +6402,7 @@
         <v>519</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>869</v>
+        <v>691</v>
       </c>
       <c r="J92" s="0">
         <v>9494.3554999999997</v>
@@ -6434,7 +6434,7 @@
         <v>520</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>870</v>
+        <v>692</v>
       </c>
       <c r="J93" s="0">
         <v>6959.3242</v>
@@ -6466,7 +6466,7 @@
         <v>523</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>871</v>
+        <v>695</v>
       </c>
       <c r="J94" s="0">
         <v>528.32619999999997</v>
@@ -6498,7 +6498,7 @@
         <v>524</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>872</v>
+        <v>696</v>
       </c>
       <c r="J95" s="0">
         <v>502.16129999999998</v>
@@ -6530,7 +6530,7 @@
         <v>525</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>873</v>
+        <v>697</v>
       </c>
       <c r="J96" s="0">
         <v>468.14839999999998</v>
@@ -6562,7 +6562,7 @@
         <v>526</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>874</v>
+        <v>698</v>
       </c>
       <c r="J97" s="0">
         <v>413.35890000000001</v>
@@ -6594,7 +6594,7 @@
         <v>527</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>875</v>
+        <v>699</v>
       </c>
       <c r="J98" s="0">
         <v>410.47199999999998</v>
@@ -6626,7 +6626,7 @@
         <v>528</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>876</v>
+        <v>700</v>
       </c>
       <c r="J99" s="0">
         <v>371.8809</v>
@@ -6658,7 +6658,7 @@
         <v>529</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>877</v>
+        <v>701</v>
       </c>
       <c r="J100" s="0">
         <v>347.0478</v>
@@ -6690,7 +6690,7 @@
         <v>530</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>878</v>
+        <v>702</v>
       </c>
       <c r="J101" s="0">
         <v>302.97559999999999</v>
@@ -6722,7 +6722,7 @@
         <v>531</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>879</v>
+        <v>703</v>
       </c>
       <c r="J102" s="0">
         <v>8923.2001999999993</v>
@@ -6754,7 +6754,7 @@
         <v>532</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>880</v>
+        <v>704</v>
       </c>
       <c r="J103" s="0">
         <v>7434.9364999999998</v>
@@ -6786,7 +6786,7 @@
         <v>533</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>881</v>
+        <v>705</v>
       </c>
       <c r="J104" s="0">
         <v>1198.5989</v>
@@ -6818,7 +6818,7 @@
         <v>534</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>882</v>
+        <v>706</v>
       </c>
       <c r="J105" s="0">
         <v>1016.6576</v>
@@ -6850,7 +6850,7 @@
         <v>543</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>883</v>
+        <v>715</v>
       </c>
       <c r="J106" s="0">
         <v>10363.415999999999</v>
@@ -6882,7 +6882,7 @@
         <v>544</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>884</v>
+        <v>716</v>
       </c>
       <c r="J107" s="0">
         <v>8731.0702999999994</v>
@@ -6914,7 +6914,7 @@
         <v>547</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>885</v>
+        <v>719</v>
       </c>
       <c r="J108" s="0">
         <v>509.65910000000002</v>
@@ -6946,7 +6946,7 @@
         <v>548</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>886</v>
+        <v>720</v>
       </c>
       <c r="J109" s="0">
         <v>473.81920000000002</v>
@@ -6978,7 +6978,7 @@
         <v>549</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>887</v>
+        <v>721</v>
       </c>
       <c r="J110" s="0">
         <v>386.12639999999999</v>
@@ -7010,7 +7010,7 @@
         <v>550</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>888</v>
+        <v>722</v>
       </c>
       <c r="J111" s="0">
         <v>381.40570000000002</v>
@@ -7042,7 +7042,7 @@
         <v>551</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>889</v>
+        <v>723</v>
       </c>
       <c r="J112" s="0">
         <v>371.59660000000002</v>
@@ -7074,7 +7074,7 @@
         <v>552</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>890</v>
+        <v>724</v>
       </c>
       <c r="J113" s="0">
         <v>364.02569999999997</v>
@@ -7106,7 +7106,7 @@
         <v>146</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>891</v>
+        <v>725</v>
       </c>
       <c r="J114" s="0">
         <v>342.74220000000003</v>
@@ -7138,7 +7138,7 @@
         <v>553</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>892</v>
+        <v>726</v>
       </c>
       <c r="J115" s="0">
         <v>331.7552</v>
@@ -7170,7 +7170,7 @@
         <v>129</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>893</v>
+        <v>296</v>
       </c>
       <c r="J116" s="0">
         <v>8389.2909999999993</v>
@@ -7202,7 +7202,7 @@
         <v>130</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>894</v>
+        <v>297</v>
       </c>
       <c r="J117" s="0">
         <v>8068.0429999999997</v>
@@ -7234,7 +7234,7 @@
         <v>133</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>895</v>
+        <v>300</v>
       </c>
       <c r="J118" s="0">
         <v>528.16520000000003</v>
@@ -7266,7 +7266,7 @@
         <v>134</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>896</v>
+        <v>301</v>
       </c>
       <c r="J119" s="0">
         <v>464.43889999999999</v>
@@ -7298,7 +7298,7 @@
         <v>135</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>897</v>
+        <v>302</v>
       </c>
       <c r="J120" s="0">
         <v>449.87619999999998</v>
@@ -7330,7 +7330,7 @@
         <v>136</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>898</v>
+        <v>303</v>
       </c>
       <c r="J121" s="0">
         <v>447.66699999999997</v>
@@ -7362,7 +7362,7 @@
         <v>137</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>899</v>
+        <v>304</v>
       </c>
       <c r="J122" s="0">
         <v>391.69869999999997</v>
@@ -7394,7 +7394,7 @@
         <v>138</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>900</v>
+        <v>305</v>
       </c>
       <c r="J123" s="0">
         <v>372.4153</v>
@@ -7426,7 +7426,7 @@
         <v>139</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>901</v>
+        <v>306</v>
       </c>
       <c r="J124" s="0">
         <v>366.97289999999998</v>
@@ -7458,7 +7458,7 @@
         <v>140</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>902</v>
+        <v>307</v>
       </c>
       <c r="J125" s="0">
         <v>329.11259999999999</v>
@@ -7490,7 +7490,7 @@
         <v>58</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>903</v>
+        <v>308</v>
       </c>
       <c r="J126" s="0">
         <v>9741.5614999999998</v>
@@ -7522,7 +7522,7 @@
         <v>59</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>904</v>
+        <v>309</v>
       </c>
       <c r="J127" s="0">
         <v>8198.8974999999991</v>
@@ -7554,7 +7554,7 @@
         <v>60</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>905</v>
+        <v>310</v>
       </c>
       <c r="J128" s="0">
         <v>1259.1116</v>
@@ -7586,7 +7586,7 @@
         <v>61</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>906</v>
+        <v>311</v>
       </c>
       <c r="J129" s="0">
         <v>863.95190000000002</v>
@@ -7618,7 +7618,7 @@
         <v>141</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>907</v>
+        <v>312</v>
       </c>
       <c r="J130" s="0">
         <v>539.45429999999999</v>
@@ -7650,7 +7650,7 @@
         <v>142</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>908</v>
+        <v>313</v>
       </c>
       <c r="J131" s="0">
         <v>485.64830000000001</v>
@@ -7682,7 +7682,7 @@
         <v>143</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>909</v>
+        <v>314</v>
       </c>
       <c r="J132" s="0">
         <v>457.39609999999999</v>
@@ -7714,7 +7714,7 @@
         <v>144</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>910</v>
+        <v>315</v>
       </c>
       <c r="J133" s="0">
         <v>454.66460000000001</v>
@@ -7746,7 +7746,7 @@
         <v>145</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>911</v>
+        <v>316</v>
       </c>
       <c r="J134" s="0">
         <v>368.51979999999998</v>
@@ -7778,7 +7778,7 @@
         <v>146</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>912</v>
+        <v>317</v>
       </c>
       <c r="J135" s="0">
         <v>342.74220000000003</v>
@@ -7810,7 +7810,7 @@
         <v>147</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>913</v>
+        <v>318</v>
       </c>
       <c r="J136" s="0">
         <v>302.46800000000002</v>
@@ -7842,7 +7842,7 @@
         <v>148</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>914</v>
+        <v>319</v>
       </c>
       <c r="J137" s="0">
         <v>300.47250000000003</v>
@@ -7874,7 +7874,7 @@
         <v>149</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>915</v>
+        <v>320</v>
       </c>
       <c r="J138" s="0">
         <v>10892.9414</v>
@@ -7906,7 +7906,7 @@
         <v>150</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>916</v>
+        <v>321</v>
       </c>
       <c r="J139" s="0">
         <v>5918.6806999999999</v>
@@ -7938,7 +7938,7 @@
         <v>151</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>917</v>
+        <v>322</v>
       </c>
       <c r="J140" s="0">
         <v>829.46619999999996</v>
@@ -7970,7 +7970,7 @@
         <v>152</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>918</v>
+        <v>323</v>
       </c>
       <c r="J141" s="0">
         <v>726.14110000000005</v>
@@ -8002,7 +8002,7 @@
         <v>153</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>919</v>
+        <v>324</v>
       </c>
       <c r="J142" s="0">
         <v>498.3132</v>
@@ -8034,7 +8034,7 @@
         <v>154</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>920</v>
+        <v>325</v>
       </c>
       <c r="J143" s="0">
         <v>487.10520000000002</v>
@@ -8066,7 +8066,7 @@
         <v>155</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>921</v>
+        <v>326</v>
       </c>
       <c r="J144" s="0">
         <v>485.66770000000002</v>
@@ -8098,7 +8098,7 @@
         <v>156</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>922</v>
+        <v>327</v>
       </c>
       <c r="J145" s="0">
         <v>478.11529999999999</v>
@@ -8130,7 +8130,7 @@
         <v>157</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>923</v>
+        <v>328</v>
       </c>
       <c r="J146" s="0">
         <v>375.48970000000003</v>
@@ -8162,7 +8162,7 @@
         <v>158</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>924</v>
+        <v>329</v>
       </c>
       <c r="J147" s="0">
         <v>359.0838</v>
@@ -8194,7 +8194,7 @@
         <v>159</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>925</v>
+        <v>330</v>
       </c>
       <c r="J148" s="0">
         <v>338.9837</v>
@@ -8226,7 +8226,7 @@
         <v>160</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>926</v>
+        <v>331</v>
       </c>
       <c r="J149" s="0">
         <v>293.55579999999998</v>
@@ -8258,7 +8258,7 @@
         <v>161</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>927</v>
+        <v>332</v>
       </c>
       <c r="J150" s="0">
         <v>9826.1103999999996</v>
@@ -8290,7 +8290,7 @@
         <v>162</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>928</v>
+        <v>333</v>
       </c>
       <c r="J151" s="0">
         <v>7957.9004000000004</v>
@@ -8322,7 +8322,7 @@
         <v>163</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>929</v>
+        <v>334</v>
       </c>
       <c r="J152" s="0">
         <v>1958.7829999999999</v>
@@ -8354,7 +8354,7 @@
         <v>165</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>930</v>
+        <v>336</v>
       </c>
       <c r="J153" s="0">
         <v>574.80640000000005</v>
@@ -8386,7 +8386,7 @@
         <v>166</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>931</v>
+        <v>337</v>
       </c>
       <c r="J154" s="0">
         <v>532.89999999999998</v>
@@ -8418,7 +8418,7 @@
         <v>167</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>932</v>
+        <v>338</v>
       </c>
       <c r="J155" s="0">
         <v>470.99040000000002</v>
@@ -8450,7 +8450,7 @@
         <v>168</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>933</v>
+        <v>339</v>
       </c>
       <c r="J156" s="0">
         <v>428.05349999999999</v>
@@ -8482,7 +8482,7 @@
         <v>169</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>934</v>
+        <v>340</v>
       </c>
       <c r="J157" s="0">
         <v>370.83409999999998</v>
@@ -8514,7 +8514,7 @@
         <v>170</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>935</v>
+        <v>341</v>
       </c>
       <c r="J158" s="0">
         <v>361.65289999999999</v>
@@ -8546,7 +8546,7 @@
         <v>171</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>936</v>
+        <v>342</v>
       </c>
       <c r="J159" s="0">
         <v>328.18830000000003</v>
@@ -8578,7 +8578,7 @@
         <v>172</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>937</v>
+        <v>343</v>
       </c>
       <c r="J160" s="0">
         <v>313.28399999999999</v>
@@ -8610,7 +8610,7 @@
         <v>47</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>938</v>
+        <v>345</v>
       </c>
       <c r="J161" s="0">
         <v>9104.8721000000005</v>
@@ -8642,7 +8642,7 @@
         <v>48</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>939</v>
+        <v>346</v>
       </c>
       <c r="J162" s="0">
         <v>1438.8326</v>
@@ -8674,7 +8674,7 @@
         <v>49</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>940</v>
+        <v>347</v>
       </c>
       <c r="J163" s="0">
         <v>1210.5242000000001</v>
@@ -8706,7 +8706,7 @@
         <v>50</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>941</v>
+        <v>348</v>
       </c>
       <c r="J164" s="0">
         <v>542.07240000000002</v>
@@ -8738,7 +8738,7 @@
         <v>51</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>942</v>
+        <v>349</v>
       </c>
       <c r="J165" s="0">
         <v>528.39120000000003</v>
@@ -8770,7 +8770,7 @@
         <v>52</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>943</v>
+        <v>350</v>
       </c>
       <c r="J166" s="0">
         <v>519.83349999999996</v>
@@ -8802,7 +8802,7 @@
         <v>53</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>944</v>
+        <v>351</v>
       </c>
       <c r="J167" s="0">
         <v>465.38400000000001</v>
@@ -8834,7 +8834,7 @@
         <v>54</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>945</v>
+        <v>352</v>
       </c>
       <c r="J168" s="0">
         <v>387.42579999999998</v>
@@ -8866,7 +8866,7 @@
         <v>55</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>946</v>
+        <v>353</v>
       </c>
       <c r="J169" s="0">
         <v>376.01639999999998</v>
@@ -8898,7 +8898,7 @@
         <v>56</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>947</v>
+        <v>354</v>
       </c>
       <c r="J170" s="0">
         <v>367.9187</v>
@@ -8930,7 +8930,7 @@
         <v>57</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>948</v>
+        <v>355</v>
       </c>
       <c r="J171" s="0">
         <v>345.6712</v>
@@ -8962,7 +8962,7 @@
         <v>173</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>949</v>
+        <v>356</v>
       </c>
       <c r="J172" s="0">
         <v>11026.299800000001</v>
@@ -8994,7 +8994,7 @@
         <v>174</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>950</v>
+        <v>357</v>
       </c>
       <c r="J173" s="0">
         <v>8759.9452999999994</v>
@@ -9026,7 +9026,7 @@
         <v>175</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>951</v>
+        <v>358</v>
       </c>
       <c r="J174" s="0">
         <v>1159.0046</v>
@@ -9058,7 +9058,7 @@
         <v>176</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>952</v>
+        <v>359</v>
       </c>
       <c r="J175" s="0">
         <v>1153.3887</v>
@@ -9090,7 +9090,7 @@
         <v>177</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>953</v>
+        <v>360</v>
       </c>
       <c r="J176" s="0">
         <v>531.56039999999996</v>
@@ -9122,7 +9122,7 @@
         <v>178</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>954</v>
+        <v>361</v>
       </c>
       <c r="J177" s="0">
         <v>513.93790000000001</v>
@@ -9154,7 +9154,7 @@
         <v>179</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>955</v>
+        <v>362</v>
       </c>
       <c r="J178" s="0">
         <v>499.63580000000002</v>
@@ -9186,7 +9186,7 @@
         <v>180</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>956</v>
+        <v>363</v>
       </c>
       <c r="J179" s="0">
         <v>475.38760000000002</v>
@@ -9218,7 +9218,7 @@
         <v>181</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>957</v>
+        <v>364</v>
       </c>
       <c r="J180" s="0">
         <v>357.59019999999998</v>
@@ -9250,7 +9250,7 @@
         <v>182</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>958</v>
+        <v>365</v>
       </c>
       <c r="J181" s="0">
         <v>346.22629999999998</v>
@@ -9282,7 +9282,7 @@
         <v>183</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>959</v>
+        <v>366</v>
       </c>
       <c r="J182" s="0">
         <v>331.46199999999999</v>
@@ -9314,7 +9314,7 @@
         <v>184</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>960</v>
+        <v>367</v>
       </c>
       <c r="J183" s="0">
         <v>308.1046</v>
@@ -9346,7 +9346,7 @@
         <v>72</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>961</v>
+        <v>370</v>
       </c>
       <c r="J184" s="0">
         <v>901.9991</v>
@@ -9378,7 +9378,7 @@
         <v>73</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>962</v>
+        <v>371</v>
       </c>
       <c r="J185" s="0">
         <v>893.56960000000004</v>
@@ -9410,7 +9410,7 @@
         <v>74</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>963</v>
+        <v>372</v>
       </c>
       <c r="J186" s="0">
         <v>549.74869999999999</v>
@@ -9442,7 +9442,7 @@
         <v>75</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>964</v>
+        <v>373</v>
       </c>
       <c r="J187" s="0">
         <v>530.14729999999997</v>
@@ -9474,7 +9474,7 @@
         <v>76</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>965</v>
+        <v>374</v>
       </c>
       <c r="J188" s="0">
         <v>489.4966</v>
@@ -9506,7 +9506,7 @@
         <v>77</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>966</v>
+        <v>375</v>
       </c>
       <c r="J189" s="0">
         <v>482.49549999999999</v>
@@ -9538,7 +9538,7 @@
         <v>78</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>967</v>
+        <v>376</v>
       </c>
       <c r="J190" s="0">
         <v>378.9196</v>
@@ -9570,7 +9570,7 @@
         <v>79</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>968</v>
+        <v>377</v>
       </c>
       <c r="J191" s="0">
         <v>366.15300000000002</v>
@@ -9602,7 +9602,7 @@
         <v>80</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>969</v>
+        <v>378</v>
       </c>
       <c r="J192" s="0">
         <v>340.57749999999999</v>
@@ -9634,7 +9634,7 @@
         <v>185</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>970</v>
+        <v>380</v>
       </c>
       <c r="J193" s="0">
         <v>4307.7025999999996</v>
@@ -9666,7 +9666,7 @@
         <v>186</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>971</v>
+        <v>381</v>
       </c>
       <c r="J194" s="0">
         <v>1837.0477000000001</v>
@@ -9698,7 +9698,7 @@
         <v>187</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>972</v>
+        <v>382</v>
       </c>
       <c r="J195" s="0">
         <v>616.08360000000005</v>
@@ -9730,7 +9730,7 @@
         <v>188</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>973</v>
+        <v>383</v>
       </c>
       <c r="J196" s="0">
         <v>552.42719999999997</v>
@@ -9762,7 +9762,7 @@
         <v>189</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>974</v>
+        <v>384</v>
       </c>
       <c r="J197" s="0">
         <v>399.44740000000002</v>
@@ -9794,7 +9794,7 @@
         <v>190</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>975</v>
+        <v>385</v>
       </c>
       <c r="J198" s="0">
         <v>377.98289999999997</v>
@@ -9826,7 +9826,7 @@
         <v>191</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>976</v>
+        <v>386</v>
       </c>
       <c r="J199" s="0">
         <v>376.71690000000001</v>
@@ -9858,7 +9858,7 @@
         <v>192</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>977</v>
+        <v>387</v>
       </c>
       <c r="J200" s="0">
         <v>375.52019999999999</v>
@@ -9890,7 +9890,7 @@
         <v>193</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>978</v>
+        <v>388</v>
       </c>
       <c r="J201" s="0">
         <v>370.8648</v>
@@ -9922,7 +9922,7 @@
         <v>194</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>979</v>
+        <v>389</v>
       </c>
       <c r="J202" s="0">
         <v>342.89479999999998</v>
@@ -9954,7 +9954,7 @@
         <v>195</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>980</v>
+        <v>390</v>
       </c>
       <c r="J203" s="0">
         <v>307.26029999999997</v>
@@ -9986,7 +9986,7 @@
         <v>196</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>981</v>
+        <v>391</v>
       </c>
       <c r="J204" s="0">
         <v>261.58179999999999</v>
@@ -10018,7 +10018,7 @@
         <v>82</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>982</v>
+        <v>392</v>
       </c>
       <c r="J205" s="0">
         <v>10466.208000000001</v>
@@ -10050,7 +10050,7 @@
         <v>83</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>983</v>
+        <v>393</v>
       </c>
       <c r="J206" s="0">
         <v>7328.0029000000004</v>
@@ -10082,7 +10082,7 @@
         <v>84</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>984</v>
+        <v>394</v>
       </c>
       <c r="J207" s="0">
         <v>1015.5606</v>
@@ -10114,7 +10114,7 @@
         <v>85</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>985</v>
+        <v>395</v>
       </c>
       <c r="J208" s="0">
         <v>908.67830000000004</v>
@@ -10146,7 +10146,7 @@
         <v>86</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>986</v>
+        <v>396</v>
       </c>
       <c r="J209" s="0">
         <v>520.97770000000003</v>
@@ -10178,7 +10178,7 @@
         <v>87</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>987</v>
+        <v>397</v>
       </c>
       <c r="J210" s="0">
         <v>488.97149999999999</v>
@@ -10210,7 +10210,7 @@
         <v>88</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>988</v>
+        <v>398</v>
       </c>
       <c r="J211" s="0">
         <v>484.75029999999998</v>
@@ -10242,7 +10242,7 @@
         <v>89</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>989</v>
+        <v>399</v>
       </c>
       <c r="J212" s="0">
         <v>438.36930000000001</v>
@@ -10274,7 +10274,7 @@
         <v>90</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>990</v>
+        <v>400</v>
       </c>
       <c r="J213" s="0">
         <v>369.10219999999998</v>
@@ -10306,7 +10306,7 @@
         <v>91</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>991</v>
+        <v>401</v>
       </c>
       <c r="J214" s="0">
         <v>342.30680000000001</v>
@@ -10338,7 +10338,7 @@
         <v>92</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>992</v>
+        <v>402</v>
       </c>
       <c r="J215" s="0">
         <v>280.75409999999999</v>
@@ -10370,7 +10370,7 @@
         <v>93</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>993</v>
+        <v>403</v>
       </c>
       <c r="J216" s="0">
         <v>270.84679999999997</v>
@@ -10402,7 +10402,7 @@
         <v>94</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>994</v>
+        <v>404</v>
       </c>
       <c r="J217" s="0">
         <v>8934.2567999999992</v>
@@ -10434,7 +10434,7 @@
         <v>95</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>995</v>
+        <v>405</v>
       </c>
       <c r="J218" s="0">
         <v>7192.2339000000002</v>
@@ -10466,7 +10466,7 @@
         <v>99</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>996</v>
+        <v>409</v>
       </c>
       <c r="J219" s="0">
         <v>489.01900000000001</v>
@@ -10498,7 +10498,7 @@
         <v>100</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>997</v>
+        <v>410</v>
       </c>
       <c r="J220" s="0">
         <v>486.78719999999999</v>
@@ -10530,7 +10530,7 @@
         <v>101</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>998</v>
+        <v>411</v>
       </c>
       <c r="J221" s="0">
         <v>478.59969999999999</v>
@@ -10562,7 +10562,7 @@
         <v>102</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>999</v>
+        <v>412</v>
       </c>
       <c r="J222" s="0">
         <v>456.38220000000001</v>
@@ -10594,7 +10594,7 @@
         <v>103</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>1000</v>
+        <v>413</v>
       </c>
       <c r="J223" s="0">
         <v>361.197</v>
@@ -10626,7 +10626,7 @@
         <v>104</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>1001</v>
+        <v>414</v>
       </c>
       <c r="J224" s="0">
         <v>350.10750000000002</v>
@@ -10658,7 +10658,7 @@
         <v>105</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>1002</v>
+        <v>415</v>
       </c>
       <c r="J225" s="0">
         <v>332.8802</v>
@@ -10690,7 +10690,7 @@
         <v>106</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>1003</v>
+        <v>416</v>
       </c>
       <c r="J226" s="0">
         <v>9850.5967000000001</v>
@@ -10722,7 +10722,7 @@
         <v>107</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>1004</v>
+        <v>417</v>
       </c>
       <c r="J227" s="0">
         <v>8299.1229999999996</v>
@@ -10754,7 +10754,7 @@
         <v>108</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>1005</v>
+        <v>418</v>
       </c>
       <c r="J228" s="0">
         <v>1061.2550000000001</v>
@@ -10786,7 +10786,7 @@
         <v>61</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>1006</v>
+        <v>419</v>
       </c>
       <c r="J229" s="0">
         <v>863.95190000000002</v>
@@ -10818,7 +10818,7 @@
         <v>109</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>1007</v>
+        <v>420</v>
       </c>
       <c r="J230" s="0">
         <v>537.24440000000004</v>
@@ -10850,7 +10850,7 @@
         <v>110</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>1008</v>
+        <v>421</v>
       </c>
       <c r="J231" s="0">
         <v>512.39139999999998</v>
@@ -10882,7 +10882,7 @@
         <v>111</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>1009</v>
+        <v>422</v>
       </c>
       <c r="J232" s="0">
         <v>461.678</v>
@@ -10914,7 +10914,7 @@
         <v>112</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>1010</v>
+        <v>423</v>
       </c>
       <c r="J233" s="0">
         <v>446.13510000000002</v>
@@ -10946,7 +10946,7 @@
         <v>113</v>
       </c>
       <c r="I234" s="0" t="s">
-        <v>1011</v>
+        <v>424</v>
       </c>
       <c r="J234" s="0">
         <v>416.1148</v>
@@ -10978,7 +10978,7 @@
         <v>114</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>1012</v>
+        <v>425</v>
       </c>
       <c r="J235" s="0">
         <v>385.80329999999998</v>
@@ -11010,7 +11010,7 @@
         <v>115</v>
       </c>
       <c r="I236" s="0" t="s">
-        <v>1013</v>
+        <v>426</v>
       </c>
       <c r="J236" s="0">
         <v>376.43869999999998</v>
@@ -11042,7 +11042,7 @@
         <v>116</v>
       </c>
       <c r="I237" s="0" t="s">
-        <v>1014</v>
+        <v>427</v>
       </c>
       <c r="J237" s="0">
         <v>340.64490000000001</v>
@@ -11074,7 +11074,7 @@
         <v>117</v>
       </c>
       <c r="I238" s="0" t="s">
-        <v>1015</v>
+        <v>428</v>
       </c>
       <c r="J238" s="0">
         <v>9114.7715000000008</v>
@@ -11106,7 +11106,7 @@
         <v>118</v>
       </c>
       <c r="I239" s="0" t="s">
-        <v>1016</v>
+        <v>429</v>
       </c>
       <c r="J239" s="0">
         <v>7656.0316999999996</v>
@@ -11138,7 +11138,7 @@
         <v>121</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>1017</v>
+        <v>432</v>
       </c>
       <c r="J240" s="0">
         <v>542.5788</v>
@@ -11170,7 +11170,7 @@
         <v>122</v>
       </c>
       <c r="I241" s="0" t="s">
-        <v>1018</v>
+        <v>433</v>
       </c>
       <c r="J241" s="0">
         <v>534.76580000000001</v>
@@ -11202,7 +11202,7 @@
         <v>123</v>
       </c>
       <c r="I242" s="0" t="s">
-        <v>1019</v>
+        <v>434</v>
       </c>
       <c r="J242" s="0">
         <v>484.83710000000002</v>
@@ -11234,7 +11234,7 @@
         <v>124</v>
       </c>
       <c r="I243" s="0" t="s">
-        <v>1020</v>
+        <v>435</v>
       </c>
       <c r="J243" s="0">
         <v>468.87529999999998</v>
@@ -11266,7 +11266,7 @@
         <v>125</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>1021</v>
+        <v>436</v>
       </c>
       <c r="J244" s="0">
         <v>398.83769999999998</v>
@@ -11298,7 +11298,7 @@
         <v>126</v>
       </c>
       <c r="I245" s="0" t="s">
-        <v>1022</v>
+        <v>437</v>
       </c>
       <c r="J245" s="0">
         <v>337.36939999999999</v>
@@ -11330,7 +11330,7 @@
         <v>127</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>1023</v>
+        <v>438</v>
       </c>
       <c r="J246" s="0">
         <v>311.84429999999998</v>
@@ -11362,7 +11362,7 @@
         <v>128</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>1024</v>
+        <v>439</v>
       </c>
       <c r="J247" s="0">
         <v>245.285</v>
@@ -11394,7 +11394,7 @@
         <v>197</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>1025</v>
+        <v>440</v>
       </c>
       <c r="J248" s="0">
         <v>2887.6174000000001</v>
@@ -11426,7 +11426,7 @@
         <v>198</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>1026</v>
+        <v>441</v>
       </c>
       <c r="J249" s="0">
         <v>2872.1073999999999</v>
@@ -11458,7 +11458,7 @@
         <v>199</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>1027</v>
+        <v>442</v>
       </c>
       <c r="J250" s="0">
         <v>975.3777</v>
@@ -11490,7 +11490,7 @@
         <v>187</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>1028</v>
+        <v>443</v>
       </c>
       <c r="J251" s="0">
         <v>616.08360000000005</v>
@@ -11522,7 +11522,7 @@
         <v>200</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>1029</v>
+        <v>444</v>
       </c>
       <c r="J252" s="0">
         <v>465.53719999999999</v>
@@ -11554,7 +11554,7 @@
         <v>201</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>1030</v>
+        <v>445</v>
       </c>
       <c r="J253" s="0">
         <v>436.18400000000003</v>
@@ -11586,7 +11586,7 @@
         <v>202</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>1031</v>
+        <v>446</v>
       </c>
       <c r="J254" s="0">
         <v>415.78980000000001</v>
@@ -11618,7 +11618,7 @@
         <v>203</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>1032</v>
+        <v>447</v>
       </c>
       <c r="J255" s="0">
         <v>391.16430000000003</v>
@@ -11650,7 +11650,7 @@
         <v>204</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>1033</v>
+        <v>448</v>
       </c>
       <c r="J256" s="0">
         <v>362.91770000000002</v>
@@ -11682,7 +11682,7 @@
         <v>205</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>1034</v>
+        <v>449</v>
       </c>
       <c r="J257" s="0">
         <v>315.58260000000001</v>
@@ -11714,7 +11714,7 @@
         <v>206</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>1035</v>
+        <v>450</v>
       </c>
       <c r="J258" s="0">
         <v>315.33229999999998</v>
@@ -11746,7 +11746,7 @@
         <v>207</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>1036</v>
+        <v>451</v>
       </c>
       <c r="J259" s="0">
         <v>254.02879999999999</v>
@@ -11778,7 +11778,7 @@
         <v>507</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>1037</v>
+        <v>727</v>
       </c>
       <c r="J260" s="0">
         <v>10897.75</v>
@@ -11810,7 +11810,7 @@
         <v>508</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>1038</v>
+        <v>728</v>
       </c>
       <c r="J261" s="0">
         <v>5963.8306000000002</v>
@@ -11842,7 +11842,7 @@
         <v>509</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>1039</v>
+        <v>729</v>
       </c>
       <c r="J262" s="0">
         <v>1364.115</v>
@@ -11874,7 +11874,7 @@
         <v>510</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>1040</v>
+        <v>730</v>
       </c>
       <c r="J263" s="0">
         <v>1002.6719000000001</v>
@@ -11906,7 +11906,7 @@
         <v>511</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>1041</v>
+        <v>731</v>
       </c>
       <c r="J264" s="0">
         <v>557.97879999999998</v>
@@ -11938,7 +11938,7 @@
         <v>512</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>1042</v>
+        <v>732</v>
       </c>
       <c r="J265" s="0">
         <v>511.4341</v>
@@ -11970,7 +11970,7 @@
         <v>513</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>1043</v>
+        <v>733</v>
       </c>
       <c r="J266" s="0">
         <v>485.53699999999998</v>
@@ -12002,7 +12002,7 @@
         <v>514</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>1044</v>
+        <v>734</v>
       </c>
       <c r="J267" s="0">
         <v>456.29579999999999</v>
@@ -12034,7 +12034,7 @@
         <v>515</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>1045</v>
+        <v>735</v>
       </c>
       <c r="J268" s="0">
         <v>403.62130000000002</v>
@@ -12066,7 +12066,7 @@
         <v>516</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>1046</v>
+        <v>736</v>
       </c>
       <c r="J269" s="0">
         <v>384.92849999999999</v>
@@ -12098,7 +12098,7 @@
         <v>517</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>1047</v>
+        <v>737</v>
       </c>
       <c r="J270" s="0">
         <v>345.9332</v>
@@ -12130,7 +12130,7 @@
         <v>518</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>1048</v>
+        <v>738</v>
       </c>
       <c r="J271" s="0">
         <v>329.33870000000002</v>
@@ -12162,7 +12162,7 @@
         <v>519</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>1049</v>
+        <v>739</v>
       </c>
       <c r="J272" s="0">
         <v>9494.3554999999997</v>
@@ -12194,7 +12194,7 @@
         <v>520</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>1050</v>
+        <v>740</v>
       </c>
       <c r="J273" s="0">
         <v>6959.3242</v>
@@ -12226,7 +12226,7 @@
         <v>523</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>1051</v>
+        <v>743</v>
       </c>
       <c r="J274" s="0">
         <v>528.32619999999997</v>
@@ -12258,7 +12258,7 @@
         <v>524</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>1052</v>
+        <v>744</v>
       </c>
       <c r="J275" s="0">
         <v>502.16129999999998</v>
@@ -12290,7 +12290,7 @@
         <v>525</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>1053</v>
+        <v>745</v>
       </c>
       <c r="J276" s="0">
         <v>468.14839999999998</v>
@@ -12322,7 +12322,7 @@
         <v>526</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>1054</v>
+        <v>746</v>
       </c>
       <c r="J277" s="0">
         <v>413.35890000000001</v>
@@ -12354,7 +12354,7 @@
         <v>527</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>1055</v>
+        <v>747</v>
       </c>
       <c r="J278" s="0">
         <v>410.47199999999998</v>
@@ -12386,7 +12386,7 @@
         <v>528</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>1056</v>
+        <v>748</v>
       </c>
       <c r="J279" s="0">
         <v>371.8809</v>
@@ -12418,7 +12418,7 @@
         <v>529</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>1057</v>
+        <v>749</v>
       </c>
       <c r="J280" s="0">
         <v>347.0478</v>
@@ -12450,7 +12450,7 @@
         <v>530</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>1058</v>
+        <v>750</v>
       </c>
       <c r="J281" s="0">
         <v>302.97559999999999</v>
@@ -12482,7 +12482,7 @@
         <v>531</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>1059</v>
+        <v>751</v>
       </c>
       <c r="J282" s="0">
         <v>8923.2001999999993</v>
@@ -12514,7 +12514,7 @@
         <v>532</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>1060</v>
+        <v>752</v>
       </c>
       <c r="J283" s="0">
         <v>7434.9364999999998</v>
@@ -12546,7 +12546,7 @@
         <v>533</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>1061</v>
+        <v>753</v>
       </c>
       <c r="J284" s="0">
         <v>1198.5989</v>
@@ -12578,7 +12578,7 @@
         <v>534</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>1062</v>
+        <v>754</v>
       </c>
       <c r="J285" s="0">
         <v>1016.6576</v>
@@ -12610,7 +12610,7 @@
         <v>543</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>1063</v>
+        <v>755</v>
       </c>
       <c r="J286" s="0">
         <v>10363.415999999999</v>
@@ -12642,7 +12642,7 @@
         <v>544</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>1064</v>
+        <v>756</v>
       </c>
       <c r="J287" s="0">
         <v>8731.0702999999994</v>
@@ -12674,7 +12674,7 @@
         <v>547</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>1065</v>
+        <v>759</v>
       </c>
       <c r="J288" s="0">
         <v>509.65910000000002</v>
@@ -12706,7 +12706,7 @@
         <v>64</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>1066</v>
+        <v>760</v>
       </c>
       <c r="J289" s="0">
         <v>497.6062</v>
@@ -12738,7 +12738,7 @@
         <v>548</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>1067</v>
+        <v>761</v>
       </c>
       <c r="J290" s="0">
         <v>473.81920000000002</v>
@@ -12770,7 +12770,7 @@
         <v>549</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>1068</v>
+        <v>762</v>
       </c>
       <c r="J291" s="0">
         <v>386.12639999999999</v>
@@ -12802,7 +12802,7 @@
         <v>550</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>1069</v>
+        <v>763</v>
       </c>
       <c r="J292" s="0">
         <v>381.40570000000002</v>
@@ -12834,7 +12834,7 @@
         <v>551</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>1070</v>
+        <v>764</v>
       </c>
       <c r="J293" s="0">
         <v>371.59660000000002</v>
@@ -12866,7 +12866,7 @@
         <v>552</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>1071</v>
+        <v>765</v>
       </c>
       <c r="J294" s="0">
         <v>364.02569999999997</v>
@@ -12898,7 +12898,7 @@
         <v>553</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>1072</v>
+        <v>766</v>
       </c>
       <c r="J295" s="0">
         <v>331.7552</v>
@@ -12930,7 +12930,7 @@
         <v>554</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>1073</v>
+        <v>767</v>
       </c>
       <c r="J296" s="0">
         <v>1621.762</v>
@@ -12962,7 +12962,7 @@
         <v>555</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>1074</v>
+        <v>768</v>
       </c>
       <c r="J297" s="0">
         <v>1023.5883</v>
@@ -12994,7 +12994,7 @@
         <v>556</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>1075</v>
+        <v>769</v>
       </c>
       <c r="J298" s="0">
         <v>634.67409999999995</v>
@@ -13026,7 +13026,7 @@
         <v>557</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>1076</v>
+        <v>770</v>
       </c>
       <c r="J299" s="0">
         <v>589.45230000000004</v>
@@ -13058,7 +13058,7 @@
         <v>558</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>1077</v>
+        <v>771</v>
       </c>
       <c r="J300" s="0">
         <v>441.32260000000002</v>
@@ -13090,7 +13090,7 @@
         <v>559</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>1078</v>
+        <v>772</v>
       </c>
       <c r="J301" s="0">
         <v>406.00639999999999</v>
@@ -13122,7 +13122,7 @@
         <v>560</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>1079</v>
+        <v>773</v>
       </c>
       <c r="J302" s="0">
         <v>404.98939999999999</v>
@@ -13154,7 +13154,7 @@
         <v>561</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>1080</v>
+        <v>774</v>
       </c>
       <c r="J303" s="0">
         <v>356.87450000000001</v>
@@ -13186,7 +13186,7 @@
         <v>562</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>1081</v>
+        <v>775</v>
       </c>
       <c r="J304" s="0">
         <v>326.86750000000001</v>
@@ -13218,7 +13218,7 @@
         <v>563</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>1082</v>
+        <v>776</v>
       </c>
       <c r="J305" s="0">
         <v>313.15320000000003</v>
@@ -13250,7 +13250,7 @@
         <v>564</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>1083</v>
+        <v>777</v>
       </c>
       <c r="J306" s="0">
         <v>302.25330000000002</v>
@@ -13282,7 +13282,7 @@
         <v>565</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>1084</v>
+        <v>778</v>
       </c>
       <c r="J307" s="0">
         <v>241.7327</v>
@@ -13314,7 +13314,7 @@
         <v>129</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>1085</v>
+        <v>452</v>
       </c>
       <c r="J308" s="0">
         <v>8389.2909999999993</v>
@@ -13346,7 +13346,7 @@
         <v>130</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>1086</v>
+        <v>453</v>
       </c>
       <c r="J309" s="0">
         <v>8068.0429999999997</v>
@@ -13378,7 +13378,7 @@
         <v>208</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>1087</v>
+        <v>454</v>
       </c>
       <c r="J310" s="0">
         <v>1304.9119000000001</v>
@@ -13410,7 +13410,7 @@
         <v>133</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>1088</v>
+        <v>456</v>
       </c>
       <c r="J311" s="0">
         <v>528.16520000000003</v>
@@ -13442,7 +13442,7 @@
         <v>134</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>1089</v>
+        <v>457</v>
       </c>
       <c r="J312" s="0">
         <v>464.43889999999999</v>
@@ -13474,7 +13474,7 @@
         <v>135</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>1090</v>
+        <v>458</v>
       </c>
       <c r="J313" s="0">
         <v>449.87619999999998</v>
@@ -13506,7 +13506,7 @@
         <v>136</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>1091</v>
+        <v>459</v>
       </c>
       <c r="J314" s="0">
         <v>447.66699999999997</v>
@@ -13538,7 +13538,7 @@
         <v>137</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>1092</v>
+        <v>460</v>
       </c>
       <c r="J315" s="0">
         <v>391.69869999999997</v>
@@ -13570,7 +13570,7 @@
         <v>138</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>1093</v>
+        <v>461</v>
       </c>
       <c r="J316" s="0">
         <v>372.4153</v>
@@ -13602,7 +13602,7 @@
         <v>139</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>1094</v>
+        <v>462</v>
       </c>
       <c r="J317" s="0">
         <v>366.97289999999998</v>
@@ -13634,7 +13634,7 @@
         <v>140</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>1095</v>
+        <v>463</v>
       </c>
       <c r="J318" s="0">
         <v>329.11259999999999</v>
@@ -13666,7 +13666,7 @@
         <v>58</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>1096</v>
+        <v>464</v>
       </c>
       <c r="J319" s="0">
         <v>9741.5614999999998</v>
@@ -13698,7 +13698,7 @@
         <v>59</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>1097</v>
+        <v>465</v>
       </c>
       <c r="J320" s="0">
         <v>8198.8974999999991</v>
@@ -13730,7 +13730,7 @@
         <v>60</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>1098</v>
+        <v>466</v>
       </c>
       <c r="J321" s="0">
         <v>1259.1116</v>
@@ -13762,7 +13762,7 @@
         <v>210</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>1099</v>
+        <v>467</v>
       </c>
       <c r="J322" s="0">
         <v>964.0145</v>
@@ -13794,7 +13794,7 @@
         <v>141</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>1100</v>
+        <v>468</v>
       </c>
       <c r="J323" s="0">
         <v>539.45429999999999</v>
@@ -13826,7 +13826,7 @@
         <v>142</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>1101</v>
+        <v>469</v>
       </c>
       <c r="J324" s="0">
         <v>485.64830000000001</v>
@@ -13858,7 +13858,7 @@
         <v>143</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>1102</v>
+        <v>470</v>
       </c>
       <c r="J325" s="0">
         <v>457.39609999999999</v>
@@ -13890,7 +13890,7 @@
         <v>144</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>1103</v>
+        <v>471</v>
       </c>
       <c r="J326" s="0">
         <v>454.66460000000001</v>
@@ -13922,7 +13922,7 @@
         <v>145</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>1104</v>
+        <v>472</v>
       </c>
       <c r="J327" s="0">
         <v>368.51979999999998</v>
@@ -13954,7 +13954,7 @@
         <v>146</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>1105</v>
+        <v>473</v>
       </c>
       <c r="J328" s="0">
         <v>342.74220000000003</v>
@@ -13986,7 +13986,7 @@
         <v>147</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>1106</v>
+        <v>474</v>
       </c>
       <c r="J329" s="0">
         <v>302.46800000000002</v>
@@ -14018,7 +14018,7 @@
         <v>148</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>1107</v>
+        <v>475</v>
       </c>
       <c r="J330" s="0">
         <v>300.47250000000003</v>
@@ -14050,7 +14050,7 @@
         <v>149</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>1108</v>
+        <v>476</v>
       </c>
       <c r="J331" s="0">
         <v>10892.9414</v>
@@ -14082,7 +14082,7 @@
         <v>150</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>1109</v>
+        <v>477</v>
       </c>
       <c r="J332" s="0">
         <v>5918.6806999999999</v>
@@ -14114,7 +14114,7 @@
         <v>152</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>1110</v>
+        <v>479</v>
       </c>
       <c r="J333" s="0">
         <v>726.14110000000005</v>
@@ -14146,7 +14146,7 @@
         <v>153</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>1111</v>
+        <v>480</v>
       </c>
       <c r="J334" s="0">
         <v>498.3132</v>
@@ -14178,7 +14178,7 @@
         <v>154</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>1112</v>
+        <v>481</v>
       </c>
       <c r="J335" s="0">
         <v>487.10520000000002</v>
@@ -14210,7 +14210,7 @@
         <v>155</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>1113</v>
+        <v>482</v>
       </c>
       <c r="J336" s="0">
         <v>485.66770000000002</v>
@@ -14242,7 +14242,7 @@
         <v>156</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>1114</v>
+        <v>483</v>
       </c>
       <c r="J337" s="0">
         <v>478.11529999999999</v>
@@ -14274,7 +14274,7 @@
         <v>157</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>1115</v>
+        <v>484</v>
       </c>
       <c r="J338" s="0">
         <v>375.48970000000003</v>
@@ -14306,7 +14306,7 @@
         <v>158</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>1116</v>
+        <v>485</v>
       </c>
       <c r="J339" s="0">
         <v>359.0838</v>
@@ -14338,7 +14338,7 @@
         <v>159</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>1117</v>
+        <v>486</v>
       </c>
       <c r="J340" s="0">
         <v>338.9837</v>
@@ -14370,7 +14370,7 @@
         <v>160</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>1118</v>
+        <v>487</v>
       </c>
       <c r="J341" s="0">
         <v>293.55579999999998</v>
@@ -14402,7 +14402,7 @@
         <v>161</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>1119</v>
+        <v>488</v>
       </c>
       <c r="J342" s="0">
         <v>9826.1103999999996</v>
@@ -14434,7 +14434,7 @@
         <v>162</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>1120</v>
+        <v>489</v>
       </c>
       <c r="J343" s="0">
         <v>7957.9004000000004</v>
@@ -14466,7 +14466,7 @@
         <v>163</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>1121</v>
+        <v>490</v>
       </c>
       <c r="J344" s="0">
         <v>1958.7829999999999</v>
@@ -14498,7 +14498,7 @@
         <v>165</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>1122</v>
+        <v>492</v>
       </c>
       <c r="J345" s="0">
         <v>574.80640000000005</v>
@@ -14530,7 +14530,7 @@
         <v>166</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>1123</v>
+        <v>493</v>
       </c>
       <c r="J346" s="0">
         <v>532.89999999999998</v>
@@ -14562,7 +14562,7 @@
         <v>167</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>1124</v>
+        <v>494</v>
       </c>
       <c r="J347" s="0">
         <v>470.99040000000002</v>
@@ -14594,7 +14594,7 @@
         <v>168</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>1125</v>
+        <v>495</v>
       </c>
       <c r="J348" s="0">
         <v>428.05349999999999</v>
@@ -14626,7 +14626,7 @@
         <v>169</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>1126</v>
+        <v>496</v>
       </c>
       <c r="J349" s="0">
         <v>370.83409999999998</v>
@@ -14658,7 +14658,7 @@
         <v>170</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>1127</v>
+        <v>497</v>
       </c>
       <c r="J350" s="0">
         <v>361.65289999999999</v>
@@ -14690,7 +14690,7 @@
         <v>171</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>1128</v>
+        <v>498</v>
       </c>
       <c r="J351" s="0">
         <v>328.18830000000003</v>
@@ -14722,7 +14722,7 @@
         <v>172</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>1129</v>
+        <v>499</v>
       </c>
       <c r="J352" s="0">
         <v>313.28399999999999</v>

--- a/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="199754" uniqueCount="1130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="212430" uniqueCount="1130">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="212430" uniqueCount="1130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="215599" uniqueCount="1130">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="215599" uniqueCount="1130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="218768" uniqueCount="1130">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="218768" uniqueCount="1130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="225106" uniqueCount="1130">
   <si>
     <t>Year</t>
   </si>

--- a/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="225106" uniqueCount="1130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="253627" uniqueCount="1130">
   <si>
     <t>Year</t>
   </si>
@@ -3452,16 +3452,16 @@
   <dimension ref="A1:J397"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" customWidth="true"/>
-    <col min="2" max="2" width="6.54296875" customWidth="true"/>
-    <col min="3" max="3" width="10.36328125" customWidth="true"/>
-    <col min="4" max="4" width="16.36328125" customWidth="true"/>
-    <col min="5" max="5" width="11.81640625" customWidth="true"/>
-    <col min="6" max="6" width="11.90625" customWidth="true"/>
-    <col min="7" max="7" width="7.90625" customWidth="true"/>
-    <col min="8" max="8" width="36.26953125" customWidth="true"/>
-    <col min="9" max="9" width="167.54296875" customWidth="true"/>
-    <col min="10" max="10" width="10.453125" customWidth="true"/>
+    <col min="1" max="1" width="14.85546875" customWidth="true"/>
+    <col min="2" max="2" width="7" customWidth="true"/>
+    <col min="3" max="3" width="11.28515625" customWidth="true"/>
+    <col min="4" max="4" width="17.28515625" customWidth="true"/>
+    <col min="5" max="5" width="12.7109375" customWidth="true"/>
+    <col min="6" max="6" width="13" customWidth="true"/>
+    <col min="7" max="7" width="8.5703125" customWidth="true"/>
+    <col min="8" max="8" width="37.42578125" customWidth="true"/>
+    <col min="9" max="9" width="175.42578125" customWidth="true"/>
+    <col min="10" max="10" width="10.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
+++ b/OrganizedData/2025_organized/Classified_Max_Force_Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="253627" uniqueCount="1130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="266303" uniqueCount="1130">
   <si>
     <t>Year</t>
   </si>
@@ -3460,7 +3460,7 @@
     <col min="6" max="6" width="13" customWidth="true"/>
     <col min="7" max="7" width="8.5703125" customWidth="true"/>
     <col min="8" max="8" width="37.42578125" customWidth="true"/>
-    <col min="9" max="9" width="175.42578125" customWidth="true"/>
+    <col min="9" max="9" width="147" customWidth="true"/>
     <col min="10" max="10" width="10.7109375" customWidth="true"/>
   </cols>
   <sheetData>
@@ -3522,7 +3522,7 @@
         <v>46</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>212</v>
+        <v>779</v>
       </c>
       <c r="J2" s="0">
         <v>13088.609399999999</v>
@@ -3554,7 +3554,7 @@
         <v>47</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>213</v>
+        <v>780</v>
       </c>
       <c r="J3" s="0">
         <v>9104.8721000000005</v>
@@ -3586,7 +3586,7 @@
         <v>48</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>214</v>
+        <v>781</v>
       </c>
       <c r="J4" s="0">
         <v>1438.8326</v>
@@ -3618,7 +3618,7 @@
         <v>49</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>215</v>
+        <v>782</v>
       </c>
       <c r="J5" s="0">
         <v>1210.5242000000001</v>
@@ -3650,7 +3650,7 @@
         <v>50</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>216</v>
+        <v>783</v>
       </c>
       <c r="J6" s="0">
         <v>542.07240000000002</v>
@@ -3682,7 +3682,7 @@
         <v>51</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>217</v>
+        <v>784</v>
       </c>
       <c r="J7" s="0">
         <v>528.39120000000003</v>
@@ -3714,7 +3714,7 @@
         <v>52</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>218</v>
+        <v>785</v>
       </c>
       <c r="J8" s="0">
         <v>519.83349999999996</v>
@@ -3746,7 +3746,7 @@
         <v>53</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>219</v>
+        <v>786</v>
       </c>
       <c r="J9" s="0">
         <v>465.38400000000001</v>
@@ -3778,7 +3778,7 @@
         <v>54</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>220</v>
+        <v>787</v>
       </c>
       <c r="J10" s="0">
         <v>387.42579999999998</v>
@@ -3810,7 +3810,7 @@
         <v>55</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>221</v>
+        <v>788</v>
       </c>
       <c r="J11" s="0">
         <v>376.01639999999998</v>
@@ -3842,7 +3842,7 @@
         <v>56</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>222</v>
+        <v>789</v>
       </c>
       <c r="J12" s="0">
         <v>367.9187</v>
@@ -3874,7 +3874,7 @@
         <v>57</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>223</v>
+        <v>790</v>
       </c>
       <c r="J13" s="0">
         <v>345.6712</v>
@@ -3906,7 +3906,7 @@
         <v>58</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>224</v>
+        <v>791</v>
       </c>
       <c r="J14" s="0">
         <v>9741.5614999999998</v>
@@ -3938,7 +3938,7 @@
         <v>59</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>225</v>
+        <v>792</v>
       </c>
       <c r="J15" s="0">
         <v>8198.8974999999991</v>
@@ -3970,7 +3970,7 @@
         <v>60</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>226</v>
+        <v>793</v>
       </c>
       <c r="J16" s="0">
         <v>1259.1116</v>
@@ -4002,7 +4002,7 @@
         <v>61</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>227</v>
+        <v>794</v>
       </c>
       <c r="J17" s="0">
         <v>863.95190000000002</v>
@@ -4034,7 +4034,7 @@
         <v>62</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>228</v>
+        <v>795</v>
       </c>
       <c r="J18" s="0">
         <v>574.15189999999996</v>
@@ -4066,7 +4066,7 @@
         <v>63</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>229</v>
+        <v>796</v>
       </c>
       <c r="J19" s="0">
         <v>514.2156</v>
@@ -4098,7 +4098,7 @@
         <v>64</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>230</v>
+        <v>797</v>
       </c>
       <c r="J20" s="0">
         <v>497.6062</v>
@@ -4130,7 +4130,7 @@
         <v>65</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>231</v>
+        <v>798</v>
       </c>
       <c r="J21" s="0">
         <v>496.00400000000002</v>
@@ -4162,7 +4162,7 @@
         <v>66</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>232</v>
+        <v>799</v>
       </c>
       <c r="J22" s="0">
         <v>389.9522</v>
@@ -4194,7 +4194,7 @@
         <v>67</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>233</v>
+        <v>800</v>
       </c>
       <c r="J23" s="0">
         <v>332.78969999999998</v>
@@ -4226,7 +4226,7 @@
         <v>68</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>234</v>
+        <v>801</v>
       </c>
       <c r="J24" s="0">
         <v>320.5446</v>
@@ -4258,7 +4258,7 @@
         <v>69</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>235</v>
+        <v>802</v>
       </c>
       <c r="J25" s="0">
         <v>288.99189999999999</v>
@@ -4290,7 +4290,7 @@
         <v>71</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>237</v>
+        <v>803</v>
       </c>
       <c r="J26" s="0">
         <v>5932.7479999999996</v>
@@ -4322,7 +4322,7 @@
         <v>72</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>238</v>
+        <v>804</v>
       </c>
       <c r="J27" s="0">
         <v>901.9991</v>
@@ -4354,7 +4354,7 @@
         <v>73</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>239</v>
+        <v>805</v>
       </c>
       <c r="J28" s="0">
         <v>893.56960000000004</v>
@@ -4386,7 +4386,7 @@
         <v>74</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>240</v>
+        <v>806</v>
       </c>
       <c r="J29" s="0">
         <v>549.74869999999999</v>
@@ -4418,7 +4418,7 @@
         <v>75</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>241</v>
+        <v>807</v>
       </c>
       <c r="J30" s="0">
         <v>530.14729999999997</v>
@@ -4450,7 +4450,7 @@
         <v>76</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>242</v>
+        <v>808</v>
       </c>
       <c r="J31" s="0">
         <v>489.4966</v>
@@ -4482,7 +4482,7 @@
         <v>77</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>243</v>
+        <v>809</v>
       </c>
       <c r="J32" s="0">
         <v>482.49549999999999</v>
@@ -4514,7 +4514,7 @@
         <v>78</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>244</v>
+        <v>810</v>
       </c>
       <c r="J33" s="0">
         <v>378.9196</v>
@@ -4546,7 +4546,7 @@
         <v>79</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>245</v>
+        <v>811</v>
       </c>
       <c r="J34" s="0">
         <v>366.15300000000002</v>
@@ -4578,7 +4578,7 @@
         <v>80</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>246</v>
+        <v>812</v>
       </c>
       <c r="J35" s="0">
         <v>340.57749999999999</v>
@@ -4610,7 +4610,7 @@
         <v>82</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>248</v>
+        <v>813</v>
       </c>
       <c r="J36" s="0">
         <v>10466.208000000001</v>
@@ -4642,7 +4642,7 @@
         <v>83</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>249</v>
+        <v>814</v>
       </c>
       <c r="J37" s="0">
         <v>7328.0029000000004</v>
@@ -4674,7 +4674,7 @@
         <v>84</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>250</v>
+        <v>815</v>
       </c>
       <c r="J38" s="0">
         <v>1015.5606</v>
@@ -4706,7 +4706,7 @@
         <v>85</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>251</v>
+        <v>816</v>
       </c>
       <c r="J39" s="0">
         <v>908.67830000000004</v>
@@ -4738,7 +4738,7 @@
         <v>86</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>252</v>
+        <v>817</v>
       </c>
       <c r="J40" s="0">
         <v>520.97770000000003</v>
@@ -4770,7 +4770,7 @@
         <v>87</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>253</v>
+        <v>818</v>
       </c>
       <c r="J41" s="0">
         <v>488.97149999999999</v>
@@ -4802,7 +4802,7 @@
         <v>88</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>254</v>
+        <v>819</v>
       </c>
       <c r="J42" s="0">
         <v>484.75029999999998</v>
@@ -4834,7 +4834,7 @@
         <v>89</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>255</v>
+        <v>820</v>
       </c>
       <c r="J43" s="0">
         <v>438.36930000000001</v>
@@ -4866,7 +4866,7 @@
         <v>90</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>256</v>
+        <v>821</v>
       </c>
       <c r="J44" s="0">
         <v>369.10219999999998</v>
@@ -4898,7 +4898,7 @@
         <v>91</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>257</v>
+        <v>822</v>
       </c>
       <c r="J45" s="0">
         <v>342.30680000000001</v>
@@ -4930,7 +4930,7 @@
         <v>92</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>258</v>
+        <v>823</v>
       </c>
       <c r="J46" s="0">
         <v>280.75409999999999</v>
@@ -4962,7 +4962,7 @@
         <v>93</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>259</v>
+        <v>824</v>
       </c>
       <c r="J47" s="0">
         <v>270.84679999999997</v>
@@ -4994,7 +4994,7 @@
         <v>94</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>260</v>
+        <v>825</v>
       </c>
       <c r="J48" s="0">
         <v>8934.2567999999992</v>
@@ -5026,7 +5026,7 @@
         <v>95</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>261</v>
+        <v>826</v>
       </c>
       <c r="J49" s="0">
         <v>7192.2339000000002</v>
@@ -5058,7 +5058,7 @@
         <v>97</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>263</v>
+        <v>827</v>
       </c>
       <c r="J50" s="0">
         <v>892.98720000000003</v>
@@ -5090,7 +5090,7 @@
         <v>99</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>265</v>
+        <v>828</v>
       </c>
       <c r="J51" s="0">
         <v>489.01900000000001</v>
@@ -5122,7 +5122,7 @@
         <v>100</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>266</v>
+        <v>829</v>
       </c>
       <c r="J52" s="0">
         <v>486.78719999999999</v>
@@ -5154,7 +5154,7 @@
         <v>101</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>267</v>
+        <v>830</v>
       </c>
       <c r="J53" s="0">
         <v>478.59969999999999</v>
@@ -5186,7 +5186,7 @@
         <v>102</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>268</v>
+        <v>831</v>
       </c>
       <c r="J54" s="0">
         <v>456.38220000000001</v>
@@ -5218,7 +5218,7 @@
         <v>103</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>269</v>
+        <v>832</v>
       </c>
       <c r="J55" s="0">
         <v>361.197</v>
@@ -5250,7 +5250,7 @@
         <v>104</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>270</v>
+        <v>833</v>
       </c>
       <c r="J56" s="0">
         <v>350.10750000000002</v>
@@ -5282,7 +5282,7 @@
         <v>105</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>271</v>
+        <v>834</v>
       </c>
       <c r="J57" s="0">
         <v>332.8802</v>
@@ -5314,7 +5314,7 @@
         <v>106</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>272</v>
+        <v>835</v>
       </c>
       <c r="J58" s="0">
         <v>9850.5967000000001</v>
@@ -5346,7 +5346,7 @@
         <v>107</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>273</v>
+        <v>836</v>
       </c>
       <c r="J59" s="0">
         <v>8299.1229999999996</v>
@@ -5378,7 +5378,7 @@
         <v>108</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>274</v>
+        <v>837</v>
       </c>
       <c r="J60" s="0">
         <v>1061.2550000000001</v>
@@ -5410,7 +5410,7 @@
         <v>61</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>275</v>
+        <v>838</v>
       </c>
       <c r="J61" s="0">
         <v>863.95190000000002</v>
@@ -5442,7 +5442,7 @@
         <v>109</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>276</v>
+        <v>839</v>
       </c>
       <c r="J62" s="0">
         <v>537.24440000000004</v>
@@ -5474,7 +5474,7 @@
         <v>110</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>277</v>
+        <v>840</v>
       </c>
       <c r="J63" s="0">
         <v>512.39139999999998</v>
@@ -5506,7 +5506,7 @@
         <v>111</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>278</v>
+        <v>841</v>
       </c>
       <c r="J64" s="0">
         <v>461.678</v>
@@ -5538,7 +5538,7 @@
         <v>112</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>279</v>
+        <v>842</v>
       </c>
       <c r="J65" s="0">
         <v>446.13510000000002</v>
@@ -5570,7 +5570,7 @@
         <v>113</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>280</v>
+        <v>843</v>
       </c>
       <c r="J66" s="0">
         <v>416.1148</v>
@@ -5602,7 +5602,7 @@
         <v>114</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>281</v>
+        <v>844</v>
       </c>
       <c r="J67" s="0">
         <v>385.80329999999998</v>
@@ -5634,7 +5634,7 @@
         <v>115</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>282</v>
+        <v>845</v>
       </c>
       <c r="J68" s="0">
         <v>376.43869999999998</v>
@@ -5666,7 +5666,7 @@
         <v>116</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>283</v>
+        <v>846</v>
       </c>
       <c r="J69" s="0">
         <v>340.64490000000001</v>
@@ -5698,7 +5698,7 @@
         <v>117</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>284</v>
+        <v>847</v>
       </c>
       <c r="J70" s="0">
         <v>9114.7715000000008</v>
@@ -5730,7 +5730,7 @@
         <v>118</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>285</v>
+        <v>848</v>
       </c>
       <c r="J71" s="0">
         <v>7656.0316999999996</v>
@@ -5762,7 +5762,7 @@
         <v>121</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>288</v>
+        <v>849</v>
       </c>
       <c r="J72" s="0">
         <v>542.5788</v>
@@ -5794,7 +5794,7 @@
         <v>122</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>289</v>
+        <v>850</v>
       </c>
       <c r="J73" s="0">
         <v>534.76580000000001</v>
@@ -5826,7 +5826,7 @@
         <v>123</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>290</v>
+        <v>851</v>
       </c>
       <c r="J74" s="0">
         <v>484.83710000000002</v>
@@ -5858,7 +5858,7 @@
         <v>124</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>291</v>
+        <v>852</v>
       </c>
       <c r="J75" s="0">
         <v>468.87529999999998</v>
@@ -5890,7 +5890,7 @@
         <v>125</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>292</v>
+        <v>853</v>
       </c>
       <c r="J76" s="0">
         <v>398.83769999999998</v>
@@ -5922,7 +5922,7 @@
         <v>126</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>293</v>
+        <v>854</v>
       </c>
       <c r="J77" s="0">
         <v>337.36939999999999</v>
@@ -5954,7 +5954,7 @@
         <v>127</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>294</v>
+        <v>855</v>
       </c>
       <c r="J78" s="0">
         <v>311.84429999999998</v>
@@ -5986,7 +5986,7 @@
         <v>128</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>295</v>
+        <v>856</v>
       </c>
       <c r="J79" s="0">
         <v>245.285</v>
@@ -6018,7 +6018,7 @@
         <v>507</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>679</v>
+        <v>857</v>
       </c>
       <c r="J80" s="0">
         <v>10897.75</v>
@@ -6050,7 +6050,7 @@
         <v>508</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>680</v>
+        <v>858</v>
       </c>
       <c r="J81" s="0">
         <v>5963.8306000000002</v>
@@ -6082,7 +6082,7 @@
         <v>509</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>681</v>
+        <v>859</v>
       </c>
       <c r="J82" s="0">
         <v>1364.115</v>
@@ -6114,7 +6114,7 @@
         <v>510</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>682</v>
+        <v>860</v>
       </c>
       <c r="J83" s="0">
         <v>1002.6719000000001</v>
@@ -6146,7 +6146,7 @@
         <v>511</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>683</v>
+        <v>861</v>
       </c>
       <c r="J84" s="0">
         <v>557.97879999999998</v>
@@ -6178,7 +6178,7 @@
         <v>512</v>
       </c>
       <c r="I85" s="0" t="s">
-        <v>684</v>
+        <v>862</v>
       </c>
       <c r="J85" s="0">
         <v>511.4341</v>
@@ -6210,7 +6210,7 @@
         <v>513</v>
       </c>
       <c r="I86" s="0" t="s">
-        <v>685</v>
+        <v>863</v>
       </c>
       <c r="J86" s="0">
         <v>485.53699999999998</v>
@@ -6242,7 +6242,7 @@
         <v>514</v>
       </c>
       <c r="I87" s="0" t="s">
-        <v>686</v>
+        <v>864</v>
       </c>
       <c r="J87" s="0">
         <v>456.29579999999999</v>
@@ -6274,7 +6274,7 @@
         <v>515</v>
       </c>
       <c r="I88" s="0" t="s">
-        <v>687</v>
+        <v>865</v>
       </c>
       <c r="J88" s="0">
         <v>403.62130000000002</v>
@@ -6306,7 +6306,7 @@
         <v>516</v>
       </c>
       <c r="I89" s="0" t="s">
-        <v>688</v>
+        <v>866</v>
       </c>
       <c r="J89" s="0">
         <v>384.92849999999999</v>
@@ -6338,7 +6338,7 @@
         <v>517</v>
       </c>
       <c r="I90" s="0" t="s">
-        <v>689</v>
+        <v>867</v>
       </c>
       <c r="J90" s="0">
         <v>345.9332</v>
@@ -6370,7 +6370,7 @@
         <v>518</v>
       </c>
       <c r="I91" s="0" t="s">
-        <v>690</v>
+        <v>868</v>
       </c>
       <c r="J91" s="0">
         <v>329.33870000000002</v>
@@ -6402,7 +6402,7 @@
         <v>519</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>691</v>
+        <v>869</v>
       </c>
       <c r="J92" s="0">
         <v>9494.3554999999997</v>
@@ -6434,7 +6434,7 @@
         <v>520</v>
       </c>
       <c r="I93" s="0" t="s">
-        <v>692</v>
+        <v>870</v>
       </c>
       <c r="J93" s="0">
         <v>6959.3242</v>
@@ -6466,7 +6466,7 @@
         <v>523</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>695</v>
+        <v>871</v>
       </c>
       <c r="J94" s="0">
         <v>528.32619999999997</v>
@@ -6498,7 +6498,7 @@
         <v>524</v>
       </c>
       <c r="I95" s="0" t="s">
-        <v>696</v>
+        <v>872</v>
       </c>
       <c r="J95" s="0">
         <v>502.16129999999998</v>
@@ -6530,7 +6530,7 @@
         <v>525</v>
       </c>
       <c r="I96" s="0" t="s">
-        <v>697</v>
+        <v>873</v>
       </c>
       <c r="J96" s="0">
         <v>468.14839999999998</v>
@@ -6562,7 +6562,7 @@
         <v>526</v>
       </c>
       <c r="I97" s="0" t="s">
-        <v>698</v>
+        <v>874</v>
       </c>
       <c r="J97" s="0">
         <v>413.35890000000001</v>
@@ -6594,7 +6594,7 @@
         <v>527</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>699</v>
+        <v>875</v>
       </c>
       <c r="J98" s="0">
         <v>410.47199999999998</v>
@@ -6626,7 +6626,7 @@
         <v>528</v>
       </c>
       <c r="I99" s="0" t="s">
-        <v>700</v>
+        <v>876</v>
       </c>
       <c r="J99" s="0">
         <v>371.8809</v>
@@ -6658,7 +6658,7 @@
         <v>529</v>
       </c>
       <c r="I100" s="0" t="s">
-        <v>701</v>
+        <v>877</v>
       </c>
       <c r="J100" s="0">
         <v>347.0478</v>
@@ -6690,7 +6690,7 @@
         <v>530</v>
       </c>
       <c r="I101" s="0" t="s">
-        <v>702</v>
+        <v>878</v>
       </c>
       <c r="J101" s="0">
         <v>302.97559999999999</v>
@@ -6722,7 +6722,7 @@
         <v>531</v>
       </c>
       <c r="I102" s="0" t="s">
-        <v>703</v>
+        <v>879</v>
       </c>
       <c r="J102" s="0">
         <v>8923.2001999999993</v>
@@ -6754,7 +6754,7 @@
         <v>532</v>
       </c>
       <c r="I103" s="0" t="s">
-        <v>704</v>
+        <v>880</v>
       </c>
       <c r="J103" s="0">
         <v>7434.9364999999998</v>
@@ -6786,7 +6786,7 @@
         <v>533</v>
       </c>
       <c r="I104" s="0" t="s">
-        <v>705</v>
+        <v>881</v>
       </c>
       <c r="J104" s="0">
         <v>1198.5989</v>
@@ -6818,7 +6818,7 @@
         <v>534</v>
       </c>
       <c r="I105" s="0" t="s">
-        <v>706</v>
+        <v>882</v>
       </c>
       <c r="J105" s="0">
         <v>1016.6576</v>
@@ -6850,7 +6850,7 @@
         <v>543</v>
       </c>
       <c r="I106" s="0" t="s">
-        <v>715</v>
+        <v>883</v>
       </c>
       <c r="J106" s="0">
         <v>10363.415999999999</v>
@@ -6882,7 +6882,7 @@
         <v>544</v>
       </c>
       <c r="I107" s="0" t="s">
-        <v>716</v>
+        <v>884</v>
       </c>
       <c r="J107" s="0">
         <v>8731.0702999999994</v>
@@ -6914,7 +6914,7 @@
         <v>547</v>
       </c>
       <c r="I108" s="0" t="s">
-        <v>719</v>
+        <v>885</v>
       </c>
       <c r="J108" s="0">
         <v>509.65910000000002</v>
@@ -6946,7 +6946,7 @@
         <v>548</v>
       </c>
       <c r="I109" s="0" t="s">
-        <v>720</v>
+        <v>886</v>
       </c>
       <c r="J109" s="0">
         <v>473.81920000000002</v>
@@ -6978,7 +6978,7 @@
         <v>549</v>
       </c>
       <c r="I110" s="0" t="s">
-        <v>721</v>
+        <v>887</v>
       </c>
       <c r="J110" s="0">
         <v>386.12639999999999</v>
@@ -7010,7 +7010,7 @@
         <v>550</v>
       </c>
       <c r="I111" s="0" t="s">
-        <v>722</v>
+        <v>888</v>
       </c>
       <c r="J111" s="0">
         <v>381.40570000000002</v>
@@ -7042,7 +7042,7 @@
         <v>551</v>
       </c>
       <c r="I112" s="0" t="s">
-        <v>723</v>
+        <v>889</v>
       </c>
       <c r="J112" s="0">
         <v>371.59660000000002</v>
@@ -7074,7 +7074,7 @@
         <v>552</v>
       </c>
       <c r="I113" s="0" t="s">
-        <v>724</v>
+        <v>890</v>
       </c>
       <c r="J113" s="0">
         <v>364.02569999999997</v>
@@ -7106,7 +7106,7 @@
         <v>146</v>
       </c>
       <c r="I114" s="0" t="s">
-        <v>725</v>
+        <v>891</v>
       </c>
       <c r="J114" s="0">
         <v>342.74220000000003</v>
@@ -7138,7 +7138,7 @@
         <v>553</v>
       </c>
       <c r="I115" s="0" t="s">
-        <v>726</v>
+        <v>892</v>
       </c>
       <c r="J115" s="0">
         <v>331.7552</v>
@@ -7170,7 +7170,7 @@
         <v>129</v>
       </c>
       <c r="I116" s="0" t="s">
-        <v>296</v>
+        <v>893</v>
       </c>
       <c r="J116" s="0">
         <v>8389.2909999999993</v>
@@ -7202,7 +7202,7 @@
         <v>130</v>
       </c>
       <c r="I117" s="0" t="s">
-        <v>297</v>
+        <v>894</v>
       </c>
       <c r="J117" s="0">
         <v>8068.0429999999997</v>
@@ -7234,7 +7234,7 @@
         <v>133</v>
       </c>
       <c r="I118" s="0" t="s">
-        <v>300</v>
+        <v>895</v>
       </c>
       <c r="J118" s="0">
         <v>528.16520000000003</v>
@@ -7266,7 +7266,7 @@
         <v>134</v>
       </c>
       <c r="I119" s="0" t="s">
-        <v>301</v>
+        <v>896</v>
       </c>
       <c r="J119" s="0">
         <v>464.43889999999999</v>
@@ -7298,7 +7298,7 @@
         <v>135</v>
       </c>
       <c r="I120" s="0" t="s">
-        <v>302</v>
+        <v>897</v>
       </c>
       <c r="J120" s="0">
         <v>449.87619999999998</v>
@@ -7330,7 +7330,7 @@
         <v>136</v>
       </c>
       <c r="I121" s="0" t="s">
-        <v>303</v>
+        <v>898</v>
       </c>
       <c r="J121" s="0">
         <v>447.66699999999997</v>
@@ -7362,7 +7362,7 @@
         <v>137</v>
       </c>
       <c r="I122" s="0" t="s">
-        <v>304</v>
+        <v>899</v>
       </c>
       <c r="J122" s="0">
         <v>391.69869999999997</v>
@@ -7394,7 +7394,7 @@
         <v>138</v>
       </c>
       <c r="I123" s="0" t="s">
-        <v>305</v>
+        <v>900</v>
       </c>
       <c r="J123" s="0">
         <v>372.4153</v>
@@ -7426,7 +7426,7 @@
         <v>139</v>
       </c>
       <c r="I124" s="0" t="s">
-        <v>306</v>
+        <v>901</v>
       </c>
       <c r="J124" s="0">
         <v>366.97289999999998</v>
@@ -7458,7 +7458,7 @@
         <v>140</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>307</v>
+        <v>902</v>
       </c>
       <c r="J125" s="0">
         <v>329.11259999999999</v>
@@ -7490,7 +7490,7 @@
         <v>58</v>
       </c>
       <c r="I126" s="0" t="s">
-        <v>308</v>
+        <v>903</v>
       </c>
       <c r="J126" s="0">
         <v>9741.5614999999998</v>
@@ -7522,7 +7522,7 @@
         <v>59</v>
       </c>
       <c r="I127" s="0" t="s">
-        <v>309</v>
+        <v>904</v>
       </c>
       <c r="J127" s="0">
         <v>8198.8974999999991</v>
@@ -7554,7 +7554,7 @@
         <v>60</v>
       </c>
       <c r="I128" s="0" t="s">
-        <v>310</v>
+        <v>905</v>
       </c>
       <c r="J128" s="0">
         <v>1259.1116</v>
@@ -7586,7 +7586,7 @@
         <v>61</v>
       </c>
       <c r="I129" s="0" t="s">
-        <v>311</v>
+        <v>906</v>
       </c>
       <c r="J129" s="0">
         <v>863.95190000000002</v>
@@ -7618,7 +7618,7 @@
         <v>141</v>
       </c>
       <c r="I130" s="0" t="s">
-        <v>312</v>
+        <v>907</v>
       </c>
       <c r="J130" s="0">
         <v>539.45429999999999</v>
@@ -7650,7 +7650,7 @@
         <v>142</v>
       </c>
       <c r="I131" s="0" t="s">
-        <v>313</v>
+        <v>908</v>
       </c>
       <c r="J131" s="0">
         <v>485.64830000000001</v>
@@ -7682,7 +7682,7 @@
         <v>143</v>
       </c>
       <c r="I132" s="0" t="s">
-        <v>314</v>
+        <v>909</v>
       </c>
       <c r="J132" s="0">
         <v>457.39609999999999</v>
@@ -7714,7 +7714,7 @@
         <v>144</v>
       </c>
       <c r="I133" s="0" t="s">
-        <v>315</v>
+        <v>910</v>
       </c>
       <c r="J133" s="0">
         <v>454.66460000000001</v>
@@ -7746,7 +7746,7 @@
         <v>145</v>
       </c>
       <c r="I134" s="0" t="s">
-        <v>316</v>
+        <v>911</v>
       </c>
       <c r="J134" s="0">
         <v>368.51979999999998</v>
@@ -7778,7 +7778,7 @@
         <v>146</v>
       </c>
       <c r="I135" s="0" t="s">
-        <v>317</v>
+        <v>912</v>
       </c>
       <c r="J135" s="0">
         <v>342.74220000000003</v>
@@ -7810,7 +7810,7 @@
         <v>147</v>
       </c>
       <c r="I136" s="0" t="s">
-        <v>318</v>
+        <v>913</v>
       </c>
       <c r="J136" s="0">
         <v>302.46800000000002</v>
@@ -7842,7 +7842,7 @@
         <v>148</v>
       </c>
       <c r="I137" s="0" t="s">
-        <v>319</v>
+        <v>914</v>
       </c>
       <c r="J137" s="0">
         <v>300.47250000000003</v>
@@ -7874,7 +7874,7 @@
         <v>149</v>
       </c>
       <c r="I138" s="0" t="s">
-        <v>320</v>
+        <v>915</v>
       </c>
       <c r="J138" s="0">
         <v>10892.9414</v>
@@ -7906,7 +7906,7 @@
         <v>150</v>
       </c>
       <c r="I139" s="0" t="s">
-        <v>321</v>
+        <v>916</v>
       </c>
       <c r="J139" s="0">
         <v>5918.6806999999999</v>
@@ -7938,7 +7938,7 @@
         <v>151</v>
       </c>
       <c r="I140" s="0" t="s">
-        <v>322</v>
+        <v>917</v>
       </c>
       <c r="J140" s="0">
         <v>829.46619999999996</v>
@@ -7970,7 +7970,7 @@
         <v>152</v>
       </c>
       <c r="I141" s="0" t="s">
-        <v>323</v>
+        <v>918</v>
       </c>
       <c r="J141" s="0">
         <v>726.14110000000005</v>
@@ -8002,7 +8002,7 @@
         <v>153</v>
       </c>
       <c r="I142" s="0" t="s">
-        <v>324</v>
+        <v>919</v>
       </c>
       <c r="J142" s="0">
         <v>498.3132</v>
@@ -8034,7 +8034,7 @@
         <v>154</v>
       </c>
       <c r="I143" s="0" t="s">
-        <v>325</v>
+        <v>920</v>
       </c>
       <c r="J143" s="0">
         <v>487.10520000000002</v>
@@ -8066,7 +8066,7 @@
         <v>155</v>
       </c>
       <c r="I144" s="0" t="s">
-        <v>326</v>
+        <v>921</v>
       </c>
       <c r="J144" s="0">
         <v>485.66770000000002</v>
@@ -8098,7 +8098,7 @@
         <v>156</v>
       </c>
       <c r="I145" s="0" t="s">
-        <v>327</v>
+        <v>922</v>
       </c>
       <c r="J145" s="0">
         <v>478.11529999999999</v>
@@ -8130,7 +8130,7 @@
         <v>157</v>
       </c>
       <c r="I146" s="0" t="s">
-        <v>328</v>
+        <v>923</v>
       </c>
       <c r="J146" s="0">
         <v>375.48970000000003</v>
@@ -8162,7 +8162,7 @@
         <v>158</v>
       </c>
       <c r="I147" s="0" t="s">
-        <v>329</v>
+        <v>924</v>
       </c>
       <c r="J147" s="0">
         <v>359.0838</v>
@@ -8194,7 +8194,7 @@
         <v>159</v>
       </c>
       <c r="I148" s="0" t="s">
-        <v>330</v>
+        <v>925</v>
       </c>
       <c r="J148" s="0">
         <v>338.9837</v>
@@ -8226,7 +8226,7 @@
         <v>160</v>
       </c>
       <c r="I149" s="0" t="s">
-        <v>331</v>
+        <v>926</v>
       </c>
       <c r="J149" s="0">
         <v>293.55579999999998</v>
@@ -8258,7 +8258,7 @@
         <v>161</v>
       </c>
       <c r="I150" s="0" t="s">
-        <v>332</v>
+        <v>927</v>
       </c>
       <c r="J150" s="0">
         <v>9826.1103999999996</v>
@@ -8290,7 +8290,7 @@
         <v>162</v>
       </c>
       <c r="I151" s="0" t="s">
-        <v>333</v>
+        <v>928</v>
       </c>
       <c r="J151" s="0">
         <v>7957.9004000000004</v>
@@ -8322,7 +8322,7 @@
         <v>163</v>
       </c>
       <c r="I152" s="0" t="s">
-        <v>334</v>
+        <v>929</v>
       </c>
       <c r="J152" s="0">
         <v>1958.7829999999999</v>
@@ -8354,7 +8354,7 @@
         <v>165</v>
       </c>
       <c r="I153" s="0" t="s">
-        <v>336</v>
+        <v>930</v>
       </c>
       <c r="J153" s="0">
         <v>574.80640000000005</v>
@@ -8386,7 +8386,7 @@
         <v>166</v>
       </c>
       <c r="I154" s="0" t="s">
-        <v>337</v>
+        <v>931</v>
       </c>
       <c r="J154" s="0">
         <v>532.89999999999998</v>
@@ -8418,7 +8418,7 @@
         <v>167</v>
       </c>
       <c r="I155" s="0" t="s">
-        <v>338</v>
+        <v>932</v>
       </c>
       <c r="J155" s="0">
         <v>470.99040000000002</v>
@@ -8450,7 +8450,7 @@
         <v>168</v>
       </c>
       <c r="I156" s="0" t="s">
-        <v>339</v>
+        <v>933</v>
       </c>
       <c r="J156" s="0">
         <v>428.05349999999999</v>
@@ -8482,7 +8482,7 @@
         <v>169</v>
       </c>
       <c r="I157" s="0" t="s">
-        <v>340</v>
+        <v>934</v>
       </c>
       <c r="J157" s="0">
         <v>370.83409999999998</v>
@@ -8514,7 +8514,7 @@
         <v>170</v>
       </c>
       <c r="I158" s="0" t="s">
-        <v>341</v>
+        <v>935</v>
       </c>
       <c r="J158" s="0">
         <v>361.65289999999999</v>
@@ -8546,7 +8546,7 @@
         <v>171</v>
       </c>
       <c r="I159" s="0" t="s">
-        <v>342</v>
+        <v>936</v>
       </c>
       <c r="J159" s="0">
         <v>328.18830000000003</v>
@@ -8578,7 +8578,7 @@
         <v>172</v>
       </c>
       <c r="I160" s="0" t="s">
-        <v>343</v>
+        <v>937</v>
       </c>
       <c r="J160" s="0">
         <v>313.28399999999999</v>
@@ -8610,7 +8610,7 @@
         <v>47</v>
       </c>
       <c r="I161" s="0" t="s">
-        <v>345</v>
+        <v>938</v>
       </c>
       <c r="J161" s="0">
         <v>9104.8721000000005</v>
@@ -8642,7 +8642,7 @@
         <v>48</v>
       </c>
       <c r="I162" s="0" t="s">
-        <v>346</v>
+        <v>939</v>
       </c>
       <c r="J162" s="0">
         <v>1438.8326</v>
@@ -8674,7 +8674,7 @@
         <v>49</v>
       </c>
       <c r="I163" s="0" t="s">
-        <v>347</v>
+        <v>940</v>
       </c>
       <c r="J163" s="0">
         <v>1210.5242000000001</v>
@@ -8706,7 +8706,7 @@
         <v>50</v>
       </c>
       <c r="I164" s="0" t="s">
-        <v>348</v>
+        <v>941</v>
       </c>
       <c r="J164" s="0">
         <v>542.07240000000002</v>
@@ -8738,7 +8738,7 @@
         <v>51</v>
       </c>
       <c r="I165" s="0" t="s">
-        <v>349</v>
+        <v>942</v>
       </c>
       <c r="J165" s="0">
         <v>528.39120000000003</v>
@@ -8770,7 +8770,7 @@
         <v>52</v>
       </c>
       <c r="I166" s="0" t="s">
-        <v>350</v>
+        <v>943</v>
       </c>
       <c r="J166" s="0">
         <v>519.83349999999996</v>
@@ -8802,7 +8802,7 @@
         <v>53</v>
       </c>
       <c r="I167" s="0" t="s">
-        <v>351</v>
+        <v>944</v>
       </c>
       <c r="J167" s="0">
         <v>465.38400000000001</v>
@@ -8834,7 +8834,7 @@
         <v>54</v>
       </c>
       <c r="I168" s="0" t="s">
-        <v>352</v>
+        <v>945</v>
       </c>
       <c r="J168" s="0">
         <v>387.42579999999998</v>
@@ -8866,7 +8866,7 @@
         <v>55</v>
       </c>
       <c r="I169" s="0" t="s">
-        <v>353</v>
+        <v>946</v>
       </c>
       <c r="J169" s="0">
         <v>376.01639999999998</v>
@@ -8898,7 +8898,7 @@
         <v>56</v>
       </c>
       <c r="I170" s="0" t="s">
-        <v>354</v>
+        <v>947</v>
       </c>
       <c r="J170" s="0">
         <v>367.9187</v>
@@ -8930,7 +8930,7 @@
         <v>57</v>
       </c>
       <c r="I171" s="0" t="s">
-        <v>355</v>
+        <v>948</v>
       </c>
       <c r="J171" s="0">
         <v>345.6712</v>
@@ -8962,7 +8962,7 @@
         <v>173</v>
       </c>
       <c r="I172" s="0" t="s">
-        <v>356</v>
+        <v>949</v>
       </c>
       <c r="J172" s="0">
         <v>11026.299800000001</v>
@@ -8994,7 +8994,7 @@
         <v>174</v>
       </c>
       <c r="I173" s="0" t="s">
-        <v>357</v>
+        <v>950</v>
       </c>
       <c r="J173" s="0">
         <v>8759.9452999999994</v>
@@ -9026,7 +9026,7 @@
         <v>175</v>
       </c>
       <c r="I174" s="0" t="s">
-        <v>358</v>
+        <v>951</v>
       </c>
       <c r="J174" s="0">
         <v>1159.0046</v>
@@ -9058,7 +9058,7 @@
         <v>176</v>
       </c>
       <c r="I175" s="0" t="s">
-        <v>359</v>
+        <v>952</v>
       </c>
       <c r="J175" s="0">
         <v>1153.3887</v>
@@ -9090,7 +9090,7 @@
         <v>177</v>
       </c>
       <c r="I176" s="0" t="s">
-        <v>360</v>
+        <v>953</v>
       </c>
       <c r="J176" s="0">
         <v>531.56039999999996</v>
@@ -9122,7 +9122,7 @@
         <v>178</v>
       </c>
       <c r="I177" s="0" t="s">
-        <v>361</v>
+        <v>954</v>
       </c>
       <c r="J177" s="0">
         <v>513.93790000000001</v>
@@ -9154,7 +9154,7 @@
         <v>179</v>
       </c>
       <c r="I178" s="0" t="s">
-        <v>362</v>
+        <v>955</v>
       </c>
       <c r="J178" s="0">
         <v>499.63580000000002</v>
@@ -9186,7 +9186,7 @@
         <v>180</v>
       </c>
       <c r="I179" s="0" t="s">
-        <v>363</v>
+        <v>956</v>
       </c>
       <c r="J179" s="0">
         <v>475.38760000000002</v>
@@ -9218,7 +9218,7 @@
         <v>181</v>
       </c>
       <c r="I180" s="0" t="s">
-        <v>364</v>
+        <v>957</v>
       </c>
       <c r="J180" s="0">
         <v>357.59019999999998</v>
@@ -9250,7 +9250,7 @@
         <v>182</v>
       </c>
       <c r="I181" s="0" t="s">
-        <v>365</v>
+        <v>958</v>
       </c>
       <c r="J181" s="0">
         <v>346.22629999999998</v>
@@ -9282,7 +9282,7 @@
         <v>183</v>
       </c>
       <c r="I182" s="0" t="s">
-        <v>366</v>
+        <v>959</v>
       </c>
       <c r="J182" s="0">
         <v>331.46199999999999</v>
@@ -9314,7 +9314,7 @@
         <v>184</v>
       </c>
       <c r="I183" s="0" t="s">
-        <v>367</v>
+        <v>960</v>
       </c>
       <c r="J183" s="0">
         <v>308.1046</v>
@@ -9346,7 +9346,7 @@
         <v>72</v>
       </c>
       <c r="I184" s="0" t="s">
-        <v>370</v>
+        <v>961</v>
       </c>
       <c r="J184" s="0">
         <v>901.9991</v>
@@ -9378,7 +9378,7 @@
         <v>73</v>
       </c>
       <c r="I185" s="0" t="s">
-        <v>371</v>
+        <v>962</v>
       </c>
       <c r="J185" s="0">
         <v>893.56960000000004</v>
@@ -9410,7 +9410,7 @@
         <v>74</v>
       </c>
       <c r="I186" s="0" t="s">
-        <v>372</v>
+        <v>963</v>
       </c>
       <c r="J186" s="0">
         <v>549.74869999999999</v>
@@ -9442,7 +9442,7 @@
         <v>75</v>
       </c>
       <c r="I187" s="0" t="s">
-        <v>373</v>
+        <v>964</v>
       </c>
       <c r="J187" s="0">
         <v>530.14729999999997</v>
@@ -9474,7 +9474,7 @@
         <v>76</v>
       </c>
       <c r="I188" s="0" t="s">
-        <v>374</v>
+        <v>965</v>
       </c>
       <c r="J188" s="0">
         <v>489.4966</v>
@@ -9506,7 +9506,7 @@
         <v>77</v>
       </c>
       <c r="I189" s="0" t="s">
-        <v>375</v>
+        <v>966</v>
       </c>
       <c r="J189" s="0">
         <v>482.49549999999999</v>
@@ -9538,7 +9538,7 @@
         <v>78</v>
       </c>
       <c r="I190" s="0" t="s">
-        <v>376</v>
+        <v>967</v>
       </c>
       <c r="J190" s="0">
         <v>378.9196</v>
@@ -9570,7 +9570,7 @@
         <v>79</v>
       </c>
       <c r="I191" s="0" t="s">
-        <v>377</v>
+        <v>968</v>
       </c>
       <c r="J191" s="0">
         <v>366.15300000000002</v>
@@ -9602,7 +9602,7 @@
         <v>80</v>
       </c>
       <c r="I192" s="0" t="s">
-        <v>378</v>
+        <v>969</v>
       </c>
       <c r="J192" s="0">
         <v>340.57749999999999</v>
@@ -9634,7 +9634,7 @@
         <v>185</v>
       </c>
       <c r="I193" s="0" t="s">
-        <v>380</v>
+        <v>970</v>
       </c>
       <c r="J193" s="0">
         <v>4307.7025999999996</v>
@@ -9666,7 +9666,7 @@
         <v>186</v>
       </c>
       <c r="I194" s="0" t="s">
-        <v>381</v>
+        <v>971</v>
       </c>
       <c r="J194" s="0">
         <v>1837.0477000000001</v>
@@ -9698,7 +9698,7 @@
         <v>187</v>
       </c>
       <c r="I195" s="0" t="s">
-        <v>382</v>
+        <v>972</v>
       </c>
       <c r="J195" s="0">
         <v>616.08360000000005</v>
@@ -9730,7 +9730,7 @@
         <v>188</v>
       </c>
       <c r="I196" s="0" t="s">
-        <v>383</v>
+        <v>973</v>
       </c>
       <c r="J196" s="0">
         <v>552.42719999999997</v>
@@ -9762,7 +9762,7 @@
         <v>189</v>
       </c>
       <c r="I197" s="0" t="s">
-        <v>384</v>
+        <v>974</v>
       </c>
       <c r="J197" s="0">
         <v>399.44740000000002</v>
@@ -9794,7 +9794,7 @@
         <v>190</v>
       </c>
       <c r="I198" s="0" t="s">
-        <v>385</v>
+        <v>975</v>
       </c>
       <c r="J198" s="0">
         <v>377.98289999999997</v>
@@ -9826,7 +9826,7 @@
         <v>191</v>
       </c>
       <c r="I199" s="0" t="s">
-        <v>386</v>
+        <v>976</v>
       </c>
       <c r="J199" s="0">
         <v>376.71690000000001</v>
@@ -9858,7 +9858,7 @@
         <v>192</v>
       </c>
       <c r="I200" s="0" t="s">
-        <v>387</v>
+        <v>977</v>
       </c>
       <c r="J200" s="0">
         <v>375.52019999999999</v>
@@ -9890,7 +9890,7 @@
         <v>193</v>
       </c>
       <c r="I201" s="0" t="s">
-        <v>388</v>
+        <v>978</v>
       </c>
       <c r="J201" s="0">
         <v>370.8648</v>
@@ -9922,7 +9922,7 @@
         <v>194</v>
       </c>
       <c r="I202" s="0" t="s">
-        <v>389</v>
+        <v>979</v>
       </c>
       <c r="J202" s="0">
         <v>342.89479999999998</v>
@@ -9954,7 +9954,7 @@
         <v>195</v>
       </c>
       <c r="I203" s="0" t="s">
-        <v>390</v>
+        <v>980</v>
       </c>
       <c r="J203" s="0">
         <v>307.26029999999997</v>
@@ -9986,7 +9986,7 @@
         <v>196</v>
       </c>
       <c r="I204" s="0" t="s">
-        <v>391</v>
+        <v>981</v>
       </c>
       <c r="J204" s="0">
         <v>261.58179999999999</v>
@@ -10018,7 +10018,7 @@
         <v>82</v>
       </c>
       <c r="I205" s="0" t="s">
-        <v>392</v>
+        <v>982</v>
       </c>
       <c r="J205" s="0">
         <v>10466.208000000001</v>
@@ -10050,7 +10050,7 @@
         <v>83</v>
       </c>
       <c r="I206" s="0" t="s">
-        <v>393</v>
+        <v>983</v>
       </c>
       <c r="J206" s="0">
         <v>7328.0029000000004</v>
@@ -10082,7 +10082,7 @@
         <v>84</v>
       </c>
       <c r="I207" s="0" t="s">
-        <v>394</v>
+        <v>984</v>
       </c>
       <c r="J207" s="0">
         <v>1015.5606</v>
@@ -10114,7 +10114,7 @@
         <v>85</v>
       </c>
       <c r="I208" s="0" t="s">
-        <v>395</v>
+        <v>985</v>
       </c>
       <c r="J208" s="0">
         <v>908.67830000000004</v>
@@ -10146,7 +10146,7 @@
         <v>86</v>
       </c>
       <c r="I209" s="0" t="s">
-        <v>396</v>
+        <v>986</v>
       </c>
       <c r="J209" s="0">
         <v>520.97770000000003</v>
@@ -10178,7 +10178,7 @@
         <v>87</v>
       </c>
       <c r="I210" s="0" t="s">
-        <v>397</v>
+        <v>987</v>
       </c>
       <c r="J210" s="0">
         <v>488.97149999999999</v>
@@ -10210,7 +10210,7 @@
         <v>88</v>
       </c>
       <c r="I211" s="0" t="s">
-        <v>398</v>
+        <v>988</v>
       </c>
       <c r="J211" s="0">
         <v>484.75029999999998</v>
@@ -10242,7 +10242,7 @@
         <v>89</v>
       </c>
       <c r="I212" s="0" t="s">
-        <v>399</v>
+        <v>989</v>
       </c>
       <c r="J212" s="0">
         <v>438.36930000000001</v>
@@ -10274,7 +10274,7 @@
         <v>90</v>
       </c>
       <c r="I213" s="0" t="s">
-        <v>400</v>
+        <v>990</v>
       </c>
       <c r="J213" s="0">
         <v>369.10219999999998</v>
@@ -10306,7 +10306,7 @@
         <v>91</v>
       </c>
       <c r="I214" s="0" t="s">
-        <v>401</v>
+        <v>991</v>
       </c>
       <c r="J214" s="0">
         <v>342.30680000000001</v>
@@ -10338,7 +10338,7 @@
         <v>92</v>
       </c>
       <c r="I215" s="0" t="s">
-        <v>402</v>
+        <v>992</v>
       </c>
       <c r="J215" s="0">
         <v>280.75409999999999</v>
@@ -10370,7 +10370,7 @@
         <v>93</v>
       </c>
       <c r="I216" s="0" t="s">
-        <v>403</v>
+        <v>993</v>
       </c>
       <c r="J216" s="0">
         <v>270.84679999999997</v>
@@ -10402,7 +10402,7 @@
         <v>94</v>
       </c>
       <c r="I217" s="0" t="s">
-        <v>404</v>
+        <v>994</v>
       </c>
       <c r="J217" s="0">
         <v>8934.2567999999992</v>
@@ -10434,7 +10434,7 @@
         <v>95</v>
       </c>
       <c r="I218" s="0" t="s">
-        <v>405</v>
+        <v>995</v>
       </c>
       <c r="J218" s="0">
         <v>7192.2339000000002</v>
@@ -10466,7 +10466,7 @@
         <v>99</v>
       </c>
       <c r="I219" s="0" t="s">
-        <v>409</v>
+        <v>996</v>
       </c>
       <c r="J219" s="0">
         <v>489.01900000000001</v>
@@ -10498,7 +10498,7 @@
         <v>100</v>
       </c>
       <c r="I220" s="0" t="s">
-        <v>410</v>
+        <v>997</v>
       </c>
       <c r="J220" s="0">
         <v>486.78719999999999</v>
@@ -10530,7 +10530,7 @@
         <v>101</v>
       </c>
       <c r="I221" s="0" t="s">
-        <v>411</v>
+        <v>998</v>
       </c>
       <c r="J221" s="0">
         <v>478.59969999999999</v>
@@ -10562,7 +10562,7 @@
         <v>102</v>
       </c>
       <c r="I222" s="0" t="s">
-        <v>412</v>
+        <v>999</v>
       </c>
       <c r="J222" s="0">
         <v>456.38220000000001</v>
@@ -10594,7 +10594,7 @@
         <v>103</v>
       </c>
       <c r="I223" s="0" t="s">
-        <v>413</v>
+        <v>1000</v>
       </c>
       <c r="J223" s="0">
         <v>361.197</v>
@@ -10626,7 +10626,7 @@
         <v>104</v>
       </c>
       <c r="I224" s="0" t="s">
-        <v>414</v>
+        <v>1001</v>
       </c>
       <c r="J224" s="0">
         <v>350.10750000000002</v>
@@ -10658,7 +10658,7 @@
         <v>105</v>
       </c>
       <c r="I225" s="0" t="s">
-        <v>415</v>
+        <v>1002</v>
       </c>
       <c r="J225" s="0">
         <v>332.8802</v>
@@ -10690,7 +10690,7 @@
         <v>106</v>
       </c>
       <c r="I226" s="0" t="s">
-        <v>416</v>
+        <v>1003</v>
       </c>
       <c r="J226" s="0">
         <v>9850.5967000000001</v>
@@ -10722,7 +10722,7 @@
         <v>107</v>
       </c>
       <c r="I227" s="0" t="s">
-        <v>417</v>
+        <v>1004</v>
       </c>
       <c r="J227" s="0">
         <v>8299.1229999999996</v>
@@ -10754,7 +10754,7 @@
         <v>108</v>
       </c>
       <c r="I228" s="0" t="s">
-        <v>418</v>
+        <v>1005</v>
       </c>
       <c r="J228" s="0">
         <v>1061.2550000000001</v>
@@ -10786,7 +10786,7 @@
         <v>61</v>
       </c>
       <c r="I229" s="0" t="s">
-        <v>419</v>
+        <v>1006</v>
       </c>
       <c r="J229" s="0">
         <v>863.95190000000002</v>
@@ -10818,7 +10818,7 @@
         <v>109</v>
       </c>
       <c r="I230" s="0" t="s">
-        <v>420</v>
+        <v>1007</v>
       </c>
       <c r="J230" s="0">
         <v>537.24440000000004</v>
@@ -10850,7 +10850,7 @@
         <v>110</v>
       </c>
       <c r="I231" s="0" t="s">
-        <v>421</v>
+        <v>1008</v>
       </c>
       <c r="J231" s="0">
         <v>512.39139999999998</v>
@@ -10882,7 +10882,7 @@
         <v>111</v>
       </c>
       <c r="I232" s="0" t="s">
-        <v>422</v>
+        <v>1009</v>
       </c>
       <c r="J232" s="0">
         <v>461.678</v>
@@ -10914,7 +10914,7 @@
         <v>112</v>
       </c>
       <c r="I233" s="0" t="s">
-        <v>423</v>
+        <v>1010</v>
       </c>
       <c r="J233" s="0">
         <v>446.13510000000002</v>
@@ -10946,7 +10946,7 @@
         <v>113</v>
       </c>
       <c r="I234" s="0" t="s">
-        <v>424</v>
+        <v>1011</v>
       </c>
       <c r="J234" s="0">
         <v>416.1148</v>
@@ -10978,7 +10978,7 @@
         <v>114</v>
       </c>
       <c r="I235" s="0" t="s">
-        <v>425</v>
+        <v>1012</v>
       </c>
       <c r="J235" s="0">
         <v>385.80329999999998</v>
@@ -11010,7 +11010,7 @@
         <v>115</v>
       </c>
       <c r="I236" s="0" t="s">
-        <v>426</v>
+        <v>1013</v>
       </c>
       <c r="J236" s="0">
         <v>376.43869999999998</v>
@@ -11042,7 +11042,7 @@
         <v>116</v>
       </c>
       <c r="I237" s="0" t="s">
-        <v>427</v>
+        <v>1014</v>
       </c>
       <c r="J237" s="0">
         <v>340.64490000000001</v>
@@ -11074,7 +11074,7 @@
         <v>117</v>
       </c>
       <c r="I238" s="0" t="s">
-        <v>428</v>
+        <v>1015</v>
       </c>
       <c r="J238" s="0">
         <v>9114.7715000000008</v>
@@ -11106,7 +11106,7 @@
         <v>118</v>
       </c>
       <c r="I239" s="0" t="s">
-        <v>429</v>
+        <v>1016</v>
       </c>
       <c r="J239" s="0">
         <v>7656.0316999999996</v>
@@ -11138,7 +11138,7 @@
         <v>121</v>
       </c>
       <c r="I240" s="0" t="s">
-        <v>432</v>
+        <v>1017</v>
       </c>
       <c r="J240" s="0">
         <v>542.5788</v>
@@ -11170,7 +11170,7 @@
         <v>122</v>
       </c>
       <c r="I241" s="0" t="s">
-        <v>433</v>
+        <v>1018</v>
       </c>
       <c r="J241" s="0">
         <v>534.76580000000001</v>
@@ -11202,7 +11202,7 @@
         <v>123</v>
       </c>
       <c r="I242" s="0" t="s">
-        <v>434</v>
+        <v>1019</v>
       </c>
       <c r="J242" s="0">
         <v>484.83710000000002</v>
@@ -11234,7 +11234,7 @@
         <v>124</v>
       </c>
       <c r="I243" s="0" t="s">
-        <v>435</v>
+        <v>1020</v>
       </c>
       <c r="J243" s="0">
         <v>468.87529999999998</v>
@@ -11266,7 +11266,7 @@
         <v>125</v>
       </c>
       <c r="I244" s="0" t="s">
-        <v>436</v>
+        <v>1021</v>
       </c>
       <c r="J244" s="0">
         <v>398.83769999999998</v>
@@ -11298,7 +11298,7 @@
         <v>126</v>
       </c>
       <c r="I245" s="0" t="s">
-        <v>437</v>
+        <v>1022</v>
       </c>
       <c r="J245" s="0">
         <v>337.36939999999999</v>
@@ -11330,7 +11330,7 @@
         <v>127</v>
       </c>
       <c r="I246" s="0" t="s">
-        <v>438</v>
+        <v>1023</v>
       </c>
       <c r="J246" s="0">
         <v>311.84429999999998</v>
@@ -11362,7 +11362,7 @@
         <v>128</v>
       </c>
       <c r="I247" s="0" t="s">
-        <v>439</v>
+        <v>1024</v>
       </c>
       <c r="J247" s="0">
         <v>245.285</v>
@@ -11394,7 +11394,7 @@
         <v>197</v>
       </c>
       <c r="I248" s="0" t="s">
-        <v>440</v>
+        <v>1025</v>
       </c>
       <c r="J248" s="0">
         <v>2887.6174000000001</v>
@@ -11426,7 +11426,7 @@
         <v>198</v>
       </c>
       <c r="I249" s="0" t="s">
-        <v>441</v>
+        <v>1026</v>
       </c>
       <c r="J249" s="0">
         <v>2872.1073999999999</v>
@@ -11458,7 +11458,7 @@
         <v>199</v>
       </c>
       <c r="I250" s="0" t="s">
-        <v>442</v>
+        <v>1027</v>
       </c>
       <c r="J250" s="0">
         <v>975.3777</v>
@@ -11490,7 +11490,7 @@
         <v>187</v>
       </c>
       <c r="I251" s="0" t="s">
-        <v>443</v>
+        <v>1028</v>
       </c>
       <c r="J251" s="0">
         <v>616.08360000000005</v>
@@ -11522,7 +11522,7 @@
         <v>200</v>
       </c>
       <c r="I252" s="0" t="s">
-        <v>444</v>
+        <v>1029</v>
       </c>
       <c r="J252" s="0">
         <v>465.53719999999999</v>
@@ -11554,7 +11554,7 @@
         <v>201</v>
       </c>
       <c r="I253" s="0" t="s">
-        <v>445</v>
+        <v>1030</v>
       </c>
       <c r="J253" s="0">
         <v>436.18400000000003</v>
@@ -11586,7 +11586,7 @@
         <v>202</v>
       </c>
       <c r="I254" s="0" t="s">
-        <v>446</v>
+        <v>1031</v>
       </c>
       <c r="J254" s="0">
         <v>415.78980000000001</v>
@@ -11618,7 +11618,7 @@
         <v>203</v>
       </c>
       <c r="I255" s="0" t="s">
-        <v>447</v>
+        <v>1032</v>
       </c>
       <c r="J255" s="0">
         <v>391.16430000000003</v>
@@ -11650,7 +11650,7 @@
         <v>204</v>
       </c>
       <c r="I256" s="0" t="s">
-        <v>448</v>
+        <v>1033</v>
       </c>
       <c r="J256" s="0">
         <v>362.91770000000002</v>
@@ -11682,7 +11682,7 @@
         <v>205</v>
       </c>
       <c r="I257" s="0" t="s">
-        <v>449</v>
+        <v>1034</v>
       </c>
       <c r="J257" s="0">
         <v>315.58260000000001</v>
@@ -11714,7 +11714,7 @@
         <v>206</v>
       </c>
       <c r="I258" s="0" t="s">
-        <v>450</v>
+        <v>1035</v>
       </c>
       <c r="J258" s="0">
         <v>315.33229999999998</v>
@@ -11746,7 +11746,7 @@
         <v>207</v>
       </c>
       <c r="I259" s="0" t="s">
-        <v>451</v>
+        <v>1036</v>
       </c>
       <c r="J259" s="0">
         <v>254.02879999999999</v>
@@ -11778,7 +11778,7 @@
         <v>507</v>
       </c>
       <c r="I260" s="0" t="s">
-        <v>727</v>
+        <v>1037</v>
       </c>
       <c r="J260" s="0">
         <v>10897.75</v>
@@ -11810,7 +11810,7 @@
         <v>508</v>
       </c>
       <c r="I261" s="0" t="s">
-        <v>728</v>
+        <v>1038</v>
       </c>
       <c r="J261" s="0">
         <v>5963.8306000000002</v>
@@ -11842,7 +11842,7 @@
         <v>509</v>
       </c>
       <c r="I262" s="0" t="s">
-        <v>729</v>
+        <v>1039</v>
       </c>
       <c r="J262" s="0">
         <v>1364.115</v>
@@ -11874,7 +11874,7 @@
         <v>510</v>
       </c>
       <c r="I263" s="0" t="s">
-        <v>730</v>
+        <v>1040</v>
       </c>
       <c r="J263" s="0">
         <v>1002.6719000000001</v>
@@ -11906,7 +11906,7 @@
         <v>511</v>
       </c>
       <c r="I264" s="0" t="s">
-        <v>731</v>
+        <v>1041</v>
       </c>
       <c r="J264" s="0">
         <v>557.97879999999998</v>
@@ -11938,7 +11938,7 @@
         <v>512</v>
       </c>
       <c r="I265" s="0" t="s">
-        <v>732</v>
+        <v>1042</v>
       </c>
       <c r="J265" s="0">
         <v>511.4341</v>
@@ -11970,7 +11970,7 @@
         <v>513</v>
       </c>
       <c r="I266" s="0" t="s">
-        <v>733</v>
+        <v>1043</v>
       </c>
       <c r="J266" s="0">
         <v>485.53699999999998</v>
@@ -12002,7 +12002,7 @@
         <v>514</v>
       </c>
       <c r="I267" s="0" t="s">
-        <v>734</v>
+        <v>1044</v>
       </c>
       <c r="J267" s="0">
         <v>456.29579999999999</v>
@@ -12034,7 +12034,7 @@
         <v>515</v>
       </c>
       <c r="I268" s="0" t="s">
-        <v>735</v>
+        <v>1045</v>
       </c>
       <c r="J268" s="0">
         <v>403.62130000000002</v>
@@ -12066,7 +12066,7 @@
         <v>516</v>
       </c>
       <c r="I269" s="0" t="s">
-        <v>736</v>
+        <v>1046</v>
       </c>
       <c r="J269" s="0">
         <v>384.92849999999999</v>
@@ -12098,7 +12098,7 @@
         <v>517</v>
       </c>
       <c r="I270" s="0" t="s">
-        <v>737</v>
+        <v>1047</v>
       </c>
       <c r="J270" s="0">
         <v>345.9332</v>
@@ -12130,7 +12130,7 @@
         <v>518</v>
       </c>
       <c r="I271" s="0" t="s">
-        <v>738</v>
+        <v>1048</v>
       </c>
       <c r="J271" s="0">
         <v>329.33870000000002</v>
@@ -12162,7 +12162,7 @@
         <v>519</v>
       </c>
       <c r="I272" s="0" t="s">
-        <v>739</v>
+        <v>1049</v>
       </c>
       <c r="J272" s="0">
         <v>9494.3554999999997</v>
@@ -12194,7 +12194,7 @@
         <v>520</v>
       </c>
       <c r="I273" s="0" t="s">
-        <v>740</v>
+        <v>1050</v>
       </c>
       <c r="J273" s="0">
         <v>6959.3242</v>
@@ -12226,7 +12226,7 @@
         <v>523</v>
       </c>
       <c r="I274" s="0" t="s">
-        <v>743</v>
+        <v>1051</v>
       </c>
       <c r="J274" s="0">
         <v>528.32619999999997</v>
@@ -12258,7 +12258,7 @@
         <v>524</v>
       </c>
       <c r="I275" s="0" t="s">
-        <v>744</v>
+        <v>1052</v>
       </c>
       <c r="J275" s="0">
         <v>502.16129999999998</v>
@@ -12290,7 +12290,7 @@
         <v>525</v>
       </c>
       <c r="I276" s="0" t="s">
-        <v>745</v>
+        <v>1053</v>
       </c>
       <c r="J276" s="0">
         <v>468.14839999999998</v>
@@ -12322,7 +12322,7 @@
         <v>526</v>
       </c>
       <c r="I277" s="0" t="s">
-        <v>746</v>
+        <v>1054</v>
       </c>
       <c r="J277" s="0">
         <v>413.35890000000001</v>
@@ -12354,7 +12354,7 @@
         <v>527</v>
       </c>
       <c r="I278" s="0" t="s">
-        <v>747</v>
+        <v>1055</v>
       </c>
       <c r="J278" s="0">
         <v>410.47199999999998</v>
@@ -12386,7 +12386,7 @@
         <v>528</v>
       </c>
       <c r="I279" s="0" t="s">
-        <v>748</v>
+        <v>1056</v>
       </c>
       <c r="J279" s="0">
         <v>371.8809</v>
@@ -12418,7 +12418,7 @@
         <v>529</v>
       </c>
       <c r="I280" s="0" t="s">
-        <v>749</v>
+        <v>1057</v>
       </c>
       <c r="J280" s="0">
         <v>347.0478</v>
@@ -12450,7 +12450,7 @@
         <v>530</v>
       </c>
       <c r="I281" s="0" t="s">
-        <v>750</v>
+        <v>1058</v>
       </c>
       <c r="J281" s="0">
         <v>302.97559999999999</v>
@@ -12482,7 +12482,7 @@
         <v>531</v>
       </c>
       <c r="I282" s="0" t="s">
-        <v>751</v>
+        <v>1059</v>
       </c>
       <c r="J282" s="0">
         <v>8923.2001999999993</v>
@@ -12514,7 +12514,7 @@
         <v>532</v>
       </c>
       <c r="I283" s="0" t="s">
-        <v>752</v>
+        <v>1060</v>
       </c>
       <c r="J283" s="0">
         <v>7434.9364999999998</v>
@@ -12546,7 +12546,7 @@
         <v>533</v>
       </c>
       <c r="I284" s="0" t="s">
-        <v>753</v>
+        <v>1061</v>
       </c>
       <c r="J284" s="0">
         <v>1198.5989</v>
@@ -12578,7 +12578,7 @@
         <v>534</v>
       </c>
       <c r="I285" s="0" t="s">
-        <v>754</v>
+        <v>1062</v>
       </c>
       <c r="J285" s="0">
         <v>1016.6576</v>
@@ -12610,7 +12610,7 @@
         <v>543</v>
       </c>
       <c r="I286" s="0" t="s">
-        <v>755</v>
+        <v>1063</v>
       </c>
       <c r="J286" s="0">
         <v>10363.415999999999</v>
@@ -12642,7 +12642,7 @@
         <v>544</v>
       </c>
       <c r="I287" s="0" t="s">
-        <v>756</v>
+        <v>1064</v>
       </c>
       <c r="J287" s="0">
         <v>8731.0702999999994</v>
@@ -12674,7 +12674,7 @@
         <v>547</v>
       </c>
       <c r="I288" s="0" t="s">
-        <v>759</v>
+        <v>1065</v>
       </c>
       <c r="J288" s="0">
         <v>509.65910000000002</v>
@@ -12706,7 +12706,7 @@
         <v>64</v>
       </c>
       <c r="I289" s="0" t="s">
-        <v>760</v>
+        <v>1066</v>
       </c>
       <c r="J289" s="0">
         <v>497.6062</v>
@@ -12738,7 +12738,7 @@
         <v>548</v>
       </c>
       <c r="I290" s="0" t="s">
-        <v>761</v>
+        <v>1067</v>
       </c>
       <c r="J290" s="0">
         <v>473.81920000000002</v>
@@ -12770,7 +12770,7 @@
         <v>549</v>
       </c>
       <c r="I291" s="0" t="s">
-        <v>762</v>
+        <v>1068</v>
       </c>
       <c r="J291" s="0">
         <v>386.12639999999999</v>
@@ -12802,7 +12802,7 @@
         <v>550</v>
       </c>
       <c r="I292" s="0" t="s">
-        <v>763</v>
+        <v>1069</v>
       </c>
       <c r="J292" s="0">
         <v>381.40570000000002</v>
@@ -12834,7 +12834,7 @@
         <v>551</v>
       </c>
       <c r="I293" s="0" t="s">
-        <v>764</v>
+        <v>1070</v>
       </c>
       <c r="J293" s="0">
         <v>371.59660000000002</v>
@@ -12866,7 +12866,7 @@
         <v>552</v>
       </c>
       <c r="I294" s="0" t="s">
-        <v>765</v>
+        <v>1071</v>
       </c>
       <c r="J294" s="0">
         <v>364.02569999999997</v>
@@ -12898,7 +12898,7 @@
         <v>553</v>
       </c>
       <c r="I295" s="0" t="s">
-        <v>766</v>
+        <v>1072</v>
       </c>
       <c r="J295" s="0">
         <v>331.7552</v>
@@ -12930,7 +12930,7 @@
         <v>554</v>
       </c>
       <c r="I296" s="0" t="s">
-        <v>767</v>
+        <v>1073</v>
       </c>
       <c r="J296" s="0">
         <v>1621.762</v>
@@ -12962,7 +12962,7 @@
         <v>555</v>
       </c>
       <c r="I297" s="0" t="s">
-        <v>768</v>
+        <v>1074</v>
       </c>
       <c r="J297" s="0">
         <v>1023.5883</v>
@@ -12994,7 +12994,7 @@
         <v>556</v>
       </c>
       <c r="I298" s="0" t="s">
-        <v>769</v>
+        <v>1075</v>
       </c>
       <c r="J298" s="0">
         <v>634.67409999999995</v>
@@ -13026,7 +13026,7 @@
         <v>557</v>
       </c>
       <c r="I299" s="0" t="s">
-        <v>770</v>
+        <v>1076</v>
       </c>
       <c r="J299" s="0">
         <v>589.45230000000004</v>
@@ -13058,7 +13058,7 @@
         <v>558</v>
       </c>
       <c r="I300" s="0" t="s">
-        <v>771</v>
+        <v>1077</v>
       </c>
       <c r="J300" s="0">
         <v>441.32260000000002</v>
@@ -13090,7 +13090,7 @@
         <v>559</v>
       </c>
       <c r="I301" s="0" t="s">
-        <v>772</v>
+        <v>1078</v>
       </c>
       <c r="J301" s="0">
         <v>406.00639999999999</v>
@@ -13122,7 +13122,7 @@
         <v>560</v>
       </c>
       <c r="I302" s="0" t="s">
-        <v>773</v>
+        <v>1079</v>
       </c>
       <c r="J302" s="0">
         <v>404.98939999999999</v>
@@ -13154,7 +13154,7 @@
         <v>561</v>
       </c>
       <c r="I303" s="0" t="s">
-        <v>774</v>
+        <v>1080</v>
       </c>
       <c r="J303" s="0">
         <v>356.87450000000001</v>
@@ -13186,7 +13186,7 @@
         <v>562</v>
       </c>
       <c r="I304" s="0" t="s">
-        <v>775</v>
+        <v>1081</v>
       </c>
       <c r="J304" s="0">
         <v>326.86750000000001</v>
@@ -13218,7 +13218,7 @@
         <v>563</v>
       </c>
       <c r="I305" s="0" t="s">
-        <v>776</v>
+        <v>1082</v>
       </c>
       <c r="J305" s="0">
         <v>313.15320000000003</v>
@@ -13250,7 +13250,7 @@
         <v>564</v>
       </c>
       <c r="I306" s="0" t="s">
-        <v>777</v>
+        <v>1083</v>
       </c>
       <c r="J306" s="0">
         <v>302.25330000000002</v>
@@ -13282,7 +13282,7 @@
         <v>565</v>
       </c>
       <c r="I307" s="0" t="s">
-        <v>778</v>
+        <v>1084</v>
       </c>
       <c r="J307" s="0">
         <v>241.7327</v>
@@ -13314,7 +13314,7 @@
         <v>129</v>
       </c>
       <c r="I308" s="0" t="s">
-        <v>452</v>
+        <v>1085</v>
       </c>
       <c r="J308" s="0">
         <v>8389.2909999999993</v>
@@ -13346,7 +13346,7 @@
         <v>130</v>
       </c>
       <c r="I309" s="0" t="s">
-        <v>453</v>
+        <v>1086</v>
       </c>
       <c r="J309" s="0">
         <v>8068.0429999999997</v>
@@ -13378,7 +13378,7 @@
         <v>208</v>
       </c>
       <c r="I310" s="0" t="s">
-        <v>454</v>
+        <v>1087</v>
       </c>
       <c r="J310" s="0">
         <v>1304.9119000000001</v>
@@ -13410,7 +13410,7 @@
         <v>133</v>
       </c>
       <c r="I311" s="0" t="s">
-        <v>456</v>
+        <v>1088</v>
       </c>
       <c r="J311" s="0">
         <v>528.16520000000003</v>
@@ -13442,7 +13442,7 @@
         <v>134</v>
       </c>
       <c r="I312" s="0" t="s">
-        <v>457</v>
+        <v>1089</v>
       </c>
       <c r="J312" s="0">
         <v>464.43889999999999</v>
@@ -13474,7 +13474,7 @@
         <v>135</v>
       </c>
       <c r="I313" s="0" t="s">
-        <v>458</v>
+        <v>1090</v>
       </c>
       <c r="J313" s="0">
         <v>449.87619999999998</v>
@@ -13506,7 +13506,7 @@
         <v>136</v>
       </c>
       <c r="I314" s="0" t="s">
-        <v>459</v>
+        <v>1091</v>
       </c>
       <c r="J314" s="0">
         <v>447.66699999999997</v>
@@ -13538,7 +13538,7 @@
         <v>137</v>
       </c>
       <c r="I315" s="0" t="s">
-        <v>460</v>
+        <v>1092</v>
       </c>
       <c r="J315" s="0">
         <v>391.69869999999997</v>
@@ -13570,7 +13570,7 @@
         <v>138</v>
       </c>
       <c r="I316" s="0" t="s">
-        <v>461</v>
+        <v>1093</v>
       </c>
       <c r="J316" s="0">
         <v>372.4153</v>
@@ -13602,7 +13602,7 @@
         <v>139</v>
       </c>
       <c r="I317" s="0" t="s">
-        <v>462</v>
+        <v>1094</v>
       </c>
       <c r="J317" s="0">
         <v>366.97289999999998</v>
@@ -13634,7 +13634,7 @@
         <v>140</v>
       </c>
       <c r="I318" s="0" t="s">
-        <v>463</v>
+        <v>1095</v>
       </c>
       <c r="J318" s="0">
         <v>329.11259999999999</v>
@@ -13666,7 +13666,7 @@
         <v>58</v>
       </c>
       <c r="I319" s="0" t="s">
-        <v>464</v>
+        <v>1096</v>
       </c>
       <c r="J319" s="0">
         <v>9741.5614999999998</v>
@@ -13698,7 +13698,7 @@
         <v>59</v>
       </c>
       <c r="I320" s="0" t="s">
-        <v>465</v>
+        <v>1097</v>
       </c>
       <c r="J320" s="0">
         <v>8198.8974999999991</v>
@@ -13730,7 +13730,7 @@
         <v>60</v>
       </c>
       <c r="I321" s="0" t="s">
-        <v>466</v>
+        <v>1098</v>
       </c>
       <c r="J321" s="0">
         <v>1259.1116</v>
@@ -13762,7 +13762,7 @@
         <v>210</v>
       </c>
       <c r="I322" s="0" t="s">
-        <v>467</v>
+        <v>1099</v>
       </c>
       <c r="J322" s="0">
         <v>964.0145</v>
@@ -13794,7 +13794,7 @@
         <v>141</v>
       </c>
       <c r="I323" s="0" t="s">
-        <v>468</v>
+        <v>1100</v>
       </c>
       <c r="J323" s="0">
         <v>539.45429999999999</v>
@@ -13826,7 +13826,7 @@
         <v>142</v>
       </c>
       <c r="I324" s="0" t="s">
-        <v>469</v>
+        <v>1101</v>
       </c>
       <c r="J324" s="0">
         <v>485.64830000000001</v>
@@ -13858,7 +13858,7 @@
         <v>143</v>
       </c>
       <c r="I325" s="0" t="s">
-        <v>470</v>
+        <v>1102</v>
       </c>
       <c r="J325" s="0">
         <v>457.39609999999999</v>
@@ -13890,7 +13890,7 @@
         <v>144</v>
       </c>
       <c r="I326" s="0" t="s">
-        <v>471</v>
+        <v>1103</v>
       </c>
       <c r="J326" s="0">
         <v>454.66460000000001</v>
@@ -13922,7 +13922,7 @@
         <v>145</v>
       </c>
       <c r="I327" s="0" t="s">
-        <v>472</v>
+        <v>1104</v>
       </c>
       <c r="J327" s="0">
         <v>368.51979999999998</v>
@@ -13954,7 +13954,7 @@
         <v>146</v>
       </c>
       <c r="I328" s="0" t="s">
-        <v>473</v>
+        <v>1105</v>
       </c>
       <c r="J328" s="0">
         <v>342.74220000000003</v>
@@ -13986,7 +13986,7 @@
         <v>147</v>
       </c>
       <c r="I329" s="0" t="s">
-        <v>474</v>
+        <v>1106</v>
       </c>
       <c r="J329" s="0">
         <v>302.46800000000002</v>
@@ -14018,7 +14018,7 @@
         <v>148</v>
       </c>
       <c r="I330" s="0" t="s">
-        <v>475</v>
+        <v>1107</v>
       </c>
       <c r="J330" s="0">
         <v>300.47250000000003</v>
@@ -14050,7 +14050,7 @@
         <v>149</v>
       </c>
       <c r="I331" s="0" t="s">
-        <v>476</v>
+        <v>1108</v>
       </c>
       <c r="J331" s="0">
         <v>10892.9414</v>
@@ -14082,7 +14082,7 @@
         <v>150</v>
       </c>
       <c r="I332" s="0" t="s">
-        <v>477</v>
+        <v>1109</v>
       </c>
       <c r="J332" s="0">
         <v>5918.6806999999999</v>
@@ -14114,7 +14114,7 @@
         <v>152</v>
       </c>
       <c r="I333" s="0" t="s">
-        <v>479</v>
+        <v>1110</v>
       </c>
       <c r="J333" s="0">
         <v>726.14110000000005</v>
@@ -14146,7 +14146,7 @@
         <v>153</v>
       </c>
       <c r="I334" s="0" t="s">
-        <v>480</v>
+        <v>1111</v>
       </c>
       <c r="J334" s="0">
         <v>498.3132</v>
@@ -14178,7 +14178,7 @@
         <v>154</v>
       </c>
       <c r="I335" s="0" t="s">
-        <v>481</v>
+        <v>1112</v>
       </c>
       <c r="J335" s="0">
         <v>487.10520000000002</v>
@@ -14210,7 +14210,7 @@
         <v>155</v>
       </c>
       <c r="I336" s="0" t="s">
-        <v>482</v>
+        <v>1113</v>
       </c>
       <c r="J336" s="0">
         <v>485.66770000000002</v>
@@ -14242,7 +14242,7 @@
         <v>156</v>
       </c>
       <c r="I337" s="0" t="s">
-        <v>483</v>
+        <v>1114</v>
       </c>
       <c r="J337" s="0">
         <v>478.11529999999999</v>
@@ -14274,7 +14274,7 @@
         <v>157</v>
       </c>
       <c r="I338" s="0" t="s">
-        <v>484</v>
+        <v>1115</v>
       </c>
       <c r="J338" s="0">
         <v>375.48970000000003</v>
@@ -14306,7 +14306,7 @@
         <v>158</v>
       </c>
       <c r="I339" s="0" t="s">
-        <v>485</v>
+        <v>1116</v>
       </c>
       <c r="J339" s="0">
         <v>359.0838</v>
@@ -14338,7 +14338,7 @@
         <v>159</v>
       </c>
       <c r="I340" s="0" t="s">
-        <v>486</v>
+        <v>1117</v>
       </c>
       <c r="J340" s="0">
         <v>338.9837</v>
@@ -14370,7 +14370,7 @@
         <v>160</v>
       </c>
       <c r="I341" s="0" t="s">
-        <v>487</v>
+        <v>1118</v>
       </c>
       <c r="J341" s="0">
         <v>293.55579999999998</v>
@@ -14402,7 +14402,7 @@
         <v>161</v>
       </c>
       <c r="I342" s="0" t="s">
-        <v>488</v>
+        <v>1119</v>
       </c>
       <c r="J342" s="0">
         <v>9826.1103999999996</v>
@@ -14434,7 +14434,7 @@
         <v>162</v>
       </c>
       <c r="I343" s="0" t="s">
-        <v>489</v>
+        <v>1120</v>
       </c>
       <c r="J343" s="0">
         <v>7957.9004000000004</v>
@@ -14466,7 +14466,7 @@
         <v>163</v>
       </c>
       <c r="I344" s="0" t="s">
-        <v>490</v>
+        <v>1121</v>
       </c>
       <c r="J344" s="0">
         <v>1958.7829999999999</v>
@@ -14498,7 +14498,7 @@
         <v>165</v>
       </c>
       <c r="I345" s="0" t="s">
-        <v>492</v>
+        <v>1122</v>
       </c>
       <c r="J345" s="0">
         <v>574.80640000000005</v>
@@ -14530,7 +14530,7 @@
         <v>166</v>
       </c>
       <c r="I346" s="0" t="s">
-        <v>493</v>
+        <v>1123</v>
       </c>
       <c r="J346" s="0">
         <v>532.89999999999998</v>
@@ -14562,7 +14562,7 @@
         <v>167</v>
       </c>
       <c r="I347" s="0" t="s">
-        <v>494</v>
+        <v>1124</v>
       </c>
       <c r="J347" s="0">
         <v>470.99040000000002</v>
@@ -14594,7 +14594,7 @@
         <v>168</v>
       </c>
       <c r="I348" s="0" t="s">
-        <v>495</v>
+        <v>1125</v>
       </c>
       <c r="J348" s="0">
         <v>428.05349999999999</v>
@@ -14626,7 +14626,7 @@
         <v>169</v>
       </c>
       <c r="I349" s="0" t="s">
-        <v>496</v>
+        <v>1126</v>
       </c>
       <c r="J349" s="0">
         <v>370.83409999999998</v>
@@ -14658,7 +14658,7 @@
         <v>170</v>
       </c>
       <c r="I350" s="0" t="s">
-        <v>497</v>
+        <v>1127</v>
       </c>
       <c r="J350" s="0">
         <v>361.65289999999999</v>
@@ -14690,7 +14690,7 @@
         <v>171</v>
       </c>
       <c r="I351" s="0" t="s">
-        <v>498</v>
+        <v>1128</v>
       </c>
       <c r="J351" s="0">
         <v>328.18830000000003</v>
@@ -14722,7 +14722,7 @@
         <v>172</v>
       </c>
       <c r="I352" s="0" t="s">
-        <v>499</v>
+        <v>1129</v>
       </c>
       <c r="J352" s="0">
         <v>313.28399999999999</v>
